--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>元素体系与化学式</t>
+          <t>元素体系与化学式（掺杂/合金/异质结明细走标准写法）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>标准写法待定：找国标或组内定一套</t>
+          <t>标准写法待定：找国标或组内定</t>
         </is>
       </c>
     </row>
@@ -1063,22 +1063,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>掺杂/合金/异质结</t>
+          <t>结构类型</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>掺杂剂或异质结构</t>
+          <t>材料结构类别（是否掺杂/合金/异质结，供机器检索）</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>本征/掺杂/合金/垂直异质结/横向异质结/其他</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>无 ／ WS₂/MoS₂垂直异质结</t>
+          <t>垂直异质结</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1101,9 +1101,9 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>存储方式（是否并入化学式）待议；v3暂保留独立字段</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>★v3定稿新增；明细(掺杂元素/位点、异质结上下层)走化学式标准写法</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>应用导向的目标性能（须写清用什么方法/条件测）</t>
+          <t>应用导向的目标性能（写清想要什么性能 + 打算用什么方法/判据衡量）</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>带隙≈1.8 eV（PL，室温）</t>
+          <t>高迁移率（拟FET场效应测）</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>没写方法的性能没意义</t>
+          <t>目标=愿景保持轻量；严格『数值绑测试方法』在§7实测侧</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>§6 过程事件（如实记客观事件，不是『失败』；模块中英文命名待定）</t>
+          <t>§6 过程事件 Process Events（含异常/中断/人工干预等客观事件；只记客观事实、不判成败）</t>
         </is>
       </c>
       <c r="B63" s="3" t="n"/>
@@ -3446,17 +3446,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>事件类型（含关联对象）</t>
+          <t>事件/部位</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>过程中发生的客观事件 + 关联对象（合并）</t>
+          <t>过程中发生的客观事件 + 关联部位（合并）</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3498,7 +3498,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3598,7 +3598,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -4333,7 +4333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>§1b『掺杂/合金/异质结』仍为独立字段；§3『舟/坩埚』仍长×宽×高</t>
+          <t>§3『舟/坩埚』仍长×宽×高（未拆高）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4608,27 +4608,103 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>── 2026-07-06 表头定稿修订 ──</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>v3.1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>§1b</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>掺杂/合金/异质结自由文本 → 新增『结构类型』下拉多选（本征/掺杂/合金/垂直·横向异质结）；明细走化学式标准写法</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>定稿修订</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>v3.1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>§6</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>模块定名『过程事件 Process Events』；『事件类型(含关联对象)』→『事件/部位』</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>定稿修订</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>v3.1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>§1b</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>目标性能保持轻量自由文本（性能+衡量方法）；严格『数值绑测试方法』落在§7实测侧</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>定稿修订</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>硬必填核心(15项)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>实验时间·合成方法·实验人·样品/实验编号·装置·温区数·炉体方向·前驱体名称·前驱体用量·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系(生长)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>
@@ -4645,7 +4721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4678,12 +4754,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>掺杂/合金/异质结存储：并入化学式标准写法串 vs 独立结构化字段</t>
+          <t>记录最小单元：一炉一行 vs 以样品为主线挂生长/表征事件</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>待议（v3暂保留独立字段）</t>
+          <t>待议(技术)</t>
         </is>
       </c>
     </row>
@@ -4695,12 +4771,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>记录最小单元：一炉一行 vs 以样品为主线挂生长/表征事件</t>
+          <t>化学式 / 异质结 标准写法（找国标或组内定一套）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>待议</t>
+          <t>待办(归入重写标准文档)</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4788,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>化学式 / 异质结 标准写法（找国标或组内定一套）</t>
+          <t>化学式录入方式：化学周期表点选 vs 文本输入</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>待办</t>
+          <t>待办(技术)</t>
         </is>
       </c>
     </row>
@@ -4729,63 +4805,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>§6 过程事件 中英文命名（直白且严谨）</t>
+          <t>表征独立表的关联模型/批次选择</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>待办</t>
+          <t>待办(技术)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>化学式录入方式：化学周期表点选 vs 文本输入</t>
+          <t>已定稿：掺杂→结构类型 · §6命名 · 目标性能措辞</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>待办(技术)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>表征独立表的关联模型/批次选择</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>待办(技术)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>目标性能须绑测试方法——最终措辞</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>待老师</t>
+          <t>见『v2→v3变更说明』</t>
         </is>
       </c>
     </row>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>元素体系与化学式（掺杂/合金/异质结明细走标准写法）</t>
+          <t>元素体系与化学式（规范/显示串，可由组成明细自动生成）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>标准写法（另定）</t>
+          <t>标准写法（渲染规则）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1034,14 +1034,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Mo–S / MoS₂</t>
+          <t>MoS₂</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1049,9 +1049,9 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>标准写法待定：找国标或组内定</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2升R0；结构化明细见『组成明细』</t>
         </is>
       </c>
     </row>
@@ -1101,9 +1101,9 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>★v3定稿新增；明细(掺杂元素/位点、异质结上下层)走化学式标准写法</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>判别器</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1115,47 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>目标层数</t>
+          <t>组成明细(components)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>期望层数</t>
+          <t>逐组分结构化：化学式·角色·数量，供机器检索</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>数组items[]</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>每条:化学式/角色(基体·掺杂剂·上层·下层·横向域)/数量(at%或层序)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>1（单层）</t>
+          <t>{MoS₂,基体};{Nb,掺杂剂,0.5at%}</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>目标与实测分开</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2新增；替代把掺杂/异质结塞进化学式串（Fable评审）</t>
         </is>
       </c>
     </row>
@@ -1167,47 +1167,47 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>体相空间群</t>
+          <t>目标层数</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>晶体对称性：用体相空间群号 + 说明单层结构</t>
+          <t>期望层数</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>下拉+文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>空间群号(1–230)+单层结构说明；未指定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>层</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>194(P6₃/mmc)，单层2H</t>
+          <t>1（单层）</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>★v3：从『层群/点群/多型』改回体相空间群；手性/扭转角/堆垛→备注</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>目标与实测分开</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>样品形态</t>
+          <t>体相空间群</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>目标形态</t>
+          <t>晶体对称性：用体相空间群号 + 说明单层结构</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉+文本</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>连续膜/纳米片(flake)/纳米带/纳米管/纳米棒/纳米颗粒/其他</t>
+          <t>空间群号(1–230)+单层结构说明；未指定</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1242,22 +1242,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>单层连续膜</t>
+          <t>194(P6₃/mmc)，单层2H</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>★v3：从『层群/点群/多型』改回体相空间群；手性/扭转角/堆垛→备注</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1267,37 +1271,37 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>目标性能</t>
+          <t>样品形态</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>应用导向的目标性能（写清想要什么性能 + 打算用什么方法/判据衡量）</t>
+          <t>目标形态</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>自由+数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>连续膜/纳米片(flake)/纳米带/纳米管/纳米棒/纳米颗粒/其他</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>视性能</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>高迁移率（拟FET场效应测）</t>
+          <t>单层连续膜</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1305,11 +1309,7 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>目标=愿景保持轻量；严格『数值绑测试方法』在§7实测侧</t>
-        </is>
-      </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1319,109 +1319,113 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>目标性能</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>应用导向的目标性能（写清想要什么性能 + 打算用什么方法/判据衡量）</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>自由+数值</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>视性能</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>高迁移率（拟FET场效应测）</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>目标=愿景保持轻量；严格『数值绑测试方法』在§7实测侧</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>目标产物</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>补充说明（手性/扭转角/堆垛类型等放这里）</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>自由</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>盐辅助法，追求大畴单层；手性:右手</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>§2 实验设备与设计（用到的炉子/装置——一台炉录一次，以后直接引用）</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>设备</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>装置（引用）</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>选择已登记的装置</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>装置库</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>1号双温区管式炉</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1431,22 +1435,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>品牌/型号</t>
+          <t>装置（引用）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>设备品牌与型号</t>
+          <t>选择已登记的装置</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>装置库</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1454,14 +1458,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1479,22 +1483,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>品牌/型号</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>热壁炉还是冷壁炉（影响生长机理）</t>
+          <t>设备品牌与型号</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1509,12 +1513,12 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>合肥科晶 OTF-1200X</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
@@ -1527,42 +1531,42 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>独立控温的温区数量</t>
+          <t>热壁炉还是冷壁炉（影响生长机理）</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1/2/3…</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
@@ -1575,27 +1579,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>炉管水平还是竖直</t>
+          <t>独立控温的温区数量</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>1/2/3…</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1623,22 +1627,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>管材质/形状</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>炉管材料与截面形状</t>
+          <t>炉管水平还是竖直</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>石英/刚玉；圆/方/矩</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1646,14 +1650,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>石英·圆形</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1671,27 +1675,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>管外径/壁厚</t>
+          <t>管材质/形状</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>管径规格与壁厚（内径自动算）</t>
+          <t>炉管材料与截面形状</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1″/2″/4″/自定义 + 壁厚</t>
+          <t>石英/刚玉；圆/方/矩</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>1″(25.4)，壁厚2</t>
+          <t>石英·圆形</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1709,11 +1713,7 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>内径决定流速/分压</t>
-        </is>
-      </c>
+      <c r="J26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1723,47 +1723,47 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>坐标系</t>
+          <t>管外径/壁厚</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>本装置位置参照；全局固定、不可编辑</t>
+          <t>管径规格与壁厚（内径自动算）</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上游为负 / 下游为正，原点固定</t>
+          <t>1″/2″/4″/自定义 + 壁厚</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>定义项</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>1″(25.4)，壁厚2</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>内径决定流速/分压</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1775,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>外场激励</t>
+          <t>坐标系</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>是否有等离子/光/电场（区分PECVD/光CVD）</t>
+          <t>本装置位置参照；全局固定、不可编辑</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>多选+展开</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>无/等离子/光/电</t>
+          <t>上游为负 / 下游为正，原点固定</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1798,24 +1798,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>仅选『用了哪些』；定量参数在§5，定性几何进示意图</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
         </is>
       </c>
     </row>
@@ -1827,22 +1827,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>装置示意图/描述</t>
+          <t>外场激励</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>装置照片或示意图 + 文字批注</t>
+          <t>是否有等离子/光/电场（区分PECVD/光CVD）</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>附件+自由</t>
+          <t>多选+展开</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无/等离子/光/电</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1850,22 +1850,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>setup.png + 卧式双温区</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>仅选『用了哪些』；定量参数在§5，定性几何进示意图</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1875,113 +1879,113 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>装置示意图/描述</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>装置照片或示意图 + 文字批注</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>附件+自由</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>setup.png + 卧式双温区</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>炉管/舟履历</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>累计使用与重置情况</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>数值×2</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>重置次数 + 重置后使用次数</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>次</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>重置1，之后用7</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>★v3：自由文本→结构化两数字；退火/清管方法另记</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>§3 前驱体（用了哪些原料：主源、辅助剂等，可多个；每个一组）</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>名称/化学式</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>原料名称与化学式</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>受控+其他</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>三氧化钼 / MoO₃</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1991,22 +1995,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CAS/InChI</t>
+          <t>名称/化学式</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>唯一化学标识（消除同名歧义）</t>
+          <t>原料名称与化学式</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>CAS 或 InChI</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2014,19 +2018,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>1313-27-5</t>
+          <t>三氧化钼 / MoO₃</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
@@ -2039,22 +2043,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>CAS/InChI</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
+          <t>唯一化学标识（消除同名歧义）</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>CAS 或 InChI</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2062,26 +2066,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>MoO₃-B202（锁 v1）</t>
+          <t>1313-27-5</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>防以后改批次信息影响旧记录</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2091,22 +2091,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>角色（role）</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>在反应里的角色</t>
+          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>主源/辅助剂/掺杂源/其他</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2114,24 +2114,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>主源</t>
+          <t>MoO₃-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>界面中文(英文)</t>
+          <t>防以后改批次信息影响旧记录</t>
         </is>
       </c>
     </row>
@@ -2143,47 +2143,47 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>角色（role）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>投料量（只记投料，不记残余）</t>
+          <t>在反应里的角色</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>主源/辅助剂/掺杂源/其他</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>mg</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>主源</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>★v3：推荐→必填（纳入R0）</t>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>界面中文(英文)</t>
         </is>
       </c>
     </row>
@@ -2195,45 +2195,49 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>用量</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>投料前处理（可多步，选了再展开参数）</t>
+          <t>投料量（只记投料，不记残余）</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>直接加载/熔融凝固/压片/旋涂/退火/研磨/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>见展开</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>条件必填(固态源)</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>直接加载</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2：气态源/PVD无mg，改条件必填</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2243,27 +2247,27 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>舟/坩埚</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>盛装容器材质与尺寸</t>
+          <t>投料前处理（可多步，选了再展开参数）</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>石英舟/陶瓷(刚玉)舟/其他；长×宽×高（直径）</t>
+          <t>直接加载/熔融凝固/压片/旋涂/退火/研磨/其他</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>见展开</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -2273,19 +2277,15 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>石英舟 90×15</t>
+          <t>直接加载</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>v3暂保留长×宽×高</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>所在温区/源温</t>
+          <t>舟/坩埚</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>放第几温区、源温（若可设/可测）</t>
+          <t>盛装容器材质与尺寸</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>温区1…</t>
+          <t>石英舟/陶瓷(刚玉)舟/其他；长×宽×高（直径）</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>温区1，设定~620</t>
+          <t>石英舟 90×15</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>按进气端编号</t>
+          <t>v3暂保留长×宽×高</t>
         </is>
       </c>
     </row>
@@ -2347,113 +2347,117 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
+          <t>所在温区/源温</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>放第几温区、源温（若可设/可测）</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>下拉+数值</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>温区1…</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>温区1，设定~620</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>按进气端编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>前驱体</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
           <t>距热电偶距离</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>距所在温区热电偶的水平距离</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>上游为负、下游为正</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>§4 衬底（长在什么基底上，可多片）</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>衬底材料</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>衬底种类</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>SiO₂/Si</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr"/>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2463,22 +2467,22 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>化学式/取向</t>
+          <t>衬底材料</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>化学式与晶面取向/偏转角</t>
+          <t>衬底种类</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>标准写法（如 x面向x轴偏X°）</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2486,14 +2490,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Si(100)</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2501,11 +2505,7 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>单晶记取向+偏转角</t>
-        </is>
-      </c>
+      <c r="J43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2515,37 +2515,37 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>氧化层厚度</t>
+          <t>化学式/取向</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）</t>
+          <t>化学式与晶面取向/偏转角</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>写成 SiO₂/Si(285nm)</t>
+          <t>标准写法（如 x面向x轴偏X°）</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>Si(100)</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2553,7 +2553,11 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>单晶记取向+偏转角</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2563,12 +2567,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>表面粗糙度</t>
+          <t>氧化层厚度</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Ra / RMS</t>
+          <t>SiO₂ 层厚度（决定光学判层数）</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2578,7 +2582,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>写成 SiO₂/Si(285nm)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2586,26 +2590,22 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>&lt;1</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>常比化学式更决定成核；可问厂家或AFM</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2615,27 +2615,27 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>尺寸/朝向</t>
+          <t>表面粗糙度</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>几何尺寸与放置朝向</t>
+          <t>Ra / RMS</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>数值+下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>长×宽×厚；正放/倒扣/倾角/竖放</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2645,15 +2645,19 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>10×10×0.5；正放</t>
+          <t>&lt;1</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>会议/建议</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>常比化学式更决定成核；可问厂家或AFM</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2663,42 +2667,42 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>尺寸/朝向</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>几何尺寸与放置朝向</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值+下拉</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>清洗/退火/等离子/亲水化/其他</t>
+          <t>长×宽×厚；正放/倒扣/倾角/竖放</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>见展开</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>丙酮→异丙醇→N₂吹干</t>
+          <t>10×10×0.5；正放</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>会议/建议</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr"/>
@@ -2711,49 +2715,45 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>处理到装炉间隔/暴露环境</t>
+          <t>预处理（有序步骤）</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>清洗后到装炉的时间与环境</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>清洗/退火/等离子/亲水化/其他</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>见展开</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>30 min，空气</t>
+          <t>丙酮→异丙醇→N₂吹干</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>表面老化</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2763,113 +2763,113 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
+          <t>处理到装炉间隔/暴露环境</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>清洗后到装炉的时间与环境</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>30 min，空气</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>表面老化</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>所在温区/距热电偶距离</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>第几温区、距离(±)</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>下拉+数值</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>温区2…</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>温区2，+15</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>§5 反应条件（按时间顺序的各阶段；每阶段填同一套：气体/温度/压力/时长；阶段类型驱动动态表单）</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
-      <c r="J50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>阶段类型</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>这一步在做什么（选后只显示对应参数）</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>抽气/漏检/吹扫/预处理/升温/温度稳定/反应生长/后退火/降温/放气/卸样</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>反应生长</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>多步可加；跨组比较看类型</t>
-        </is>
-      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -2879,69 +2879,69 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>步序/起止时刻</t>
+          <t>阶段类型</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>第几步、起止时间</t>
+          <t>这一步在做什么（选后只显示对应参数）</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>数值+时间</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>抽气/漏检/吹扫/预处理/升温/温度稳定/反应生长/后退火/降温/放气/卸样</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>#3，10:20–10:35</t>
+          <t>反应生长</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>支持重叠/循环</t>
+          <t>多步可加；跨组比较看类型</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>步序/起止时刻</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>各温区升温曲线（目标温/速率/保温）</t>
+          <t>第几步、起止时间</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>数组</t>
+          <t>数值+时间</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2951,27 +2951,27 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>℃·℃/min·min</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>温区2：25→750@20℃/min，保温15</t>
+          <t>#3，10:20–10:35</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>设定值；分温区</t>
+          <t>支持重叠/循环</t>
         </is>
       </c>
     </row>
@@ -2983,17 +2983,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>实测温度</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>控温热电偶实测曲线（导入）。注意：不是衬底真温</t>
+          <t>各温区升温曲线（目标温/速率/保温）</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>数组(时序)</t>
+          <t>数组</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -3003,27 +3003,27 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>℃·℃/min·min</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>[导入 furnace.csv]</t>
+          <t>温区2：25→750@20℃/min，保温15</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>★v3：删『估算衬底真温』，只留设定+实测</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>设定值；分温区</t>
         </is>
       </c>
     </row>
@@ -3035,37 +3035,37 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>测温设备/不确定度</t>
+          <t>实测温度</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>测温点用什么设备、不确定度多少</t>
+          <t>控温热电偶实测曲线（导入）。注意：不是衬底真温</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>引用+数值</t>
+          <t>数组(时序)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>热电偶/高温计；来源：仪器/校准/重复性/估计</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>K型热电偶，±1℃</t>
+          <t>[导入 furnace.csv]</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -3073,107 +3073,115 @@
           <t>会议/复审</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>测量不确定度</t>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>★v3：删『估算衬底真温』，只留设定+实测</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>气体组分</t>
+          <t>测温设备/不确定度</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>每种气体单独一条（混合气拆开）</t>
+          <t>测温点用什么设备、不确定度多少</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>下拉(多条)</t>
+          <t>引用+数值</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Ar/N₂/H₂/O₂/CH₄/其他</t>
+          <t>热电偶/高温计；来源：仪器/校准/重复性/估计</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t>K型热电偶，±1℃</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>测量不确定度</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>纯度/浓度/水氧</t>
+          <t>降温方式/开盖温度/速率</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>纯度、体积比、水氧杂质</t>
+          <t>降温段参数（阶段类型=降温 时）</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>随炉冷却/开盖冷却/移炉快速冷却；开盖温度；降温速率</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>N·%·ppm</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>条件必填(降温段)</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Ar 5N；水氧&lt;1ppm</t>
+          <t>随炉冷却；开盖~580</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2补回：review文档头部隐变量，勿再漏（Fable评审）</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -3183,27 +3191,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>流量/来源</t>
+          <t>气体组分</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>流量、流量计类型</t>
+          <t>每种气体单独一条（混合气拆开）</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>数值+下拉</t>
+          <t>下拉(多条)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>MFC/转子</t>
+          <t>Ar/N₂/H₂/O₂/CH₄/其他</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>sccm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3213,111 +3221,103 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>80（MFC）</t>
+          <t>Ar</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>sccm须绑标准状态；设定+实测</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>压力体系/工作压力</t>
+          <t>纯度/浓度/水氧</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>常压/低压/超高真空 + 工作压力</t>
+          <t>纯度、体积比、水氧杂质</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>必填(生长)/选填(其余)</t>
+          <t>N·%·ppm</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>常压；1.0×10⁵ Pa</t>
+          <t>Ar 5N；水氧&lt;1ppm</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>所有阶段可出现</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>本底压力/漏率</t>
+          <t>流量/来源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>反应前底压、漏率</t>
+          <t>流量、流量计类型</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>数值+下拉</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFC/转子</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Pa·Pa·L/s</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>sccm</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80（MFC）</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3325,47 +3325,51 @@
           <t>会议/复审</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>sccm须绑标准状态；设定+实测</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>时长/循环次数</t>
+          <t>压力体系/工作压力</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>本阶段时长、吹扫抽-充次数</t>
+          <t>常压/低压/超高真空 + 工作压力</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>min·次</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>必填/选填</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>必填(生长)/选填(其余)</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>常压；1.0×10⁵ Pa</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3373,22 +3377,26 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>所有阶段可出现</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>外场参数</t>
+          <t>本底压力/漏率</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>等离子功率/光源（有外场才填，可自填添加）</t>
+          <t>反应前底压、漏率</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3398,12 +3406,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>电场强度；光场:中心波长/线宽/功率密度/光斑大小</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>V·nm·W…</t>
+          <t>Pa·Pa·L/s</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -3418,60 +3426,88 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>setup无外场则不显示</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（含异常/中断/人工干预等客观事件；只记客观事实、不判成败）</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-      <c r="J63" s="3" t="n"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>时长/循环次数</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>本阶段时长、吹扫抽-充次数</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>min·次</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>必填/选填</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>事件/部位</t>
+          <t>外场参数</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>过程中发生的客观事件 + 关联部位（合并）</t>
+          <t>等离子功率/光源（有外场才填，可自填添加）</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>供电/供水/供气中断·管路堵塞·压力突变·信号异常·人工干预·其他（可加）</t>
+          <t>电场强度；光场:中心波长/线宽/功率密度/光斑大小</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>V·nm·W…</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3481,71 +3517,35 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>气流中断（Ar气路）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>★v3：事件类型与关联对象合并为一个下拉</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>发生时刻</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>何时发生（记绝对时间）</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>相对时间可由t0算</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>setup无外场则不显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（含异常/中断/人工干预等客观事件；只记客观事实、不判成败）</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -3555,22 +3555,22 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>中止原因</t>
+          <t>事件/部位</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>若中止（只记客观原因，不写成败）</t>
+          <t>过程中发生的客观事件 + 关联部位（合并）</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划结束</t>
+          <t>供电/供水/供气中断·管路堵塞·压力突变·信号异常·人工干预·其他（可加）</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>计划结束</t>
+          <t>气流中断（Ar气路）</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3593,7 +3593,11 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr"/>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>★v3：事件类型与关联对象合并为一个下拉</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -3603,17 +3607,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>描述/措施/附件</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>现象、处理、相关文件</t>
+          <t>何时发生（记绝对时间）</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>自由+附件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3633,7 +3637,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Ar瓶压不足，已更换</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3641,48 +3645,84 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="3" t="n"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>相对时间可由t0算</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>中止原因</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>若中止（只记客观原因，不写成败）</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>设备报警/人工停止/计划结束</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>计划结束</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>表征类型/仪器</t>
+          <t>描述/措施/附件</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>表征手段 + 引用仪器</t>
+          <t>现象、处理、相关文件</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>自由+附件</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3690,14 +3730,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Ar瓶压不足，已更换</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3705,63 +3745,23 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>测试条件</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>该表征的测试参数</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>文本/自由</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>视仪器</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>532nm / 1mW / 100×</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
-        </is>
-      </c>
+      <c r="J69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+      <c r="J70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -3771,22 +3771,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>表征类型/仪器</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>表征手段 + 引用仪器</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3801,35 +3801,39 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>检出相/多型</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>测到的物相/多型</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -3839,49 +3843,49 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>视仪器</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>2H-MoS₂</t>
+          <t>532nm / 1mW / 100×</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>最小结构化结果</t>
+          <t>随仪器导出</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>实测层数/覆盖率</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>实测层数与覆盖率</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3891,22 +3895,22 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>层·%</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>1 层；~70%</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr"/>
@@ -3919,23 +3923,27 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>畴尺寸/成核密度/连续性</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr"/>
+          <t>观察到的现象</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>光镜可判的客观现象（非成败判断）</t>
+        </is>
+      </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>μm·cm⁻²·(连续/孤立)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -3945,7 +3953,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>畴 ~50 μm</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3953,7 +3961,11 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr"/>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2新增；替代被废失败模式词表的客观部分，失败炉次最小痕迹（Fable评审）</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3963,105 +3975,133 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>关键谱学指标</t>
+          <t>检出相/多型</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位；AFM厚度/粗糙度；SEM占比/尺寸</t>
+          <t>测到的物相/多型</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>2H-MoS₂</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>最小结构化结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>实测层数/覆盖率</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>实测层数与覆盖率</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>cm⁻¹·eV·nm…</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>层·%</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>Δ(A1g-E2g)≈20；PL~1.85eV</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>1 层；~70%</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>随技术选填</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="3" t="n"/>
+      <c r="J76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>靶材化学身份 + 批次</t>
-        </is>
-      </c>
+          <t>畴尺寸/成核密度/连续性</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>μm·cm⁻²·(连续/孤立)</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>畴 ~50 μm</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -4074,17 +4114,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位；AFM厚度/粗糙度；SEM占比/尺寸</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4099,17 +4139,17 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>cm⁻¹·eV·nm…</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Δ(A1g-E2g)≈20；PL~1.85eV</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4117,55 +4157,27 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>功率/偏压</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>DC/RF 功率、基底偏压</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>DC/RF</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>W·V</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>RF 150W；偏压 -50V</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>随技术选填</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -4175,27 +4187,27 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>等离子气氛/工作气压</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -4205,7 +4217,7 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4223,12 +4235,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>预溅射/挡板时序</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4243,7 +4255,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -4253,7 +4265,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4271,56 +4283,200 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
+          <t>功率/偏压</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>DC/RF 功率、基底偏压</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>DC/RF</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>W·V</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>RF 150W；偏压 -50V</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>等离子气氛/工作气压</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>溅射气体与气压</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>下拉+数值</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Ar / Ar+N₂…</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Ar，0.5 Pa</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>预溅射/挡板时序</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
           <t>沉积速率</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>速率（QCM 等）</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>nm/s</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="I85" s="4" t="inlineStr">
         <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr"/>
+      <c r="J85" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A51:J51"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A42:J42"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4333,7 +4489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4684,27 +4840,245 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>── 2026-07-06 v3.2 评审回炉（Fable 独立评审）──</t>
+        </is>
+      </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>§7</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>新增『观察到的现象』客观多选词表——录入端仍不判成败，但保留光镜可判的客观负结果（失败炉次最小结构化痕迹）</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>评审回炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>§1b</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>化学式升R0；新增『组成明细 components[]』结构化掺杂/异质结，替代字符串承载；结构类型保留为判别器</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>评审回炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>§5</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>补回降温段参数（方式/开盖温度/速率），条件必填(降温段)——review头部隐变量勿再漏</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>评审回炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>硬必填核心(15项)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>实验时间·合成方法·实验人·样品/实验编号·装置·温区数·炉体方向·前驱体名称·前驱体用量·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系(生长)</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>按合成方法条件化：前驱体用量→条件必填(固态源)，气态源/PVD不逼填mg</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>评审回炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>数据模型</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>记录最小单元拍板：炉次=记录单元、样品=关联主键、表征外键指向样品</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>评审回炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>── review→v3 回退存档（每条给去向）──</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>湿度</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>装置加热区长/泵型号/MFC配置/PID</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>炉管履历</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>时序四元组</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>硬必填核心(≈16项，含条件必填)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>实验时间·合成方法·实验人·样品编号·目标化学式·装置·温区数·炉体方向·前驱体名称·前驱体用量(固态源)·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系(生长)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>
@@ -4721,7 +5095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4754,12 +5128,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>记录最小单元：一炉一行 vs 以样品为主线挂生长/表征事件</t>
+          <t>一等实体字段表：MaterialLot / 装置 / 表征仪器（补进本xlsx新sheet）</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>待议(技术)</t>
+          <t>下一轮</t>
         </is>
       </c>
     </row>
@@ -4771,12 +5145,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>化学式 / 异质结 标准写法（找国标或组内定一套）</t>
+          <t>化学式 / 异质结 标准写法（渲染规则，找国标或组内定）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>待办(归入重写标准文档)</t>
+          <t>待办</t>
         </is>
       </c>
     </row>
@@ -4788,7 +5162,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>化学式录入方式：化学周期表点选 vs 文本输入</t>
+          <t>化学式录入：文本+元素校验/自动补全（建议，非周期表点选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4805,27 +5179,44 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>表征独立表的关联模型/批次选择</t>
+          <t>权威源从xlsx转仓库内YAML/CSV（可行级diff），xlsx反向生成给人看</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>待办(技术)</t>
+          <t>下一轮</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>已定稿：掺杂→结构类型 · §6命名 · 目标性能措辞</t>
+          <t>v1→v2 逐字段迁移映射（68字段去向，含quality_label/failure_modes/color_change落点）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>下一轮</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>已定/已改：记录单元=炉次+样品关联 · 掺杂→结构类型+components · §6命名 · 观察现象词表 · 降温参数 · R0条件化</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>见『v2→v3变更说明』</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -70,12 +70,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E4ECF7"/>
+        <fgColor rgb="00FCEFD6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCEFD6"/>
+        <fgColor rgb="00E4ECF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>元素体系与化学式（规范/显示串，可由组成明细自动生成）</t>
+          <t>规范显示串；复合体系须与组成明细一致、以组成明细为准（可自动生成）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>★v3.2升R0；结构化明细见『组成明细』</t>
+          <t>★R0；复合体系权威在『组成明细』</t>
         </is>
       </c>
     </row>
@@ -1086,14 +1086,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>垂直异质结</t>
+          <t>本征</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>判别器</t>
+          <t>判别器；决定组成明细是否必填</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>逐组分结构化：化学式·角色·数量，供机器检索</t>
+          <t>逐组分结构化（复合体系的权威数据源）</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>每条:化学式/角色(基体·掺杂剂·上层·下层·横向域)/数量(at%或层序)</t>
+          <t>每条:化学式/角色(基体·掺杂剂·上层·下层·横向域)/浓度(at%)/层序(整数)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1138,14 +1138,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>条件必填(结构类型≠本征)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>{MoS₂,基体};{Nb,掺杂剂,0.5at%}</t>
+          <t>{WS₂,上层,层序2};{MoS₂,下层,层序1}</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>★v3.2新增；替代把掺杂/异质结塞进化学式串（Fable评审）</t>
+          <t>★v3.2b升为权威源+条件必填；数量拆浓度/层序；杜绝退回字符串（复审N2）</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>定义项</t>
         </is>
@@ -2091,22 +2091,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>相态</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
+          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>固/气/液</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2114,24 +2114,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>MoO₃-B202（锁 v1）</t>
+          <t>固</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>防以后改批次信息影响旧记录</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
         </is>
       </c>
     </row>
@@ -2143,22 +2143,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>角色（role）</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>在反应里的角色</t>
+          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>主源/辅助剂/掺杂源/其他</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2166,24 +2166,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>主源</t>
+          <t>MoO₃-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>界面中文(英文)</t>
+          <t>防以后改批次信息影响旧记录</t>
         </is>
       </c>
     </row>
@@ -2195,47 +2195,47 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>角色（role）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>投料量（只记投料，不记残余）</t>
+          <t>在反应里的角色</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>主源/辅助剂/掺杂源/其他</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>mg</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(固态源)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>主源</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>★v3.2：气态源/PVD无mg，改条件必填</t>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>界面中文(英文)</t>
         </is>
       </c>
     </row>
@@ -2247,45 +2247,49 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>用量</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>投料前处理（可多步，选了再展开参数）</t>
+          <t>投料量（只记投料，不记残余）</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>直接加载/熔融凝固/压片/旋涂/退火/研磨/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>见展开</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>条件必填(固态源)</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>直接加载</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2：气态源/PVD无mg，改条件必填</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2295,27 +2299,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>舟/坩埚</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>盛装容器材质与尺寸</t>
+          <t>投料前处理（可多步，选了再展开参数）</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>石英舟/陶瓷(刚玉)舟/其他；长×宽×高（直径）</t>
+          <t>直接加载/熔融凝固/压片/旋涂/退火/研磨/其他</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>见展开</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -2325,19 +2329,15 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>石英舟 90×15</t>
+          <t>直接加载</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>v3暂保留长×宽×高</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>所在温区/源温</t>
+          <t>舟/坩埚</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>放第几温区、源温（若可设/可测）</t>
+          <t>盛装容器材质与尺寸</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>温区1…</t>
+          <t>石英舟/陶瓷(刚玉)舟/其他；长×宽×高（直径）</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -2377,17 +2377,17 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>温区1，设定~620</t>
+          <t>石英舟 90×15</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>按进气端编号</t>
+          <t>v3暂保留长×宽×高</t>
         </is>
       </c>
     </row>
@@ -2399,113 +2399,117 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>所在温区/源温</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>放第几温区、源温（若可设/可测）</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>下拉+数值</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>温区1…</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>温区1，设定~620</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>按进气端编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>前驱体</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>距热电偶距离</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>距所在温区热电偶的水平距离</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>上游为负、下游为正</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>§4 衬底（长在什么基底上，可多片）</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>衬底材料</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>衬底种类</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>SiO₂/Si</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2515,22 +2519,22 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>化学式/取向</t>
+          <t>衬底材料</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>化学式与晶面取向/偏转角</t>
+          <t>衬底种类</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>标准写法（如 x面向x轴偏X°）</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2538,14 +2542,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Si(100)</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2553,11 +2557,7 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>单晶记取向+偏转角</t>
-        </is>
-      </c>
+      <c r="J44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2567,37 +2567,37 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>氧化层厚度</t>
+          <t>化学式/取向</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）</t>
+          <t>化学式与晶面取向/偏转角</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>写成 SiO₂/Si(285nm)</t>
+          <t>标准写法（如 x面向x轴偏X°）</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>Si(100)</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2605,7 +2605,11 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>单晶记取向+偏转角</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2615,12 +2619,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>表面粗糙度</t>
+          <t>氧化层厚度</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Ra / RMS</t>
+          <t>SiO₂ 层厚度（决定光学判层数）</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2630,7 +2634,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>写成 SiO₂/Si(285nm)</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2638,26 +2642,22 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>&lt;1</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>常比化学式更决定成核；可问厂家或AFM</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2667,27 +2667,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>尺寸/朝向</t>
+          <t>表面粗糙度</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>几何尺寸与放置朝向</t>
+          <t>Ra / RMS</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>数值+下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>长×宽×厚；正放/倒扣/倾角/竖放</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2697,15 +2697,19 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>10×10×0.5；正放</t>
+          <t>&lt;1</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>会议/建议</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>常比化学式更决定成核；可问厂家或AFM</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2715,42 +2719,42 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>尺寸/朝向</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>几何尺寸与放置朝向</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值+下拉</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>清洗/退火/等离子/亲水化/其他</t>
+          <t>长×宽×厚；正放/倒扣/倾角/竖放</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>见展开</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>丙酮→异丙醇→N₂吹干</t>
+          <t>10×10×0.5；正放</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>会议/建议</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
@@ -2763,49 +2767,45 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>处理到装炉间隔/暴露环境</t>
+          <t>预处理（有序步骤）</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>清洗后到装炉的时间与环境</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>清洗/退火/等离子/亲水化/其他</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>见展开</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>30 min，空气</t>
+          <t>丙酮→异丙醇→N₂吹干</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>表面老化</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -2815,113 +2815,113 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>处理到装炉间隔/暴露环境</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>清洗后到装炉的时间与环境</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>30 min，空气</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>表面老化</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>所在温区/距热电偶距离</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>第几温区、距离(±)</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>下拉+数值</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>温区2…</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>温区2，+15</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>§5 反应条件（按时间顺序的各阶段；每阶段填同一套：气体/温度/压力/时长；阶段类型驱动动态表单）</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>阶段类型</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>这一步在做什么（选后只显示对应参数）</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>抽气/漏检/吹扫/预处理/升温/温度稳定/反应生长/后退火/降温/放气/卸样</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>反应生长</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>多步可加；跨组比较看类型</t>
-        </is>
-      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -2931,69 +2931,69 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>步序/起止时刻</t>
+          <t>阶段类型</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>第几步、起止时间</t>
+          <t>这一步在做什么（选后只显示对应参数）</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>数值+时间</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>抽气/漏检/吹扫/预处理/升温/温度稳定/反应生长/后退火/降温/放气/卸样</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>#3，10:20–10:35</t>
+          <t>反应生长</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>支持重叠/循环</t>
+          <t>多步可加；跨组比较看类型</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>步序/起止时刻</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>各温区升温曲线（目标温/速率/保温）</t>
+          <t>第几步、起止时间</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>数组</t>
+          <t>数值+时间</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -3003,27 +3003,27 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>℃·℃/min·min</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>温区2：25→750@20℃/min，保温15</t>
+          <t>#3，10:20–10:35</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>设定值；分温区</t>
+          <t>支持重叠/循环</t>
         </is>
       </c>
     </row>
@@ -3035,17 +3035,17 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>实测温度</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>控温热电偶实测曲线（导入）。注意：不是衬底真温</t>
+          <t>各温区升温曲线（目标温/速率/保温）</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>数组(时序)</t>
+          <t>数组</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>℃·℃/min·min</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>[导入 furnace.csv]</t>
+          <t>温区2：25→750@20℃/min，保温15</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>★v3：删『估算衬底真温』，只留设定+实测</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>设定值；分温区</t>
         </is>
       </c>
     </row>
@@ -3087,37 +3087,37 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>测温设备/不确定度</t>
+          <t>实测温度</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>测温点用什么设备、不确定度多少</t>
+          <t>控温热电偶实测曲线（导入）。注意：不是衬底真温</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>引用+数值</t>
+          <t>数组(时序)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>热电偶/高温计；来源：仪器/校准/重复性/估计</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>K型热电偶，±1℃</t>
+          <t>[导入 furnace.csv]</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3125,111 +3125,115 @@
           <t>会议/复审</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>测量不确定度</t>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>★v3：删『估算衬底真温』，只留设定+实测</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>降温方式/开盖温度/速率</t>
+          <t>测温设备/不确定度</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>降温段参数（阶段类型=降温 时）</t>
+          <t>测温点用什么设备、不确定度多少</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>引用+数值</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>随炉冷却/开盖冷却/移炉快速冷却；开盖温度；降温速率</t>
+          <t>热电偶/高温计；来源：仪器/校准/重复性/估计</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(降温段)</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>随炉冷却；开盖~580</t>
+          <t>K型热电偶，±1℃</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>★v3.2补回：review文档头部隐变量，勿再漏（Fable评审）</t>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>测量不确定度</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>气体组分</t>
+          <t>降温方式/开盖温度/速率</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>每种气体单独一条（混合气拆开）</t>
+          <t>降温段参数（阶段类型=降温 时）</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>下拉(多条)</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Ar/N₂/H₂/O₂/CH₄/其他</t>
+          <t>随炉冷却/开盖冷却/移炉快速冷却；开盖温度；降温速率</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>条件必填(降温段)</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t>随炉冷却；开盖~580</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>★v3.2补回：review文档头部隐变量，勿再漏（Fable评审）</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -3239,42 +3243,42 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>纯度/浓度/水氧</t>
+          <t>气体组分</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>纯度、体积比、水氧杂质</t>
+          <t>每种气体单独一条（混合气拆开）</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉(多条)</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar/N₂/H₂/O₂/CH₄/其他</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>N·%·ppm</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Ar 5N；水氧&lt;1ppm</t>
+          <t>Ar</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr"/>
@@ -3287,37 +3291,37 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>流量/来源</t>
+          <t>纯度/浓度/水氧</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>流量、流量计类型</t>
+          <t>纯度、体积比、水氧杂质</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>数值+下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>MFC/转子</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>sccm</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>N·%·ppm</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>80（MFC）</t>
+          <t>Ar 5N；水氧&lt;1ppm</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3325,61 +3329,57 @@
           <t>会议/复审</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>sccm须绑标准状态；设定+实测</t>
-        </is>
-      </c>
+      <c r="J60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>压力体系/工作压力</t>
+          <t>流量/来源</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>常压/低压/超高真空 + 工作压力</t>
+          <t>流量、流量计类型</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值+下拉</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>MFC/转子</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>sccm</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>必填(生长)/选填(其余)</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>常压；1.0×10⁵ Pa</t>
+          <t>80（MFC）</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>所有阶段可出现</t>
+          <t>sccm须绑标准状态；设定+实测</t>
         </is>
       </c>
     </row>
@@ -3391,60 +3391,64 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>本底压力/漏率</t>
+          <t>压力体系/工作压力</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>反应前底压、漏率</t>
+          <t>常压/低压/超高真空 + 工作压力</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Pa·Pa·L/s</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>必填(生长)/选填(其余)</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>常压；1.0×10⁵ Pa</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>所有阶段可出现</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>时长/循环次数</t>
+          <t>本底压力/漏率</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>本阶段时长、吹扫抽-充次数</t>
+          <t>反应前底压、漏率</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3459,22 +3463,22 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>min·次</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="inlineStr">
-        <is>
-          <t>必填/选填</t>
+          <t>Pa·Pa·L/s</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr"/>
@@ -3482,122 +3486,118 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>时长/循环次数</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>本阶段时长、吹扫抽-充次数</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>min·次</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>必填/选填</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
           <t>步·外场</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>外场参数</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>等离子功率/光源（有外场才填，可自填添加）</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>电场强度；光场:中心波长/线宽/功率密度/光斑大小</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>V·nm·W…</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>setup无外场则不显示</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>§6 过程事件 Process Events（含异常/中断/人工干预等客观事件；只记客观事实、不判成败）</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n"/>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="n"/>
-      <c r="J65" s="3" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>事件/部位</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>过程中发生的客观事件 + 关联部位（合并）</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>供电/供水/供气中断·管路堵塞·压力突变·信号异常·人工干预·其他（可加）</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>气流中断（Ar气路）</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>★v3：事件类型与关联对象合并为一个下拉</t>
-        </is>
-      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
+      <c r="J66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -3607,22 +3607,22 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>发生时刻</t>
+          <t>事件/部位</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>何时发生（记绝对时间）</t>
+          <t>过程中发生的客观事件 + 关联部位（合并）</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>供电/供水/供气中断·管路堵塞·压力突变·信号异常·人工干预·其他（可加）</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3637,17 +3637,17 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>气流中断（Ar气路）</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>相对时间可由t0算</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>★v3：事件类型与关联对象合并为一个下拉</t>
         </is>
       </c>
     </row>
@@ -3659,22 +3659,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>中止原因</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>若中止（只记客观原因，不写成败）</t>
+          <t>何时发生（记绝对时间）</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划结束</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3689,15 +3689,19 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>计划结束</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>相对时间可由t0算</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -3707,113 +3711,109 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
+          <t>中止原因</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>若中止（只记客观原因，不写成败）</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>设备报警/人工停止/计划结束</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>计划结束</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
           <t>描述/措施/附件</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>现象、处理、相关文件</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>自由+附件</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>Ar瓶压不足，已更换</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
-      <c r="J70" s="3" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>表征类型/仪器</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>表征手段 + 引用仪器</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
-        </is>
-      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
+      <c r="J71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -3823,27 +3823,27 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>表征类型/仪器</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>表征手段 + 引用仪器</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>视仪器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>532nm / 1mW / 100×</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3861,9 +3861,9 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
         </is>
       </c>
     </row>
@@ -3875,17 +3875,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>视仪器</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
@@ -3905,40 +3905,44 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>532nm / 1mW / 100×</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3946,26 +3950,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>★v3.2新增；替代被废失败模式词表的客观部分，失败炉次最小痕迹（Fable评审）</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3975,22 +3975,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>检出相/多型</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>测到的物相/多型</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>2H-MoS₂</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -4013,9 +4013,9 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>最小结构化结果</t>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
         </is>
       </c>
     </row>
@@ -4027,17 +4027,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>实测层数/覆盖率</t>
+          <t>检出相/多型</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>实测层数与覆盖率</t>
+          <t>测到的物相/多型</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>层·%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>1 层；~70%</t>
+          <t>2H-MoS₂</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -4065,7 +4065,11 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>最小结构化结果</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -4075,10 +4079,14 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>畴尺寸/成核密度/连续性</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr"/>
+          <t>实测层数/覆盖率</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>实测层数与覆盖率</t>
+        </is>
+      </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
           <t>数值</t>
@@ -4091,7 +4099,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>μm·cm⁻²·(连续/孤立)</t>
+          <t>层·%</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -4101,7 +4109,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>畴 ~50 μm</t>
+          <t>1 层；~70%</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -4119,113 +4127,109 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
+          <t>畴尺寸/成核密度/连续性</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>μm·cm⁻²·(连续/孤立)</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>畴 ~50 μm</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
           <t>关键谱学指标</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Raman峰位/峰宽/峰面积；PL峰位；AFM厚度/粗糙度；SEM占比/尺寸</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>cm⁻¹·eV·nm…</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>Δ(A1g-E2g)≈20；PL~1.85eV</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
         <is>
           <t>随技术选填</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="3" t="n"/>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>靶材（批次）</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>靶材化学身份 + 批次</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>批次库</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>MoS₂ 靶-T01</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr"/>
+      <c r="B80" s="3" t="n"/>
+      <c r="C80" s="3" t="n"/>
+      <c r="D80" s="3" t="n"/>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -4235,37 +4239,37 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4283,12 +4287,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>功率/偏压</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4298,22 +4302,22 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>W·V</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4331,37 +4335,37 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>等离子气氛/工作气压</t>
+          <t>功率/偏压</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr">
+          <t>W·V</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4379,37 +4383,37 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>预溅射/挡板时序</t>
+          <t>等离子气氛/工作气压</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>min·s</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4427,56 +4431,104 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
+          <t>预溅射/挡板时序</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
           <t>沉积速率</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>速率（QCM 等）</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>nm/s</t>
         </is>
       </c>
-      <c r="G85" s="10" t="inlineStr">
+      <c r="G86" s="9" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J85" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A80:J80"/>
     <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A51:J51"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A71:J71"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4489,7 +4541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4962,7 +5014,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>── review→v3 回退存档（每条给去向）──</t>
+          <t>── v3.2b 二轮复审再修（Fable 第二轮）──</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -4971,114 +5023,212 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>存档</t>
+          <t>v3.2b</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>湿度</t>
+          <t>§3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
+          <t>新增前驱体『相态(固/气/液)』字段，为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>回退备案</t>
+          <t>复审再修</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>存档</t>
+          <t>v3.2b</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>装置加热区长/泵型号/MFC配置/PID</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+          <t>组成明细升为权威+条件必填(结构类型≠本征)、化学式复合体系以其为准；数量拆『浓度(at%)』『层序』；结构类型改必填（复审N2/③）</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>回退备案</t>
+          <t>复审再修</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>存档</t>
+          <t>v3.2b</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>炉管履历</t>
+          <t>§7/§10</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+          <t>加生命周期规则：炉次终态而无任何现象/表征行→『结果缺失』待办，堵『失败炉次零痕迹』（复审①）</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>回退备案</t>
+          <t>复审再修</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>存档</t>
+          <t>v3.2b</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>时序四元组</t>
+          <t>§8/§10</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+          <t>PVD 暂不纳入 v2.0 合规判定（占位），R0 不校验 PVD 炉次，待 profile 落地（复审N3）</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>回退备案</t>
+          <t>复审再修</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr"/>
-      <c r="B28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>── review→v3 回退存档（每条给去向）──</t>
+        </is>
+      </c>
       <c r="C28" s="4" t="inlineStr"/>
       <c r="D28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>湿度</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>装置加热区长/泵型号/MFC配置/PID</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>炉管履历</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>时序四元组</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>硬必填核心(≈16项，含条件必填)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>实验时间·合成方法·实验人·样品编号·目标化学式·装置·温区数·炉体方向·前驱体名称·前驱体用量(固态源)·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系(生长)</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="字段草案" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="v2→v3变更说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待明确清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="一等实体字段表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v2→v3变更说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待明确清单" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4541,7 +4542,2303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>实体</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>含义/为什么记</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>填写方式</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>可选项/格式</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>必填(登记)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>填写示例</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>※ 本表定义『实验只引用、不重复录入』的一等实体；『必填(登记)』指登记该实体时必填，与实验记录的 R0 不同。实验引用时对当时版本快照冻结。</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>实体① 物料批次库 MaterialLot（前驱体/衬底/气瓶通用 + 子类；实验中只填批号引用，纯度/粒径自动带出并锁版）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>批次类别</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>决定启用哪组子类字段</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>化学品/衬底/气瓶</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>化学品</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>驱动子类条件字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>物质名称</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>化学身份：名称</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>三氧化钼</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>review§4.1A</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>化学式</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>化学身份：分子式</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>MoO₃</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CAS号</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>唯一化学标识</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>CAS</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>1313-27-5</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>InChIKey/PubChem CID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>可选唯一标识</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>商业批次：厂商</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>下拉+其他(可扩展)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>受控+其他</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>阿拉丁</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>商业批次：产品号</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>M112056</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>批号</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>商业批次：生产批号（同名不同批的区分键）</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>B202405</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>GMP法定术语『批号』</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>纯度</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>质量分数或N值</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>%或N值</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>99.95（4N5）</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>粒径(x50/D50)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>中位径（影响挥发/成核）</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>x50严谨；目数可接受</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>形态/性状</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>试剂外观</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>粉末/颗粒/块/箔/靶/其他</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>粉末</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>外观=性状</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>开封日期</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>影响吸潮/氧化</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>存储方式</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>存放条件</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>干燥器</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>desiccator=干燥器</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>证书附件(CoA)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>质检证书</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>附件</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>coa.pdf</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>▸衬底·材料</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>子类(批次类别=衬底)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>SiO₂/Si·蓝宝石·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>SiO₂/Si</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>与§4衬底材料词表一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>▸衬底·氧化层厚度</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>仅SiO₂/Si</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>条件必填(SiO₂/Si)</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>▸衬底·晶向/抛光</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>取向与抛光面</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>文本+下拉</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>晶向；单面抛/双面抛</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Si(100)；单面抛</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>▸衬底·尺寸规格</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>出厂几何</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>长×宽×厚</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>10×10×0.5</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>▸气瓶·纯度等级</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>子类(批次类别=气瓶)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>6N/5N/4N/工业级/其他</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>条件必填(气瓶)</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>5N</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>本底纯度</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>▸气瓶·气瓶编号</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>钢瓶追溯号</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>GC-Ar-07</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>装置编号</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>唯一编号</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>CVD-炉1</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>review§4.1B</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>装置名称</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>人读名</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1号双温区管式炉</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>品牌/型号</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>设备品牌型号</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>受控+其他</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>合肥科晶 OTF-1200X</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>壁型</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>热壁/冷壁</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>热壁/冷壁</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>热壁</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>温区数</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>独立控温区数</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>炉体方向</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>水平/垂直</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>水平/垂直</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>水平</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>管材质/形状</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>炉管材料与截面</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>石英/刚玉；圆/方/矩</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>石英·圆形</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>管外径/壁厚(→内径)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>管规格</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>下拉+数值</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>1″/2″/4″/自定义 + 壁厚</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>1″，壁厚2</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>加热区长度</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>恒温区长度（影响停留/温场）</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>★review§4.1B补</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>v3曾漏，Fable点名</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>坐标系定义</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>原点固定、上游负/下游正（随引用冻结）</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>固定定义</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>原点+轴向</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>原点=温区2热电偶；下游为正</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>全局定死，防选反</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>泵型号/极限压力</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>真空能力</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>文本+数值</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>机械泵，10 Pa</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>★review§4.1B补</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>MFC配置</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>各通道气体/量程/校准日期</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>数组</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>通道/气体/量程(sccm)/校准日期</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>CH1 Ar 0–200sccm</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>★review§4.1B补</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>仪器PID</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>持久标识（预留）</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>PIDINST/PID</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>外场装置</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>是否配光/电/等离子源</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>多选+描述</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>无/光/电/等离子</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>定量参数在实验§5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>装置示意图/描述</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>照片/示意图+文字</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>附件+自由</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>setup.png</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>仪器编号</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>唯一编号</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>RAMAN-1</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>仪器名称/类型</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>手段类型</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Raman</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>厂商(vendor)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Horiba</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>型号(model)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>LabRAM HR</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>序列号(serial)</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>设备序列号</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>PID(持久标识)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>仪器持久标识（预留）</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>所在实验室/位置</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>物理位置</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>A305</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>如激光波长/物镜/探测器</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>视仪器</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>532nm激光</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>最近校准/维护</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>校准/维护日期</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5112,7 +7409,7 @@
       <c r="A28" s="4" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>── review→v3 回退存档（每条给去向）──</t>
+          <t>── v3.3 一等实体补齐（复审⑤/must-fix4-5）──</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -5121,68 +7418,56 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>存档</t>
+          <t>v3.3</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>湿度</t>
+          <t>实体表</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
+          <t>新增『一等实体字段表』sheet：MaterialLot/装置Setup/表征仪器三张权威字段表（补齐半个数据模型）；§10 合规纳入（PVD 仍排除）</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>回退备案</t>
+          <t>实体补齐</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>存档</t>
+          <t>v3.3</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>装置加热区长/泵型号/MFC配置/PID</t>
+          <t>§5/§8.1</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+          <t>AP/LP 冗余二选一敲定：保留合成方法 AP/LP，以校验规则强制与压力体系一致（不再悬置）</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>回退备案</t>
+          <t>实体补齐</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>存档</t>
-        </is>
-      </c>
+      <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>炉管履历</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>回退备案</t>
-        </is>
-      </c>
+          <t>── review→v3 回退存档（每条给去向）──</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -5192,12 +7477,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>时序四元组</t>
+          <t>湿度</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -5207,28 +7492,94 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>装置加热区长/泵型号/MFC配置/PID</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>炉管履历</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>时序四元组</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>硬必填核心(≈16项，含条件必填)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>实验时间·合成方法·实验人·样品编号·目标化学式·装置·温区数·炉体方向·前驱体名称·前驱体用量(固态源)·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系(生长)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>
@@ -5239,13 +7590,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5278,12 +7629,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>一等实体字段表：MaterialLot / 装置 / 表征仪器（补进本xlsx新sheet）</t>
+          <t>化学式 / 异质结 标准写法（渲染规则，找国标或组内定）</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>下一轮</t>
+          <t>待办</t>
         </is>
       </c>
     </row>
@@ -5295,12 +7646,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>化学式 / 异质结 标准写法（渲染规则，找国标或组内定）</t>
+          <t>化学式录入：文本+元素校验/自动补全（建议，非周期表点选）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>待办</t>
+          <t>待办(技术)</t>
         </is>
       </c>
     </row>
@@ -5312,12 +7663,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>化学式录入：文本+元素校验/自动补全（建议，非周期表点选）</t>
+          <t>权威源从xlsx转仓库内YAML/CSV（可行级diff）；词表归一到单一源</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>待办(技术)</t>
+          <t>下一轮</t>
         </is>
       </c>
     </row>
@@ -5329,7 +7680,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>权威源从xlsx转仓库内YAML/CSV（可行级diff），xlsx反向生成给人看</t>
+          <t>v1→v2 逐字段迁移映射（68字段去向，含quality_label/failure_modes/color_change落点）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5341,32 +7692,15 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>v1→v2 逐字段迁移映射（68字段去向，含quality_label/failure_modes/color_change落点）</t>
+          <t>已定/已改：一等实体字段表 · 记录单元=炉次+样品 · 掺杂→结构类型+components · 观察现象词表 · 降温参数 · R0条件化(相态判别) · AP/LP校验</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>下一轮</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>已定/已改：记录单元=炉次+样品关联 · 掺杂→结构类型+components · §6命名 · 观察现象词表 · 降温参数 · R0条件化</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>见『v2→v3变更说明』</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -1415,7 +1415,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>§2 实验设备与设计（用到的炉子/装置——一台炉录一次，以后直接引用）</t>
+          <t>§2 实验设备与设计（用到的炉子/装置——一台炉录一次，以后直接引用；壁型/温区数/炉体方向/管径/坐标系等由所引用装置快照【只读投影】带出，不重录）</t>
         </is>
       </c>
       <c r="B20" s="3" t="n"/>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>mg</t>
+          <t>mg(固)/µL(液)</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>条件必填(固态源)</t>
+          <t>条件必填(非气态)</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>★v3.2：气态源/PVD无mg，改条件必填</t>
+          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4701,17 +4701,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>物质名称</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>化学身份：名称</t>
+          <t>每次修改+1；实验引用时冻结此版本</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4731,15 +4731,19 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>三氧化钼</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>review§4.1A</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>改则新版本，旧引用不受影响</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4749,12 +4753,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>化学式</t>
+          <t>物质名称</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>化学身份：分子式</t>
+          <t>化学身份：名称</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4779,12 +4783,12 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>MoO₃</t>
+          <t>三氧化钼</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>review§4.1A</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
@@ -4797,12 +4801,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CAS号</t>
+          <t>化学式</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>唯一化学标识</t>
+          <t>化学身份：分子式</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4812,7 +4816,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -4820,14 +4824,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>1313-27-5</t>
+          <t>MoO₃</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -4845,12 +4849,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>InChIKey/PubChem CID</t>
+          <t>CAS号</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>可选唯一标识</t>
+          <t>唯一化学标识</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -4860,7 +4864,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -4868,14 +4872,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1313-27-5</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -4893,22 +4897,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>InChIKey/PubChem CID</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>商业批次：厂商</t>
+          <t>可选唯一标识</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他(可扩展)</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -4916,14 +4920,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>阿拉丁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -4941,22 +4945,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>货号</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>商业批次：产品号</t>
+          <t>商业批次：厂商</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他(可扩展)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -4964,14 +4968,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>M112056</t>
+          <t>阿拉丁</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -4989,12 +4993,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>批号</t>
+          <t>货号</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>商业批次：生产批号（同名不同批的区分键）</t>
+          <t>商业批次：产品号</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -5012,14 +5016,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>B202405</t>
+          <t>M112056</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -5027,11 +5031,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>GMP法定术语『批号』</t>
-        </is>
-      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -5041,37 +5041,37 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>纯度</t>
+          <t>批号</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>质量分数或N值</t>
+          <t>商业批次：生产批号（同名不同批的区分键）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>%或N值</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>99.95（4N5）</t>
+          <t>B202405</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -5079,7 +5079,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>GMP法定术语『批号』</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -5089,12 +5093,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>粒径(x50/D50)</t>
+          <t>纯度</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>中位径（影响挥发/成核）</t>
+          <t>质量分数或N值</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -5104,22 +5108,22 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>x50严谨；目数可接受</t>
+          <t>%或N值</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>µm</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>99.95（4N5）</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -5137,27 +5141,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>形态/性状</t>
+          <t>粒径(x50/D50)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>试剂外观</t>
+          <t>中位径（影响挥发/成核）</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>粉末/颗粒/块/箔/靶/其他</t>
+          <t>x50严谨；目数可接受</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>µm</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -5167,7 +5171,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>粉末</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -5175,11 +5179,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>外观=性状</t>
-        </is>
-      </c>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -5189,22 +5189,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>开封日期</t>
+          <t>形态/性状</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>影响吸潮/氧化</t>
+          <t>试剂外观</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>粉末/颗粒/块/箔/靶/其他</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>粉末</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -5227,7 +5227,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>外观=性状</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -5237,22 +5241,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>存储方式</t>
+          <t>开封日期</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>存放条件</t>
+          <t>影响吸潮/氧化</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -5267,7 +5271,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>干燥器</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -5275,11 +5279,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>desiccator=干燥器</t>
-        </is>
-      </c>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -5289,22 +5289,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>证书附件(CoA)</t>
+          <t>存储方式</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>质检证书</t>
+          <t>存放条件</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>coa.pdf</t>
+          <t>干燥器</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -5327,7 +5327,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>desiccator=干燥器</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -5337,22 +5341,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>▸衬底·材料</t>
+          <t>证书附件(CoA)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>子类(批次类别=衬底)</t>
+          <t>质检证书</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -5362,12 +5366,12 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>条件必填(衬底)</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>coa.pdf</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -5375,11 +5379,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>与§4衬底材料词表一致</t>
-        </is>
-      </c>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -5389,37 +5389,37 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>▸衬底·氧化层厚度</t>
+          <t>▸衬底·材料</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>仅SiO₂/Si</t>
+          <t>子类(批次类别=衬底)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SiO₂/Si·蓝宝石·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>条件必填(SiO₂/Si)</t>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -5427,7 +5427,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>与§4衬底材料词表一致</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5437,37 +5441,37 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>▸衬底·晶向/抛光</t>
+          <t>▸衬底·氧化层厚度</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>仅SiO₂/Si</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>条件必填(SiO₂/Si)</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -5485,37 +5489,37 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>▸衬底·尺寸规格</t>
+          <t>▸衬底·晶向/抛光</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>出厂几何</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -5533,37 +5537,37 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸衬底·尺寸规格</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)</t>
+          <t>出厂几何</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级/其他</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>条件必填(气瓶)</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -5571,11 +5575,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>本底纯度</t>
-        </is>
-      </c>
+      <c r="J22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -5585,109 +5585,113 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>▸气瓶·纯度等级</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>6N/5N/4N/工业级/其他</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>条件必填(气瓶)</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>5N</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>分工：base纯度填数值%、此处填等级标签(Fable三轮B4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>钢瓶追溯号</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>GC-Ar-07</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>装置编号</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>唯一编号</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>CVD-炉1</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>review§4.1B</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -5697,12 +5701,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>装置编号</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -5727,12 +5731,12 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>review§4.1B</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
@@ -5745,22 +5749,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>品牌/型号</t>
+          <t>装置名称</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>设备品牌型号</t>
+          <t>人读名</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -5768,14 +5772,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -5793,22 +5797,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -5816,22 +5820,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>对标 v1 setup_version_snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -5841,37 +5849,37 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>品牌/型号</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>设备品牌型号</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>合肥科晶 OTF-1200X</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -5889,12 +5897,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -5904,7 +5912,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -5912,19 +5920,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr"/>
@@ -5937,37 +5945,37 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>管材质/形状</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>石英/刚玉；圆/方/矩</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>石英·圆形</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -5985,37 +5993,37 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>管外径/壁厚(→内径)</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>管规格</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1″/2″/4″/自定义 + 壁厚</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>1″，壁厚2</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -6033,27 +6041,27 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>加热区长度</t>
+          <t>管材质/形状</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>恒温区长度（影响停留/温场）</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>石英/刚玉；圆/方/矩</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -6063,19 +6071,15 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>石英·圆形</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>★review§4.1B补</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>v3曾漏，Fable点名</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -6085,49 +6089,45 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>管外径/壁厚(→内径)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>原点固定、上游负/下游正（随引用冻结）</t>
+          <t>管规格</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>原点+轴向</t>
+          <t>1″/2″/4″/自定义 + 壁厚</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>原点=温区2热电偶；下游为正</t>
+          <t>1″，壁厚2</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>全局定死，防选反</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -6137,17 +6137,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>泵型号/极限压力</t>
+          <t>加热区长度</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>真空能力</t>
+          <t>恒温区长度（影响停留/温场）</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>文本+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>机械泵，10 Pa</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -6175,7 +6175,11 @@
           <t>★review§4.1B补</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>v3曾漏，Fable点名</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -6185,22 +6189,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>MFC配置</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>各通道气体/量程/校准日期</t>
+          <t>原点固定、上游负/下游正（随引用冻结）</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>数组</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>通道/气体/量程(sccm)/校准日期</t>
+          <t>原点+轴向</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -6208,22 +6212,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>CH1 Ar 0–200sccm</t>
+          <t>原点=温区2热电偶；下游为正</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>★review§4.1B补</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>全局定死，防选反</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -6233,27 +6241,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>仪器PID</t>
+          <t>泵型号/极限压力</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>持久标识（预留）</t>
+          <t>真空能力</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本+数值</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>PIDINST/PID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -6263,12 +6271,12 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>机械泵，10 Pa</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>★review§4.1B补</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
@@ -6281,22 +6289,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>外场装置</t>
+          <t>MFC配置</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>是否配光/电/等离子源</t>
+          <t>各通道气体/量程/校准日期</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>多选+描述</t>
+          <t>数组</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>无/光/电/等离子</t>
+          <t>通道/气体/量程(sccm)/校准日期</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -6311,19 +6319,15 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>CH1 Ar 0–200sccm</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>定量参数在实验§5</t>
-        </is>
-      </c>
+          <t>★review§4.1B补</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -6333,22 +6337,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>装置示意图/描述</t>
+          <t>仪器PID</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>照片/示意图+文字</t>
+          <t>持久标识（预留）</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>附件+自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PIDINST/PID</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -6356,58 +6360,94 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr"/>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>外场装置</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>是否配光/电/等离子源</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>多选+描述</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>无/光/电/等离子</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>定量参数在实验§5</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>装置示意图/描述</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>照片/示意图+文字</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>附件+自由</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -6420,70 +6460,38 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr"/>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>仪器名称/类型</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>手段类型</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -6493,12 +6501,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>厂商(vendor)</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -6516,19 +6524,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr"/>
@@ -6541,22 +6549,22 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>型号(model)</t>
+          <t>仪器名称/类型</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>手段类型</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -6564,19 +6572,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr"/>
@@ -6589,12 +6597,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>序列号(serial)</t>
+          <t>厂商(vendor)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -6612,14 +6620,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -6637,12 +6645,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>PID(持久标识)</t>
+          <t>型号(model)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>仪器持久标识（预留）</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -6660,19 +6668,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr"/>
@@ -6685,12 +6693,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>所在实验室/位置</t>
+          <t>序列号(serial)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -6715,12 +6723,12 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr"/>
@@ -6733,27 +6741,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>PID(持久标识)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
+          <t>仪器持久标识（预留）</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>如激光波长/物镜/探测器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>视仪器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -6763,12 +6771,12 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>532nm激光</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication/PIDINST</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
@@ -6781,50 +6789,146 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
+          <t>所在实验室/位置</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>物理位置</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>A305</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>如激光波长/物镜/探测器</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>视仪器</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>532nm激光</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>最近校准/维护</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>校准/维护日期</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A42:J42"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
@@ -6838,7 +6942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7460,36 +7564,36 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>v3.3b</t>
+        </is>
+      </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
+          <t>冻结前收尾</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Fable三轮B1-B4：MaterialLot/Setup 加『版本号』(锁版使能)；§2属性=Setup快照【只读投影】声明；用量含液态(非气态条件、µL)；气瓶纯度与base分工注</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>冻结前收尾</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>── review→v3 回退存档（每条给去向）──</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>存档</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>湿度</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>回退备案</t>
-        </is>
-      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -7499,12 +7603,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>装置加热区长/泵型号/MFC配置/PID</t>
+          <t>湿度</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -7521,12 +7625,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>炉管履历</t>
+          <t>装置加热区长/泵型号/MFC配置/PID</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -7543,43 +7647,65 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>炉管履历</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>时序四元组</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>回退备案</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="4" t="inlineStr"/>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-    </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>硬必填核心(≈16项，含条件必填)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>实验时间·合成方法·实验人·样品编号·目标化学式·装置·温区数·炉体方向·前驱体名称·前驱体用量(固态源)·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系(生长)</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,9 +186,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5559,7 +5556,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>条件必填(衬底)</t>
         </is>
@@ -5611,7 +5608,7 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>条件必填(SiO₂/Si)</t>
         </is>
@@ -5755,7 +5752,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>条件必填(气瓶)</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -36,14 +36,25 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
     </font>
     <font>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <color rgb="00806000"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00B26B00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
     </font>
     <font>
       <b val="1"/>
@@ -56,17 +67,6 @@
     <font>
       <color rgb="00666666"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="00C00000"/>
-    </font>
-    <font>
-      <color rgb="00806000"/>
     </font>
   </fonts>
   <fills count="9">
@@ -83,7 +83,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,22 +103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7DA"/>
+        <fgColor rgb="00E4ECF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4ECF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,49 +143,49 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>样品/实验编号</t>
+          <t>炉次编号</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>CVD-20260620-03</t>
+          <t>CVD-2026-0003</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>组成明细(components)</t>
+          <t>组成明细</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>视性能</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>见展开</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>见展开</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>视仪器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G75" s="15" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>视仪器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -793,17 +793,17 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>操作者</t>
+          <t>创建炉次的当前登录用户</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>课题组成员</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -823,10 +823,14 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr"/>
+          <t>会议·产品决策2026-07-22</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>由系统根据当前登录账号自动填入，不可修改</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -1104,7 +1108,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>化学体系/化学式</t>
+          <t>目标材料化学式</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1134,7 +1138,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>MoS₂</t>
+          <t>MoS2</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>★R0；复合体系权威在『组成明细』</t>
+          <t>★R0；复合体系权威在『组成明细』；录入使用普通数字</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>每条:化学式/角色(基体·掺杂剂·上层·下层·横向域)/浓度(at%)/层序(整数)</t>
+          <t>每条:化学式/角色(基体·掺杂剂·合金组分·上层·下层·横向域)/浓度(at%)/层序(整数)</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1238,7 +1242,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>{WS₂,上层,层序2};{MoS₂,下层,层序1}</t>
+          <t>{WS2,上层,层序2};{MoS2,下层,层序1}</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -1317,17 +1321,17 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>晶体对称性：用体相空间群号 + 说明单层结构</t>
+          <t>晶体对称性：International Tables 空间群号（1–230）</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>下拉+文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>空间群号(1–230)+单层结构说明；未指定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1342,7 +1346,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>194(P6₃/mmc)，单层2H</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -3403,7 +3407,7 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Ar/N₂/H₂/O₂/CH₄/其他</t>
+          <t>Ar/N2/H2/O2/CH4/其他</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -566,6 +566,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -619,6 +620,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>机器约束</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -654,11 +660,12 @@
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>表单UI另用红星*标必填（待实现，见待明确清单）</t>
+          <t>表单 UI 使用红星 * 标记必填项</t>
         </is>
       </c>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -675,6 +682,7 @@
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -714,7 +722,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>2026-06-20 09:30</t>
+          <t>2026-06-20T09:30:00+08:00</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -727,6 +735,7 @@
           <t>时刻不能只到天</t>
         </is>
       </c>
+      <c r="K4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -779,6 +788,7 @@
           <t>★v3新增；可挂CHMO本体ID</t>
         </is>
       </c>
+      <c r="K5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -831,6 +841,7 @@
           <t>由系统根据当前登录账号自动填入，不可修改</t>
         </is>
       </c>
+      <c r="K6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -879,6 +890,7 @@
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -927,6 +939,7 @@
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -979,6 +992,11 @@
           <t>★v3：选填→推荐（湿度隐变量）</t>
         </is>
       </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"le":100}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -1031,6 +1049,11 @@
           <t>暂无设备，先占位</t>
         </is>
       </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -1083,6 +1106,7 @@
           <t>只是提醒，不存数据</t>
         </is>
       </c>
+      <c r="K11" s="11" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -1099,6 +1123,7 @@
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -1151,6 +1176,7 @@
           <t>★R0；复合体系权威在『组成明细』；录入使用普通数字</t>
         </is>
       </c>
+      <c r="K13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -1170,7 +1196,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1203,6 +1229,7 @@
           <t>判别器；决定组成明细是否必填</t>
         </is>
       </c>
+      <c r="K14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -1252,9 +1279,10 @@
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>★v3.2b升为权威源+条件必填；数量拆浓度/层序；杜绝退回字符串（复审N2）</t>
-        </is>
-      </c>
+          <t>★v3.2b升为权威源+条件必填；数量拆浓度/层序；掺杂浓度已知时须0&lt;at%&lt;100，垂直结构下层层序须早于上层；杜绝退回字符串（复审N2）</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -1307,6 +1335,11 @@
           <t>目标与实测分开</t>
         </is>
       </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -1359,6 +1392,7 @@
           <t>★v3：从『层群/点群/多型』改回体相空间群；手性/扭转角/堆垛→备注</t>
         </is>
       </c>
+      <c r="K17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -1407,6 +1441,7 @@
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -1459,6 +1494,7 @@
           <t>★v3.4导师评审：可选项列补示例引导；目标=愿景保持轻量；严格『数值绑测试方法』在§7实测侧</t>
         </is>
       </c>
+      <c r="K19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -1507,6 +1543,7 @@
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -1523,6 +1560,7 @@
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -1571,6 +1609,7 @@
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -1619,6 +1658,7 @@
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -1667,6 +1707,7 @@
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -1715,6 +1756,11 @@
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -1763,6 +1809,7 @@
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -1811,6 +1858,7 @@
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -1830,12 +1878,12 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>1″/2″/4″/自定义 + 壁厚</t>
+          <t>{outer_diameter_mm, wall_thickness_mm}</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -1863,6 +1911,7 @@
           <t>内径决定流速/分压</t>
         </is>
       </c>
+      <c r="K28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -1915,6 +1964,7 @@
           <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
         </is>
       </c>
+      <c r="K29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -1967,6 +2017,7 @@
           <t>仅选『用了哪些』；定量参数在§5，定性几何进示意图</t>
         </is>
       </c>
+      <c r="K30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -2015,6 +2066,7 @@
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -2067,6 +2119,7 @@
           <t>★v3：自由文本→结构化两数字；退火/清管方法另记</t>
         </is>
       </c>
+      <c r="K32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -2083,6 +2136,7 @@
       <c r="H33" s="8" t="n"/>
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -2131,6 +2185,7 @@
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -2179,6 +2234,7 @@
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -2231,6 +2287,7 @@
           <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
         </is>
       </c>
+      <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -2283,6 +2340,7 @@
           <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
         </is>
       </c>
+      <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -2302,12 +2360,12 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -2335,6 +2393,7 @@
           <t>防以后改批次信息影响旧记录</t>
         </is>
       </c>
+      <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -2387,6 +2446,7 @@
           <t>界面中文(英文)</t>
         </is>
       </c>
+      <c r="K39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -2439,6 +2499,11 @@
           <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
         </is>
       </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -2487,6 +2552,7 @@
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -2506,12 +2572,12 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>石英舟/陶瓷(刚玉)舟/其他；长×宽×高（直径）</t>
+          <t>{material, length_mm, width_mm, height_mm, diameter_mm}</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -2539,6 +2605,7 @@
           <t>v3暂保留长×宽×高</t>
         </is>
       </c>
+      <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -2558,12 +2625,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>温区温度对象</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>温区1…</t>
+          <t>{zone_index, temperature_C}</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -2591,6 +2658,7 @@
           <t>按进气端编号</t>
         </is>
       </c>
+      <c r="K43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -2643,6 +2711,7 @@
           <t>上游为负、下游为正</t>
         </is>
       </c>
+      <c r="K44" s="11" t="inlineStr"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
@@ -2659,6 +2728,7 @@
       <c r="H45" s="8" t="n"/>
       <c r="I45" s="8" t="n"/>
       <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -2707,6 +2777,7 @@
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr"/>
+      <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -2716,22 +2787,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>化学式/取向</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>化学式与晶面取向/偏转角</t>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>标准写法（如 x面向x轴偏X°）</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -2746,19 +2817,20 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Si(100)</t>
+          <t>Sapphire-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>单晶记取向+偏转角</t>
-        </is>
-      </c>
+          <t>与前驱体引用使用同一不可变版本快照契约</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -2768,37 +2840,37 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度</t>
+          <t>化学式/取向</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）</t>
+          <t>化学式与晶面取向/偏转角</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>写成 SiO₂/Si(285nm)</t>
+          <t>标准写法（如 x面向x轴偏X°）</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>Si(100)</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -2806,7 +2878,12 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>单晶记取向+偏转角</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -2816,12 +2893,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>表面粗糙度</t>
+          <t>氧化层厚度</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Ra / RMS</t>
+          <t>SiO₂ 层厚度（决定光学判层数）</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -2831,7 +2908,7 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>写成 SiO₂/Si(285nm)</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -2839,24 +2916,25 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>&lt;1</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>常比化学式更决定成核；可问厂家或AFM</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -2868,27 +2946,27 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>尺寸/朝向</t>
+          <t>表面粗糙度</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>几何尺寸与放置朝向</t>
+          <t>Ra / RMS</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>数值+下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚；正放/倒扣/倾角/竖放</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2898,15 +2976,24 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5；正放</t>
+          <t>&lt;1</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>会议/建议</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>常比化学式更决定成核；可问厂家或AFM</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -2916,45 +3003,46 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>尺寸/朝向</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>几何尺寸与放置朝向</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>清洗/退火/等离子/亲水化/其他</t>
+          <t>{length_mm, width_mm, thickness_mm, placement}</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>丙酮→异丙醇→N₂吹干</t>
+          <t>10×10×0.5；正放</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>会议/建议</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -2964,49 +3052,46 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>处理到装炉间隔/暴露环境</t>
+          <t>预处理（有序步骤）</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>清洗后到装炉的时间与环境</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>清洗/退火/等离子/亲水化/其他</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>30 min，空气</t>
+          <t>丙酮→异丙醇→N₂吹干</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>表面老化</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3016,113 +3101,120 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
+          <t>处理到装炉间隔/暴露环境</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>清洗后到装炉的时间与环境</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>30 min，空气</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
           <t>所在温区/距热电偶距离</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>第几温区、距离(±)</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>下拉+数值</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>温区2…</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>温区距离对象</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>{zone_index, distance_mm}</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G53" s="15" t="inlineStr">
+      <c r="G54" s="15" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>温区2，+15</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I54" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>§5 反应条件（按时间顺序的各阶段；每阶段填同一套：气体/温度/压力/时长；阶段类型驱动动态表单）</t>
         </is>
       </c>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>阶段类型</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>这一步在做什么（选后只显示对应参数）</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>抽气/漏检/吹扫/预处理/升温/温度稳定/反应生长/后退火/降温/放气/卸样</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>反应生长</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr">
-        <is>
-          <t>多步可加；跨组比较看类型</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -3132,69 +3224,70 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>步序/起止时刻</t>
+          <t>阶段类型</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>第几步、起止时间</t>
+          <t>这一步在做什么（选后只显示对应参数）</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>数值+时间</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>抽气/漏检/吹扫/预处理/升温/温度稳定/反应生长/后退火/降温/放气/卸样</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="G56" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>#3，10:20–10:35</t>
+          <t>反应生长</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>支持重叠/循环</t>
-        </is>
-      </c>
+          <t>多步可加；跨组比较看类型</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>步序/起止时刻</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>各温区升温曲线（目标温/速率/保温）</t>
+          <t>第几步、起止时间</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>数组</t>
+          <t>数值+时间</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
@@ -3204,29 +3297,30 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min·min</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>温区2：25→750@20℃/min，保温15</t>
+          <t>#3，10:20–10:35</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>设定值；分温区</t>
-        </is>
-      </c>
+          <t>支持重叠/循环</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -3236,17 +3330,17 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>实测温度</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>控温热电偶实测曲线（导入）。注意：不是衬底真温</t>
+          <t>各温区升温曲线（目标温/速率/保温）</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>数组(时序)</t>
+          <t>数组</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -3256,29 +3350,30 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G58" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>℃·℃/min·min</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>[导入 furnace.csv]</t>
+          <t>温区2：25→750@20℃/min，保温15</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J58" s="13" t="inlineStr">
-        <is>
-          <t>★v3：删『估算衬底真温』，只留设定+实测</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>设定值；分温区</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -3288,37 +3383,37 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>测温设备/不确定度</t>
+          <t>实测温度</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>测温点用什么设备、不确定度多少</t>
+          <t>控温热电偶实测曲线（导入）。注意：不是衬底真温</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>引用+数值</t>
+          <t>数组(时序)</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>热电偶/高温计；来源：仪器/校准/重复性/估计</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>K型热电偶，±1℃</t>
+          <t>[导入 furnace.csv]</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -3326,111 +3421,118 @@
           <t>会议/复审</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr">
-        <is>
-          <t>测量不确定度</t>
-        </is>
-      </c>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>★v3：删『估算衬底真温』，只留设定+实测</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>降温方式/开盖温度/速率</t>
+          <t>测温设备/不确定度</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>降温段参数（阶段类型=降温 时）</t>
+          <t>测温点用什么设备、不确定度多少</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>引用+数值</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>随炉冷却/开盖冷却/移炉快速冷却；开盖温度；降温速率</t>
+          <t>热电偶/高温计；来源：仪器/校准/重复性/估计</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
-        </is>
-      </c>
-      <c r="G60" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(降温段)</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>随炉冷却；开盖~580</t>
+          <t>K型热电偶，±1℃</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J60" s="13" t="inlineStr">
-        <is>
-          <t>★v3.2补回：review文档头部隐变量，勿再漏（Fable评审）</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>测量不确定度</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>气体组分</t>
+          <t>降温方式/开盖温度/速率</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>每种气体单独一条（混合气拆开）</t>
+          <t>降温段参数（阶段类型=降温 时）</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>下拉(多条)</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Ar/N2/H2/O2/CH4/其他</t>
+          <t>随炉冷却/开盖冷却/移炉快速冷却；开盖温度；降温速率</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(降温段)</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t>随炉冷却；开盖~580</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>★v3.2补回：review文档头部隐变量，勿再漏（Fable评审）</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -3440,45 +3542,46 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>纯度/浓度/水氧</t>
+          <t>气体组分</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>纯度、体积比、水氧杂质</t>
+          <t>每种气体单独一条（混合气拆开）</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉(多条)</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar/N2/H2/O2/CH4/其他</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>N·%·ppm</t>
-        </is>
-      </c>
-      <c r="G62" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Ar 5N；水氧&lt;1ppm</t>
+          <t>Ar</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -3488,141 +3591,143 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>流量/来源</t>
+          <t>其他气体名称</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>流量、流量计类型</t>
+          <t>气体组分选择“其他”时记录明确化学名称或化学式</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>数值+下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>MFC/转子</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>sccm</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(气体组分含其他)</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>80（MFC）</t>
+          <t>NH3</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>科学契约审查</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>sccm须绑标准状态；设定+实测</t>
-        </is>
-      </c>
+          <t>禁止用“其他”丢失真实气体身份</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>压力体系/工作压力</t>
+          <t>纯度/浓度/水氧</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>常压/低压/超高真空 + 工作压力</t>
+          <t>纯度、体积比、水氧杂质</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>必填(生长)/选填(其余)</t>
+          <t>N·%·ppm</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>常压；1.0×10⁵ Pa</t>
+          <t>Ar 5N；水氧&lt;1ppm</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>所有阶段可出现</t>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>本底压力/漏率</t>
+          <t>流量/来源</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>反应前底压、漏率</t>
+          <t>本阶段记录值与流量计类型</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>数值+下拉</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFC/转子</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>Pa·Pa·L/s</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>sccm</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80（MFC）</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -3630,47 +3735,56 @@
           <t>会议/复审</t>
         </is>
       </c>
-      <c r="J65" s="11" t="inlineStr"/>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>sccm须绑定Setup版本中冻结的参考温度和参考绝对压力；当前仅记录单个阶段值与流量计类型，设定值/实测值拆分延后</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>时长/循环次数</t>
+          <t>压力体系/工作绝对压力</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>本阶段时长、吹扫抽-充次数</t>
+          <t>常压/低压/超高真空类别及本阶段工作绝对压力（非表压）</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>min·次</t>
-        </is>
-      </c>
-      <c r="G66" s="18" t="inlineStr">
-        <is>
-          <t>必填/选填</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>必填(生长)/选填(其余)</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>常压；1.01325×10⁵ Pa（绝对压力）</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -3678,22 +3792,31 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J66" s="11" t="inlineStr"/>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>所有阶段可出现</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>外场参数</t>
+          <t>本底压力/漏率</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>等离子功率/光源（有外场才填，可自填添加）</t>
+          <t>反应前底压、漏率</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -3703,17 +3826,17 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>电场强度；光场:中心波长/线宽/功率密度/光斑大小</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>V·nm·W…</t>
-        </is>
-      </c>
-      <c r="G67" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(Setup有外场)</t>
+          <t>Pa·Pa·L/s</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -3723,134 +3846,138 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>建议/导师</t>
-        </is>
-      </c>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(K65)：选填→条件必填；判别位=Setup.外场装置≠无；无外场则不显示</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（含异常/中断/人工干预等客观事件；只记客观事实、不判成败）</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
-      <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="8" t="n"/>
-      <c r="J68" s="8" t="n"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>时长/循环次数</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>本阶段时长、吹扫抽-充次数</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>min·次</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>必填/选填</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>事件/部位</t>
+          <t>外场参数</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>过程中发生的客观事件 + 关联部位（合并）</t>
+          <t>等离子功率/光源（有外场才填，可自填添加）</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>供电/供水/供气中断·管路堵塞·压力突变·信号异常·人工干预·其他（可加）</t>
+          <t>电场强度；光场:中心波长/线宽/功率密度/光斑大小</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>V·nm·W…</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(Setup有外场)</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>气流中断（Ar气路）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>建议/导师</t>
         </is>
       </c>
       <c r="J69" s="13" t="inlineStr">
         <is>
-          <t>★v3：事件类型与关联对象合并为一个下拉</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>发生时刻</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>何时发生（记绝对时间）</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>相对时间可由t0算</t>
-        </is>
-      </c>
+          <t>★v3.4导师评审(K65)：选填→条件必填；判别位=Setup.外场装置≠无；无外场则不显示</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（含异常/中断/人工干预等客观事件；只记客观事实、不判成败）</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
+      <c r="G70" s="8" t="n"/>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -3860,22 +3987,22 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>中止原因</t>
+          <t>事件/部位</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>若中止（只记客观原因，不写成败）</t>
+          <t>过程中发生的客观事件 + 关联部位（合并）</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划结束</t>
+          <t>供电/供水/供气中断·管路堵塞·压力突变·信号异常·人工干预·其他（可加）</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -3890,7 +4017,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>计划结束</t>
+          <t>气流中断（Ar气路）</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -3898,7 +4025,12 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J71" s="11" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>★v3：事件类型与关联对象合并为一个下拉</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -3908,17 +4040,17 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>描述/措施/附件</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>现象、处理、相关文件</t>
+          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>自由+附件</t>
+          <t>日期时间</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -3938,7 +4070,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Ar瓶压不足，已更换</t>
+          <t>2026-07-24T10:28:00+08:00</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -3946,48 +4078,86 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="8" t="n"/>
-      <c r="J73" s="8" t="n"/>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>相对时间可由t0算</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>中止原因</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>若中止（只记客观原因，不写成败）</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>设备报警/人工停止/计划结束</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>计划结束</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>表征类型/仪器</t>
+          <t>描述/措施/附件</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>表征手段 + 引用仪器</t>
+          <t>现象、处理、相关文件</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>自由+附件</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -3995,14 +4165,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G74" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Ar瓶压不足，已更换</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -4010,63 +4180,25 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J74" s="13" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>测试条件</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>该表征的测试参数</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>文本/自由</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>532nm / 1mW / 100×</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J75" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
-        </is>
-      </c>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -4076,22 +4208,22 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>表征类型/仪器</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>表征手段 + 引用仪器</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -4106,40 +4238,45 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J76" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J76" s="13" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4147,46 +4284,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>532nm / 1mW / 100×</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J77" s="13" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>检出相/多型/堆垛</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -4199,26 +4337,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J78" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr"/>
+      <c r="K78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -4228,27 +4363,27 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>实测层数/覆盖率</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>实测层数与覆盖率</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>层·%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
@@ -4258,7 +4393,7 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>1 层；~70%</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -4266,7 +4401,12 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J79" s="11" t="inlineStr"/>
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -4276,13 +4416,17 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸/成核密度/连续性</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr"/>
+          <t>检出相/多型/堆垛</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>测到的物相/多型/堆垛类型</t>
+        </is>
+      </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -4292,7 +4436,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>μm·cm⁻²·(连续/孤立)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -4302,15 +4446,20 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>畴 ~50 μm</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr"/>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J80" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -4320,12 +4469,12 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -4340,7 +4489,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>cm⁻¹·eV·nm·%…</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -4350,98 +4499,149 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Δ(A1g-E2g)≈20；PL~1.85eV</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J81" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-      <c r="J82" s="8" t="n"/>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"type":"integer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>覆盖率</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>明确视场或统计区域内材料面积占比</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"le":100}</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>μm</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>复审/科学契约审查</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>成核密度</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>指定统计区域内单位面积成核点数量</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -4456,121 +4656,104 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G84" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>复审/科学契约审查</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>功率/偏压</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>结构化指标数组</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
-        </is>
-      </c>
-      <c r="G85" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>按指标</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J85" s="11" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t>等离子气氛/工作气压</t>
-        </is>
-      </c>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>溅射气体与气压</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>下拉+数值</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>Ar / Ar+N₂…</t>
-        </is>
-      </c>
-      <c r="F86" s="11" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G86" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H86" s="11" t="inlineStr">
-        <is>
-          <t>Ar，0.5 Pa</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J86" s="11" t="inlineStr"/>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J85" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="8" t="n"/>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="8" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -4580,27 +4763,27 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>预溅射/挡板时序</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr">
@@ -4610,7 +4793,7 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -4619,6 +4802,7 @@
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -4628,57 +4812,270 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
+          <t>靶基距</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>靶到衬底距离</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H88" s="11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr"/>
+      <c r="K88" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>功率/偏压</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>DC/RF 功率、基底偏压</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>DC/RF</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>W·V</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>RF 150W；偏压 -50V</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>等离子气氛/工作气压</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>溅射气体与气压</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>下拉+数值</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>Ar / Ar+N₂…</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>Ar，0.5 Pa</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>预溅射/挡板时序</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr"/>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
           <t>沉积速率</t>
         </is>
       </c>
-      <c r="C88" s="11" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>速率（QCM 等）</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="D92" s="11" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F88" s="11" t="inlineStr">
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>nm/s</t>
         </is>
       </c>
-      <c r="G88" s="16" t="inlineStr">
+      <c r="G92" s="16" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
-      <c r="H88" s="11" t="inlineStr">
+      <c r="H92" s="11" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr">
+      <c r="I92" s="11" t="inlineStr">
         <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J88" s="11" t="inlineStr"/>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="A73:J73"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A82:J82"/>
-    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A86:K86"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A70:K70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4690,7 +5087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4703,6 +5100,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4754,6 +5152,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>机器约束</t>
         </is>
       </c>
     </row>
@@ -4772,6 +5175,7 @@
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -4788,6 +5192,7 @@
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4840,6 +5245,7 @@
           <t>驱动子类条件字段</t>
         </is>
       </c>
+      <c r="K4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -4892,6 +5298,7 @@
           <t>改则新版本，旧引用不受影响</t>
         </is>
       </c>
+      <c r="K5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -4940,6 +5347,7 @@
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -4959,12 +5367,12 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>物料化学式</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>支持括号、化学计量数与水合点</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -4988,6 +5396,7 @@
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5036,6 +5445,7 @@
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -5084,6 +5494,7 @@
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -5132,6 +5543,7 @@
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -5180,6 +5592,7 @@
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -5232,6 +5645,7 @@
           <t>GMP法定术语『批号』</t>
         </is>
       </c>
+      <c r="K12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -5246,7 +5660,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>质量分数或N值</t>
+          <t>仅存质量百分数；N值由质量百分数派生显示，不作为独立存储值</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -5256,7 +5670,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>%或N值</t>
+          <t>质量百分数（N值仅派生显示）</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -5271,7 +5685,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>99.95（4N5）</t>
+          <t>99.995（派生显示4N5）</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -5279,7 +5693,16 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>原始证书中的N值或其他纯度表述保留在CoA/附件说明中</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"le":100}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -5328,6 +5751,11 @@
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -5380,6 +5808,7 @@
           <t>外观=性状</t>
         </is>
       </c>
+      <c r="K15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -5428,6 +5857,7 @@
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr"/>
+      <c r="K16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -5480,6 +5910,7 @@
           <t>desiccator=干燥器</t>
         </is>
       </c>
+      <c r="K17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -5499,12 +5930,12 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>FileAsset引用</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{file_asset_id, sha256}</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -5528,6 +5959,7 @@
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -5580,6 +6012,7 @@
           <t>与§4衬底材料词表一致</t>
         </is>
       </c>
+      <c r="K19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -5628,6 +6061,11 @@
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -5676,6 +6114,7 @@
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -5724,6 +6163,7 @@
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -5776,6 +6216,7 @@
           <t>分工：base纯度填数值%、此处填等级标签(Fable三轮B4)</t>
         </is>
       </c>
+      <c r="K23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -5824,6 +6265,7 @@
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -5840,6 +6282,7 @@
       <c r="H25" s="8" t="n"/>
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -5888,6 +6331,7 @@
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -5936,6 +6380,7 @@
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -5988,6 +6433,7 @@
           <t>对标 v1 setup_version_snapshot</t>
         </is>
       </c>
+      <c r="K28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -6036,6 +6482,7 @@
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -6084,6 +6531,7 @@
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -6132,6 +6580,11 @@
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -6141,27 +6594,27 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>sccm参考温度</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>MFC/流量计把体积流量换算为 sccm 时采用的参考温度</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -6171,15 +6624,24 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr"/>
+          <t>科学契约审查</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>与参考压力一起随 Setup 版本冻结</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":-273.15}</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -6189,45 +6651,54 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>管材质/形状</t>
+          <t>sccm参考压力</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>MFC/流量计把体积流量换算为 sccm 时采用的参考绝对压力</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>石英/刚玉；圆/方/矩</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>石英·圆形</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
+          <t>科学契约审查</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>与参考温度一起随 Setup 版本冻结</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -6237,37 +6708,37 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>管外径/壁厚(→内径)</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>管规格</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>1″/2″/4″/自定义 + 壁厚</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>1″，壁厚2</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -6276,6 +6747,7 @@
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -6285,27 +6757,27 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>加热区长度</t>
+          <t>管材质/形状</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>恒温区长度（影响停留/温场）</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>石英/刚玉；圆/方/矩</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
@@ -6315,19 +6787,16 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>石英·圆形</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>★review§4.1B补</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>v3曾漏，Fable点名</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -6337,49 +6806,46 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>管外径/壁厚(→内径)</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>原点固定、上游负/下游正（随引用冻结）</t>
+          <t>管规格</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>原点+轴向</t>
+          <t>{outer_diameter_mm, wall_thickness_mm}</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>原点=温区2热电偶；下游为正</t>
+          <t>1″，壁厚2</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>全局定死，防选反</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -6389,17 +6855,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>泵型号/极限压力</t>
+          <t>加热区长度</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>真空能力</t>
+          <t>恒温区长度（影响停留/温场）</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>文本+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -6409,17 +6875,17 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>机械泵，10 Pa</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -6427,7 +6893,16 @@
           <t>★review§4.1B补</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>v3曾漏，Fable点名</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -6437,22 +6912,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>MFC配置</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>各通道气体/量程/校准日期</t>
+          <t>原点固定、上游负/下游正（随引用冻结）</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>数组</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>通道/气体/量程(sccm)/校准日期</t>
+          <t>原点+轴向</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -6460,22 +6935,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>CH1 Ar 0–200sccm</t>
+          <t>原点=温区2热电偶；下游为正</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>★review§4.1B补</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>全局定死，防选反</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -6485,27 +6965,27 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>仪器PID</t>
+          <t>泵型号/极限绝对压力</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>持久标识（预留）</t>
+          <t>结构化复合值；option=泵型号文本，value=极限绝对压力数值</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本+数值</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>PIDINST/PID</t>
+          <t>{option:泵型号文本,value:极限绝对压力}</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -6515,15 +6995,24 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{"option":"Edwards RV12","value":2.0}</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr"/>
+          <t>★review§4.1B补</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>保持单字段的{option,value}契约，不拆成两个字段</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -6533,22 +7022,22 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>外场装置</t>
+          <t>MFC配置</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>是否配光/电/等离子源</t>
+          <t>各通道气体/量程/校准日期</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>多选+描述</t>
+          <t>数组</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子</t>
+          <t>通道/气体/量程(sccm)/校准日期</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -6563,19 +7052,16 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>CH1 Ar 0–200sccm</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>定量参数在实验§5</t>
-        </is>
-      </c>
+          <t>★review§4.1B补</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -6585,22 +7071,22 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>装置示意图/描述</t>
+          <t>仪器PID</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>照片/示意图+文字</t>
+          <t>持久标识（预留）</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>附件+自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PIDINST/PID</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -6608,63 +7094,101 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
+      <c r="K41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>外场装置</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>是否配光/电/等离子源</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>多选+描述</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>无/光/电/等离子</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>定量参数在实验§5</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>装置示意图/描述</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>照片/示意图+文字</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -6672,70 +7196,40 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>仪器名称/类型</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>手段类型</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -6745,12 +7239,12 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>厂商(vendor)</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -6768,22 +7262,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -6793,22 +7288,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>型号(model)</t>
+          <t>仪器名称/类型</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>手段类型</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -6816,22 +7311,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr"/>
+      <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -6841,12 +7337,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>序列号(serial)</t>
+          <t>厂商(vendor)</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -6864,14 +7360,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -6880,6 +7376,7 @@
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr"/>
+      <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -6889,12 +7386,12 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>PID(持久标识)</t>
+          <t>型号(model)</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识（预留）</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -6912,22 +7409,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr"/>
+      <c r="K48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -6937,12 +7435,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>所在实验室/位置</t>
+          <t>序列号(serial)</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -6967,15 +7465,16 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -6985,22 +7484,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>PID(持久标识)</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
+          <t>仪器持久标识（预留）</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>如激光波长/物镜/探测器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -7015,15 +7514,16 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>532nm激光</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication/PIDINST</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -7033,52 +7533,151 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
+          <t>所在实验室/位置</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>物理位置</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>A305</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>如激光波长/物镜/探测器</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>532nm激光</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
           <t>最近校准/维护</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>校准/维护日期</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr"/>
+      <c r="K53" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7090,7 +7689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7996,28 +8595,94 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr"/>
-      <c r="B45" s="11" t="inlineStr"/>
-      <c r="C45" s="11" t="inlineStr"/>
-      <c r="D45" s="11" t="inlineStr"/>
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>v3.5a</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>§1b</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>结构类型由下拉多选纠正为单选判别器；选择值驱动填写提示及组成明细显隐/条件必填</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>用户走查修复</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
+          <t>v3.6</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>全表/实体</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>科学契约加固：结构类型与组成明细纳入R0；补衬底批次引用、具名几何、其他气体名称、sccm参考状态及字段级数值边界</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>全库审查修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>v3.6</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>§6–§7</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>过程事件改为带UTC offset的绝对日期时间；实测层数、覆盖率、畴尺寸、成核密度拆为独立量，关键谱学指标改为带单位的结构化数组</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>全库审查修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr"/>
+      <c r="B48" s="11" t="inlineStr"/>
+      <c r="C48" s="11" t="inlineStr"/>
+      <c r="D48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>硬必填核心(≈16项，含条件必填)</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>实验时间·合成方法·实验人·样品编号·目标化学式·装置·温区数·炉体方向·前驱体名称·前驱体用量(固态源)·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系(生长)</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>硬必填核心(18项，含条件必填)</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>实验时间·合成方法·实验人·炉次编号·目标材料化学式·结构类型·组成明细(非本征)·装置·温区数·炉体方向·前驱体名称/化学式·前驱体用量(非气态)·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系/工作压力(生长)</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>
@@ -8106,7 +8771,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>下一轮</t>
+          <t>已完成（field-source.yaml）</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8788,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>下一轮</t>
+          <t>不适用（批8整库重建，不迁移v1数据）</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8796,7 @@
       <c r="A6" s="11" t="inlineStr"/>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>── 2026-07-07 导师评审引出的待对齐（计划 07-08 当面问）──</t>
+          <t>── 2026-07-07 导师评审引出的待对齐──</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr"/>
@@ -8234,7 +8899,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>实现期</t>
+          <t>已实现</t>
         </is>
       </c>
     </row>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -46,11 +46,11 @@
       <color rgb="00C00000"/>
     </font>
     <font>
-      <color rgb="00806000"/>
+      <b val="1"/>
+      <color rgb="00B26B00"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00B26B00"/>
+      <color rgb="00806000"/>
     </font>
     <font>
       <b val="1"/>
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7DA"/>
+        <fgColor rgb="00FCEFD6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCEFD6"/>
+        <fgColor rgb="00FFF7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -147,10 +147,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,19 +173,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -803,7 +800,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>创建炉次的当前登录用户</t>
+          <t>创建本条制备记录的当前登录用户</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -851,7 +848,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>炉次编号</t>
+          <t>制备记录编号</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -861,12 +858,12 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>建议含日期</t>
+          <t>CVD-YYYY-NNNN</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -886,10 +883,14 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr"/>
+          <t>产品决策2026-07-22</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>新建制备记录时由服务端生成并校验唯一性</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
@@ -923,9 +924,9 @@
           <t>℃</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -935,10 +936,14 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>每条制备记录重新录入，不沿用上次值</t>
+        </is>
+      </c>
       <c r="K8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
@@ -972,9 +977,9 @@
           <t>%RH</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -984,12 +989,12 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>★v3：选填→推荐（湿度隐变量）</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>每条制备记录重新录入，不沿用上次值</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
@@ -1006,124 +1011,120 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>悬浮粒子浓度</t>
+          <t>实验前检查确认</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>环境洁净度，用粒子数替代主观『干净』</t>
+          <t>确认开始实验前已检查气路、水路与装置状态</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>复选确认</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已完成实验前检查</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>个/m³</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已勾选</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>暂无设备，先占位</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>基本信息</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>实验前预检查</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>开始前的检查提醒（漏率/气路/水路）</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>提示</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>（勾选确认）</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>只是提醒，不存数据</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+          <t>保存明确布尔值；只有 true 才通过锁定门</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>§1b 目标产物（你想做出什么——按你关心的维度选填，不强制全填，每项可选『其他』）</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>目标产物</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>目标材料化学式</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>规范显示串；复合体系须与组成明细一致、以组成明细为准（可自动生成）</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>标准写法（渲染规则）</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>MoS2</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>★R0；复合体系权威在『组成明细』；录入使用普通数字；允许常见圆括号、组成分组与结晶水点号</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -1133,22 +1134,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>目标材料化学式</t>
+          <t>结构类型</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>规范显示串；复合体系须与组成明细一致、以组成明细为准（可自动生成）</t>
+          <t>材料结构类别（是否掺杂/合金/异质结，供机器检索）</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>标准写法（渲染规则）</t>
+          <t>本征/掺杂/合金/垂直异质结/横向异质结/其他</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1163,17 +1164,17 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>MoS2</t>
+          <t>本征</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>★R0；复合体系权威在『组成明细』；录入使用普通数字</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>判别器；决定组成明细是否必填</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr"/>
@@ -1186,22 +1187,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>结构类型</t>
+          <t>组成明细</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>材料结构类别（是否掺杂/合金/异质结，供机器检索）</t>
+          <t>逐组分结构化（复合体系的权威数据源）</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数组items[]</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>本征/掺杂/合金/垂直异质结/横向异质结/其他</t>
+          <t>每条:化学式/角色(主体材料·掺杂剂·合金组分·上层·下层·横向域)/浓度(at%)/层序(整数)</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1209,14 +1210,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(结构类型≠本征)</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>本征</t>
+          <t>{WS2,上层,层序2};{MoS2,下层,层序1}</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -1224,9 +1225,9 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>判别器；决定组成明细是否必填</t>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>★v3.2b升为权威源+条件必填；数量拆浓度/层序；掺杂浓度已知时须0&lt;at%&lt;100，允许一个或多个掺杂剂，不强制“掺杂剂:主体材料”字符串；垂直结构下层层序须早于上层；杜绝退回字符串（复审N2）</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr"/>
@@ -1239,50 +1240,54 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>组成明细</t>
+          <t>目标层数</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>逐组分结构化（复合体系的权威数据源）</t>
+          <t>期望层数</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>数组items[]</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>每条:化学式/角色(基体·掺杂剂·合金组分·上层·下层·横向域)/浓度(at%)/层序(整数)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(结构类型≠本征)</t>
+          <t>层</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>{WS2,上层,层序2};{MoS2,下层,层序1}</t>
+          <t>1（单层）</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>★v3.2b升为权威源+条件必填；数量拆浓度/层序；掺杂浓度已知时须0&lt;at%&lt;100，垂直结构下层层序须早于上层；杜绝退回字符串（复审N2）</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>目标与实测分开</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -1292,12 +1297,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>目标层数</t>
+          <t>体相空间群</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>期望层数</t>
+          <t>晶体对称性：International Tables 空间群号（1–230）</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1312,34 +1317,30 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>1（单层）</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>目标与实测分开</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>★v3：从『层群/点群/多型』改回体相空间群；手性/扭转角/堆垛→备注</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -1349,22 +1350,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>体相空间群</t>
+          <t>样品形态</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>晶体对称性：International Tables 空间群号（1–230）</t>
+          <t>目标形态</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>连续膜/纳米片(flake)/纳米带/纳米管/纳米棒/纳米颗粒/其他</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1372,24 +1373,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>单层连续膜</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>★v3：从『层群/点群/多型』改回体相空间群；手性/扭转角/堆垛→备注</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>目标形态影响合成路线与后续结果解释</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr"/>
@@ -1402,22 +1403,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>样品形态</t>
+          <t>目标性能</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>目标形态</t>
+          <t>应用导向的目标性能（写清想要什么性能 + 打算用什么方法/判据衡量）</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>连续膜/纳米片(flake)/纳米带/纳米管/纳米棒/纳米颗粒/其他</t>
+          <t>示例：希望获得高迁移率，计划通过FET测试评价</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -1425,22 +1426,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>单层连续膜</t>
+          <t>高迁移率（拟FET场效应测）</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
+          <t>会议/导师</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审：可选项列补示例引导；目标=愿景保持轻量；严格『数值绑测试方法』在§7实测侧</t>
+        </is>
+      </c>
       <c r="K18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1451,22 +1456,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>目标性能</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>应用导向的目标性能（写清想要什么性能 + 打算用什么方法/判据衡量）</t>
+          <t>补充说明（手性/扭转角/堆垛类型等放这里）</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>自由+数值</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>示例：光学属性-高荧光量子效率 / 电属性-高迁移率</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -1474,93 +1479,89 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>高迁移率（拟FET场效应测）</t>
+          <t>盐辅助法，追求大畴单层；手性:右手</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>会议/导师</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审：可选项列补示例引导；目标=愿景保持轻量；严格『数值绑测试方法』在§7实测侧</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>目标产物</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>补充说明（手性/扭转角/堆垛类型等放这里）</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>盐辅助法，追求大畴单层；手性:右手</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>§2 实验装置与设计（每台装置只维护一次，实验中直接引用；壁型、温区数、炉体方向、管径和坐标系由所引用装置快照【只读投影】带出，不重录）</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>装置（引用）</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>选择已登记的装置</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>引用</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>装置库</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>1号双温区管式炉</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>§2 实验设备与设计（用到的炉子/装置——一台炉录一次，以后直接引用；壁型/温区数/炉体方向/管径/坐标系等由所引用装置快照【只读投影】带出，不重录）</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -1570,22 +1571,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>装置（引用）</t>
+          <t>品牌与型号</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>选择已登记的装置</t>
+          <t>设备品牌与型号</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>装置库</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -1593,14 +1594,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>合肥科晶 OTF-1200X</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -1619,22 +1620,22 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>品牌/型号</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>设备品牌与型号</t>
+          <t>热壁炉还是冷壁炉（影响生长机理）</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -1649,12 +1650,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
@@ -1668,46 +1669,50 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>热壁炉还是冷壁炉（影响生长机理）</t>
+          <t>独立控温的温区数量</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>1/2/3…</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -1717,27 +1722,27 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>独立控温的温区数量</t>
+          <t>炉管水平还是竖直</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>1/2/3…</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -1747,7 +1752,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -1756,11 +1761,7 @@
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+      <c r="K25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -1770,22 +1771,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>炉管水平还是竖直</t>
+          <t>炉管材料与截面形状</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -1793,22 +1794,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>材质与形状独立保存，禁止从斜杠或分隔符猜测</t>
+        </is>
+      </c>
       <c r="K26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1819,27 +1824,27 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>管材质/形状</t>
+          <t>炉管外径与壁厚</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面形状</t>
+          <t>管径规格与壁厚（内径自动算）</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>石英/刚玉；圆/方/矩</t>
+          <t>{outer_diameter_mm, wall_thickness_mm}</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -1849,7 +1854,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>石英·圆形</t>
+          <t>1″(25.4)，壁厚2</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -1857,7 +1862,11 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>内径决定流速/分压</t>
+        </is>
+      </c>
       <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1868,47 +1877,47 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>管外径/壁厚</t>
+          <t>坐标系</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>管径规格与壁厚（内径自动算）</t>
+          <t>本装置位置参照；全局固定、不可编辑</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>{outer_diameter_mm, wall_thickness_mm}</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>1″(25.4)，壁厚2</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>内径决定流速/分压</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -1921,47 +1930,47 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>坐标系</t>
+          <t>温度传感器与不确定度</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>本装置位置参照；全局固定、不可编辑</t>
+          <t>所引用装置版本中各温区的测温传感器与不确定度，只读带出</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>上游为负 / 下游为正，原点固定</t>
+          <t>{sensor_name, sensor_type, zone_index, uncertainty_C, uncertainty_source: 仪器|校准|重复性|估计}</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>必填(装置登记)</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>K型热电偶，温区1，±1℃</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>实验中不重复填写，由Setup版本快照冻结</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -1974,17 +1983,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>外场激励</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>是否有等离子/光/电场（区分PECVD/光CVD）</t>
+          <t>所引用装置是否具备等离子体、光或电场能力；本炉实际使用情况在反应条件中记录</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>多选+展开</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -1997,7 +2006,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -2009,12 +2018,12 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>仅选『用了哪些』；定量参数在§5，定性几何进示意图</t>
+          <t>只读投影；不得当成本炉实际使用记录</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -2027,7 +2036,7 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>装置示意图/描述</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2068,75 +2077,71 @@
       <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>设备</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>炉管/舟履历</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>累计使用与重置情况</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>数值×2</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>重置次数 + 重置后使用次数</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>次</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>重置1，之后用7</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>★v3：自由文本→结构化两数字；退火/清管方法另记</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>§3 前驱体（用了哪些原料：主源、辅助剂等，可多个；每个一组）</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>前驱体</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>前驱体标识（名称或化学式）</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>原料名称与化学式</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>受控+其他</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>MoO₃</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -2146,22 +2151,22 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>名称/化学式</t>
+          <t>化学标识（来自批次）</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>原料名称与化学式</t>
+          <t>从所选物料批次快照带出的 CAS 号和公共数据库标识</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>CAS 或 InChI</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -2169,22 +2174,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>三氧化钼 / MoO₃</t>
+          <t>1313-27-5</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>由后端根据冻结物料批次快照重建，前端只读，不接受用户覆盖</t>
+        </is>
+      </c>
       <c r="K34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2195,22 +2204,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>CAS/InChI</t>
+          <t>相态</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>唯一化学标识（消除同名歧义）</t>
+          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>CAS 或 InChI</t>
+          <t>固/气/液</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -2218,22 +2227,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>1313-27-5</t>
+          <t>固</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
+        </is>
+      </c>
       <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2244,22 +2257,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>相态</t>
+          <t>外观描述</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
+          <t>使用时外观/性状——溯源时判断是否潮解、变质（湿度隐变量的可观察代理）</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>固/气/液</t>
+          <t>白色粉末/白色晶粒/淡黄色粉末/结块或潮解/变色/其他</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -2267,24 +2280,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>推荐(固态源)</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>固</t>
+          <t>白色粉末</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>导师</t>
         </is>
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
+          <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
@@ -2297,22 +2310,22 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>外观描述</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>使用时外观/性状——溯源时判断是否潮解、变质（湿度隐变量的可观察代理）</t>
+          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>白色粉末/白色晶粒/淡黄色粉末/结块或潮解/变色/其他</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -2320,24 +2333,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>推荐(固态源)</t>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>白色粉末</t>
+          <t>MoO₃-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>导师</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>必须引用正确类别的物料批次并冻结版本，纯度、CAS和标签证据从快照带出</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
@@ -2350,22 +2363,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
+          <t>在反应里的角色</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>主源/辅助剂/掺杂源/其他</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -2373,24 +2386,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>MoO₃-B202（锁 v1）</t>
+          <t>主源</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>防以后改批次信息影响旧记录</t>
+          <t>界面中文(英文)</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -2403,50 +2416,54 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>角色（role）</t>
+          <t>用量</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>在反应里的角色</t>
+          <t>投料量（只记投料，不记残余）</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>主源/辅助剂/掺杂源/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mg 或 µL（按相态）</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件必填(非气态)</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>主源</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>界面中文(英文)</t>
-        </is>
-      </c>
-      <c r="K39" s="11" t="inlineStr"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -2456,54 +2473,50 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>投料量（只记投料，不记残余）</t>
+          <t>投料前处理（可多步，选了再展开参数）</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>前驱体处理步骤数组</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{type: 直接加载|熔融凝固|压片|旋涂|退火|研磨|其他, other_name?, parameters: 具名参数对象}</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>mg(固)/µL(液)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(非气态)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>[{type: 旋涂, parameters: {speed_rpm: 3000, duration_s: 60}}]</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
-        <is>
-          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>有序可重复；已知方式使用具名参数和固定单位；压片及其他使用至少一项{name,value,unit}，不接受无单位自由文本</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -2513,27 +2526,27 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>舟或坩埚</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>投料前处理（可多步，选了再展开参数）</t>
+          <t>盛装容器材质与尺寸</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>直接加载/熔融凝固/压片/旋涂/退火/研磨/其他</t>
+          <t>{material: 石英舟|陶瓷(刚玉)舟|其他, material_other?, length_mm?, width_mm?, height_mm?, diameter_mm?}</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -2543,15 +2556,19 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>直接加载</t>
+          <t>石英舟 90×15</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>至少填写一个具名尺寸；material=其他时material_other必填</t>
+        </is>
+      </c>
       <c r="K41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2562,27 +2579,27 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>舟/坩埚</t>
+          <t>所在温区与源温</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>盛装容器材质与尺寸</t>
+          <t>放第几温区、源温（若可设/可测）</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>温区温度对象</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>{material, length_mm, width_mm, height_mm, diameter_mm}</t>
+          <t>{zone_index, temperature_C}</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -2592,17 +2609,17 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>石英舟 90×15</t>
+          <t>温区1，设定~620</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>v3暂保留长×宽×高</t>
+          <t>按进气端编号</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -2615,27 +2632,27 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>所在温区/源温</t>
+          <t>距热电偶距离</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>放第几温区、源温（若可设/可测）</t>
+          <t>距所在温区热电偶的水平距离</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>温区温度对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, temperature_C}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
@@ -2645,7 +2662,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>温区1，设定~620</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -2655,80 +2672,76 @@
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>按进气端编号</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>距热电偶距离</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>距所在温区热电偶的水平距离</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>-20</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>§4 衬底（长在什么基底上，可多片）</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>衬底材料</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>衬底种类</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>SiO₂/Si</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>上游为负、下游为正</t>
-        </is>
-      </c>
-      <c r="K44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>§4 衬底（长在什么基底上，可多片）</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
+      <c r="J45" s="11" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -2738,22 +2751,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>衬底材料</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>衬底种类</t>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -2768,15 +2781,19 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>Sapphire-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>必须引用衬底类别的不可变物料版本</t>
+        </is>
+      </c>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2787,22 +2804,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>衬底化学式</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>引用衬底批号并冻结当时版本、规格与证据</t>
+          <t>衬底材料的化学式；可从物料批次快照带出</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -2810,24 +2827,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Sapphire-B202（锁 v1）</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>与前驱体引用使用同一不可变版本快照契约</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr"/>
@@ -2840,12 +2857,12 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>化学式/取向</t>
+          <t>晶面取向</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>化学式与晶面取向/偏转角</t>
+          <t>单晶衬底的晶面或晶轴取向</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2855,7 +2872,7 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>标准写法（如 x面向x轴偏X°）</t>
+          <t>例如 (100)、c面、a面</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -2863,24 +2880,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Si(100)</t>
+          <t>(100)</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>单晶记取向+偏转角</t>
+          <t>不与化学式或偏转角合并</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr"/>
@@ -2893,12 +2910,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度</t>
+          <t>偏转角</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）</t>
+          <t>晶面相对标称取向的偏转角</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -2908,33 +2925,37 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>写成 SiO₂/Si(285nm)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>锁定前必须确认；无偏转填0，不得留空或揉入晶向字符串</t>
+        </is>
+      </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"lt":90}</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2967,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>表面粗糙度</t>
+          <t>氧化层厚度</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Ra / RMS</t>
+          <t>SiO₂ 层厚度（决定光学判层数）</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -2961,7 +2982,7 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -2971,27 +2992,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>&lt;1</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>常比化学式更决定成核；可问厂家或AFM</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -3003,45 +3020,49 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>尺寸/朝向</t>
+          <t>表面粗糙度指标与数值</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>几何尺寸与放置朝向</t>
+          <t>表面粗糙度的指标类型和对应数值</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm, placement}</t>
+          <t>{metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5；正放</t>
+          <t>{metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>会议/建议</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>value_nm必须大于等于0；Ra和RMS不可省略</t>
+        </is>
+      </c>
       <c r="K51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3052,45 +3073,49 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>尺寸与放置方式</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>几何尺寸、放置方式及条件角度</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>清洗/退火/等离子/亲水化/其他</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>丙酮→异丙醇→N₂吹干</t>
+          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
+        </is>
+      </c>
       <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3101,54 +3126,50 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>处理到装炉间隔/暴露环境</t>
+          <t>预处理（有序步骤）</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>清洗后到装炉的时间与环境</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>30 min，空气</t>
+          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K53" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -3158,199 +3179,207 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>所在温区/距热电偶距离</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>第几温区、距离(±)</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>温区距离对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, distance_mm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G54" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>温区2，+15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr"/>
-      <c r="K54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>§5 反应条件（按时间顺序的各阶段；每阶段填同一套：气体/温度/压力/时长；阶段类型驱动动态表单）</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="8" t="n"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>暴露环境</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>处理完成到放入实验装置期间所处环境</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>空气/氮气/真空/其他</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>空气</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>与时间间隔独立保存</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>阶段类型</t>
+          <t>所在温区与热电偶距离</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>这一步在做什么（选后只显示对应参数）</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>抽气/漏检/吹扫/预处理/升温/温度稳定/反应生长/后退火/降温/放气/卸样</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>反应生长</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>多步可加；跨组比较看类型</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
     </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>步序/起止时刻</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>第几步、起止时间</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>数值+时间</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>#3，10:20–10:35</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr">
-        <is>
-          <t>支持重叠/循环</t>
-        </is>
-      </c>
-      <c r="K57" s="11" t="inlineStr"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>各温区升温曲线（目标温/速率/保温）</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min·min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -3360,17 +3389,17 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>温区2：25→750@20℃/min，保温15</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>设定值；分温区</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -3378,52 +3407,52 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>实测温度</t>
+          <t>预处理操作</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>控温热电偶实测曲线（导入）。注意：不是衬底真温</t>
+          <t>抽气、气路置换等有序可重复的实验前操作</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>数组(时序)</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G59" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(预处理记录)</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>[导入 furnace.csv]</t>
+          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J59" s="13" t="inlineStr">
-        <is>
-          <t>★v3：删『估算衬底真温』，只留设定+实测</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr"/>
@@ -3436,47 +3465,47 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>测温设备/不确定度</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>测温点用什么设备、不确定度多少</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>引用+数值</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>热电偶/高温计；来源：仪器/校准/重复性/估计</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>K型热电偶，±1℃</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>测量不确定度</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -3484,52 +3513,52 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>降温方式/开盖温度/速率</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>降温段参数（阶段类型=降温 时）</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>随炉冷却/开盖冷却/移炉快速冷却；开盖温度；降温速率</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(降温段)</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>随炉冷却；开盖~580</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>★v3.2补回：review文档头部隐变量，勿再漏（Fable评审）</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr"/>
@@ -3542,286 +3571,286 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>气体组分</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>每种气体单独一条（混合气拆开）</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>下拉(多条)</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Ar/N2/H2/O2/CH4/其他</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>min·sccm</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+        </is>
+      </c>
       <c r="K62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>其他气体名称</t>
+          <t>压力体系与工作绝对压力</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>气体组分选择“其他”时记录明确化学名称或化学式</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(气体组分含其他)</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>NH3</t>
+          <t>常压；1.01325×10⁵ Pa</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>科学契约审查</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>禁止用“其他”丢失真实气体身份</t>
-        </is>
-      </c>
-      <c r="K63" s="11" t="inlineStr"/>
+          <t>填绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>纯度/浓度/水氧</t>
+          <t>时长与循环次数</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>纯度、体积比、水氧杂质</t>
+          <t>反应条件持续时长及可选循环次数</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{duration_min, cycle_count?}</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>N·%·ppm</t>
-        </is>
-      </c>
-      <c r="G64" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min·次</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Ar 5N；水氧&lt;1ppm</t>
+          <t>{duration_min: 45, cycle_count: 2}</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr"/>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>duration_min&gt;0；cycle_count为可选正整数</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>流量/来源</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>本阶段记录值与流量计类型</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>数值+下拉</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>MFC/转子</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>sccm</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>80（MFC）</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>sccm须绑定Setup版本中冻结的参考温度和参考绝对压力；当前仅记录单个阶段值与流量计类型，设定值/实测值拆分延后</t>
-        </is>
-      </c>
-      <c r="K65" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
+          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>压力体系/工作绝对压力</t>
+          <t>实际外场程序</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>常压/低压/超高真空类别及本阶段工作绝对压力（非表压）</t>
+          <t>本炉实际启用的外场、时间区间与具名参数</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{field_type: 等离子|光|电, start_min, end_min, parameters: [{name, value, unit}]}</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>必填(生长)/选填(其余)</t>
+          <t>按参数</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>常压；1.01325×10⁵ Pa（绝对压力）</t>
+          <t>[{field_type: 等离子, start_min: 10, end_min: 40, parameters: [{name: power, value: 50, unit: W}]}]</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>所有阶段可出现</t>
-        </is>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_value":true}</t>
-        </is>
-      </c>
+          <t>field_type必须属于Setup能力；有记录时参数至少一项且不得使用混合单位单值</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>本底压力/漏率</t>
+          <t>其他记录名称</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>反应前底压、漏率</t>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -3831,30 +3860,30 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Pa·Pa·L/s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件必填(其他记录)</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>临时移动源舟</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr"/>
-      <c r="K67" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>禁止仅保存“其他”</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -3864,17 +3893,17 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>时长/循环次数</t>
+          <t>其他记录说明</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>本阶段时长、吹扫抽-充次数</t>
+          <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -3884,100 +3913,100 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>min·次</t>
-        </is>
-      </c>
-      <c r="G68" s="18" t="inlineStr">
-        <is>
-          <t>必填/选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(其他记录)</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>步·外场</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>外场参数</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>等离子功率/光源（有外场才填，可自填添加）</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>电场强度；光场:中心波长/线宽/功率密度/光斑大小</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>V·nm·W…</t>
-        </is>
-      </c>
-      <c r="G69" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(Setup有外场)</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>建议/导师</t>
-        </is>
-      </c>
-      <c r="J69" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(K65)：选填→条件必填；判别位=Setup.外场装置≠无；无外场则不显示</t>
-        </is>
-      </c>
-      <c r="K69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（含异常/中断/人工干预等客观事件；只记客观事实、不判成败）</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="n"/>
-      <c r="G70" s="8" t="n"/>
-      <c r="H70" s="8" t="n"/>
-      <c r="I70" s="8" t="n"/>
-      <c r="J70" s="8" t="n"/>
-      <c r="K70" s="8" t="n"/>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>必须持久化，绝不静默过滤</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>事件编号</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>550e8400-e29b-41d4-a716-446655440000</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>创建事件时生成，排序和编辑不得改变</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -3987,12 +4016,12 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>事件/部位</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>过程中发生的客观事件 + 关联部位（合并）</t>
+          <t>过程中发生的客观事件类型</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -4002,7 +4031,7 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>供电/供水/供气中断·管路堵塞·压力突变·信号异常·人工干预·其他（可加）</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -4010,24 +4039,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G71" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>气流中断（Ar气路）</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J71" s="13" t="inlineStr">
-        <is>
-          <t>★v3：事件类型与关联对象合并为一个下拉</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4063,9 +4092,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G72" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -4075,7 +4104,7 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
@@ -4093,22 +4122,22 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>中止原因</t>
+          <t>是否导致实验终止</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>若中止（只记客观原因，不写成败）</t>
+          <t>该事件是否导致本炉实验提前终止</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>复选</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划结束</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -4116,22 +4145,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G73" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>计划结束</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>客观记录，不等同于成败判断</t>
+        </is>
+      </c>
       <c r="K73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
@@ -4142,22 +4175,22 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>描述/措施/附件</t>
+          <t>终止原因</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>现象、处理、相关文件</t>
+          <t>事件导致实验终止时的客观原因</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>自由+附件</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设备报警/人工停止/计划变更/其他</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -4167,63 +4200,103 @@
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件必填(导致实验终止)</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Ar瓶压不足，已更换</t>
+          <t>设备报警</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>正常计划结束不是异常终止原因</t>
+        </is>
+      </c>
       <c r="K74" s="11" t="inlineStr"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
-      <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="n"/>
-      <c r="I75" s="8" t="n"/>
-      <c r="J75" s="8" t="n"/>
-      <c r="K75" s="8" t="n"/>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>事件具体说明</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>事件现象、涉及对象和上下文</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(终止原因=其他)</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>表征类型/仪器</t>
+          <t>处理措施</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>表征手段 + 引用仪器</t>
+          <t>事件发生后采取的操作</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -4231,24 +4304,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G76" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>更换气瓶后恢复供气</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J76" s="13" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>与事件说明独立保存</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4256,27 +4329,27 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4284,101 +4357,69 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G77" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>532nm / 1mW / 100×</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>随仪器导出</t>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
     </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>原始数据</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>上传原始文件（留校验和）</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>附件</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>raman.txt</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J78" s="11" t="inlineStr"/>
-      <c r="K78" s="11" t="inlineStr"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="8" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>表征方法与仪器</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>表征手段 + 引用仪器</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4386,24 +4427,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G79" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J79" s="13" t="inlineStr">
         <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
@@ -4411,22 +4452,22 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>检出相/多型/堆垛</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -4439,24 +4480,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G80" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>532nm / 1mW / 100×</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J80" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr"/>
@@ -4464,22 +4505,22 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -4489,34 +4530,26 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="G81" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J81" s="11" t="inlineStr">
-        <is>
-          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
-        </is>
-      </c>
-      <c r="K81" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -4526,54 +4559,50 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G82" s="14" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J82" s="11" t="inlineStr">
-        <is>
-          <t>量化口径仍须随表征条件记录</t>
-        </is>
-      </c>
-      <c r="K82" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"le":100}</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J82" s="13" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
@@ -4583,17 +4612,17 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -4603,30 +4632,30 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J83" s="11" t="inlineStr"/>
-      <c r="K83" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J83" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -4636,12 +4665,12 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -4656,17 +4685,17 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
-        </is>
-      </c>
-      <c r="G84" s="14" t="inlineStr">
+          <t>层</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -4674,10 +4703,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J84" s="11" t="inlineStr"/>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
+        </is>
+      </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"ge":0,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -4689,222 +4722,234 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>结构化指标数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>每条:{metric_code,value,unit}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>按指标</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J85" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
-      <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="n"/>
-      <c r="I86" s="8" t="n"/>
-      <c r="J86" s="8" t="n"/>
-      <c r="K86" s="8" t="n"/>
+          <t>{"ge":0,"le":100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>畴尺寸</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>μm</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr"/>
+      <c r="K86" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>成核密度</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>指定统计区域内单位面积成核点数量</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cm⁻²</t>
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr">
         <is>
-          <t>条件必填(PVD)</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>复审/科学契约审查</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
-      <c r="K87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>结构化指标数组</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>按指标</t>
         </is>
       </c>
       <c r="G88" s="16" t="inlineStr">
         <is>
-          <t>条件必填(PVD)</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J88" s="11" t="inlineStr"/>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J88" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+        </is>
+      </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>功率/偏压</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr">
-        <is>
-          <t>DC/RF 功率、基底偏压</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>DC/RF</t>
-        </is>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>W·V</t>
-        </is>
-      </c>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H89" s="11" t="inlineStr">
-        <is>
-          <t>RF 150W；偏压 -50V</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J89" s="11" t="inlineStr"/>
-      <c r="K89" s="11" t="inlineStr"/>
+          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -4914,37 +4959,37 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>等离子气氛/工作气压</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G90" s="16" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -4953,11 +4998,7 @@
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
-      <c r="K90" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
+      <c r="K90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -4967,12 +5008,12 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>预溅射/挡板时序</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -4987,17 +5028,17 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
-        </is>
-      </c>
-      <c r="G91" s="16" t="inlineStr">
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -5020,46 +5061,201 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
+          <t>功率与偏压</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>DC/RF 功率、基底偏压</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>DC/RF</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>W·V</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>RF 150W；偏压 -50V</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>等离子气氛与工作气压</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>溅射气体与气压</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>下拉+数值</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Ar / Ar+N₂…</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>Ar，0.5 Pa</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr"/>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>预溅射与挡板时序</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr"/>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
           <t>沉积速率</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>速率（QCM 等）</t>
         </is>
       </c>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="D95" s="11" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" s="11" t="inlineStr">
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>nm/s</t>
         </is>
       </c>
-      <c r="G92" s="16" t="inlineStr">
+      <c r="G95" s="14" t="inlineStr">
         <is>
           <t>条件必填(PVD)</t>
         </is>
       </c>
-      <c r="H92" s="11" t="inlineStr">
+      <c r="H95" s="11" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr">
+      <c r="I95" s="11" t="inlineStr">
         <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J92" s="11" t="inlineStr"/>
-      <c r="K92" s="11" t="inlineStr">
+      <c r="J95" s="11" t="inlineStr"/>
+      <c r="K95" s="11" t="inlineStr">
         <is>
           <t>{"gt":0}</t>
         </is>
@@ -5067,15 +5263,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A20:K20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A86:K86"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A89:K89"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5087,7 +5283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5180,7 +5376,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>实体① 物料批次库 MaterialLot（前驱体/衬底/气瓶通用 + 子类；实验中只填批号引用，纯度/粒径自动带出并锁版）</t>
+          <t>实体① 物料批次库 MaterialLot（统一维护前驱体、衬底与气瓶批次；实验中只引用批次，纯度和粒径自动带出并锁版）</t>
         </is>
       </c>
       <c r="B3" s="8" t="n"/>
@@ -5429,9 +5625,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(化学品或气瓶)</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -5455,7 +5651,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>InChIKey/PubChem CID</t>
+          <t>公共数据库标识</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -5478,7 +5674,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -5493,7 +5689,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>可填写 InChIKey 或 PubChem CID；没有可靠值时留空</t>
+        </is>
+      </c>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5553,7 +5753,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>货号</t>
+          <t>供应商货号</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -5576,7 +5776,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -5591,7 +5791,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>供应商产品规格编号，标签上常写作 Cat. No.；同一货号可有多个生产批号</t>
+        </is>
+      </c>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -5602,7 +5806,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>批号</t>
+          <t>生产批号</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -5642,7 +5846,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>GMP法定术语『批号』</t>
+          <t>GMP法定术语『批号』；标签上常写作 Lot No. 或 Batch No.</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr"/>
@@ -5678,9 +5882,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(化学品或气瓶)</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -5712,7 +5916,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>粒径(x50/D50)</t>
+          <t>粒径D50</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -5735,7 +5939,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -5765,7 +5969,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>形态/性状</t>
+          <t>形态与性状</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -5788,7 +5992,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -5841,7 +6045,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -5890,7 +6094,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -5943,7 +6147,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
@@ -5969,22 +6173,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·材料</t>
+          <t>瓶身或包装标签附件</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=衬底)</t>
+          <t>试剂瓶身、气瓶或衬底包装标签的原始照片，用于追溯批号与规格</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>FileAsset引用</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>{file_asset_id, sha256}</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -5992,24 +6196,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>bottle-label.jpg</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>与§4衬底材料词表一致</t>
+          <t>与CoA分开；同一物料版本至少上传一次并可预览、下载</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr"/>
@@ -6022,37 +6226,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·氧化层厚度</t>
+          <t>▸衬底·材料</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>仅SiO₂/Si</t>
+          <t>子类(批次类别=衬底)</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>条件必填(SiO₂/Si)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -6060,12 +6264,12 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>与§4衬底材料词表一致</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -6075,37 +6279,37 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向/抛光</t>
+          <t>▸衬底·氧化层厚度</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>仅SiO₂/Si</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(SiO₂/Si)</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -6114,7 +6318,11 @@
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -6124,37 +6332,37 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·尺寸规格</t>
+          <t>▸衬底·晶向与抛光</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>出厂几何</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -6173,37 +6381,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸衬底·尺寸规格</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>出厂几何</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级/其他</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>条件必填(气瓶)</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -6211,11 +6419,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>分工：base纯度填数值%、此处填等级标签(Fable三轮B4)</t>
-        </is>
-      </c>
+      <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
@@ -6226,112 +6430,116 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
+          <t>▸气瓶·纯度等级</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>6N/5N/4N/工业级</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(气瓶)</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>5N</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>分工：base纯度填数值%、此处填等级标签(Fable三轮B4)</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
           <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>钢瓶追溯号</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>GC-Ar-07</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>装置编号</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>唯一编号</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>CVD-炉1</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>review§4.1B</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="11" t="inlineStr"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -6341,12 +6549,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>装置编号</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -6371,12 +6579,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>review§4.1B</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr"/>
@@ -6390,17 +6598,17 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>装置名称</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>人读名</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -6420,19 +6628,15 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>对标 v1 setup_version_snapshot</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr"/>
       <c r="K28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
@@ -6443,22 +6647,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>品牌/型号</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>设备品牌型号</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -6466,22 +6670,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>对标 v1 setup_version_snapshot</t>
+        </is>
+      </c>
       <c r="K29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
@@ -6492,22 +6700,22 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>品牌与型号</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>设备品牌型号</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -6522,12 +6730,12 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>合肥科晶 OTF-1200X</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
@@ -6541,50 +6749,46 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr"/>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+      <c r="K31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -6594,12 +6798,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>sccm参考温度</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>MFC/流量计把体积流量换算为 sccm 时采用的参考温度</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -6614,7 +6818,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -6624,22 +6828,18 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>科学契约审查</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>与参考压力一起随 Setup 版本冻结</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>{"gt":-273.15}</t>
+          <t>{"ge":1,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -6651,27 +6851,27 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>sccm参考压力</t>
+          <t>温度传感器与不确定度</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>MFC/流量计把体积流量换算为 sccm 时采用的参考绝对压力</t>
+          <t>装置各温区的测温传感器、测量不确定度及其来源</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{sensor_name, sensor_type, zone_index, uncertainty_C, uncertainty_source: 仪器|校准|重复性|估计}</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -6681,24 +6881,20 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>101325</t>
+          <t>[{sensor_name: 炉温热电偶1, sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1, uncertainty_source: 校准}]</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>科学契约审查</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>与参考温度一起随 Setup 版本冻结</t>
-        </is>
-      </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>随Setup版本冻结，实验选择装置后自动带出</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -6757,7 +6953,7 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>管材质/形状</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -6767,12 +6963,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>石英/刚玉；圆/方/矩</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -6787,15 +6983,19 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>石英·圆形</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+        </is>
+      </c>
       <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
@@ -6806,7 +7006,7 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>管外径/壁厚(→内径)</t>
+          <t>炉管外径与壁厚</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
@@ -6844,7 +7044,11 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>内径由外径与壁厚派生显示</t>
+        </is>
+      </c>
       <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
@@ -6855,54 +7059,50 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>加热区长度</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>恒温区长度（影响停留/温场）</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>★review§4.1B补</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>v3曾漏，Fable点名</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -6912,22 +7112,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>原点固定、上游负/下游正（随引用冻结）</t>
+          <t>装置具备的光、电或等离子体能力</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>原点+轴向</t>
+          <t>无/光/电/等离子</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -6935,24 +7135,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>原点=温区2热电偶；下游为正</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>全局定死，防选反</t>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -6965,118 +7165,78 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>泵型号/极限绝对压力</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>结构化复合值；option=泵型号文本，value=极限绝对压力数值</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>文本+数值</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>{option:泵型号文本,value:极限绝对压力}</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>{"option":"Edwards RV12","value":2.0}</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>★review§4.1B补</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>保持单字段的{option,value}契约，不拆成两个字段</t>
-        </is>
-      </c>
-      <c r="K39" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>MFC配置</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>各通道气体/量程/校准日期</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>数组</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>通道/气体/量程(sccm)/校准日期</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>CH1 Ar 0–200sccm</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>★review§4.1B补</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr"/>
-      <c r="K40" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>仪器PID</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>持久标识（预留）</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -7086,7 +7246,7 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>PIDINST/PID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -7094,19 +7254,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr"/>
@@ -7115,27 +7275,27 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>外场装置</t>
+          <t>仪器名称与类型</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>是否配光/电/等离子源</t>
+          <t>手段类型</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>多选+描述</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -7143,52 +7303,48 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>定量参数在实验§5</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>装置示意图/描述</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>照片/示意图+文字</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -7203,33 +7359,65 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>LabRAM HR</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -7239,12 +7427,12 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -7262,19 +7450,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr"/>
@@ -7288,22 +7476,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>仪器名称/类型</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>手段类型</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -7311,22 +7499,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr"/>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -7337,12 +7529,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>厂商(vendor)</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -7360,19 +7552,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr"/>
@@ -7386,22 +7578,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>型号(model)</t>
+          <t>关键固定配置</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>如激光波长/物镜/探测器</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -7409,19 +7601,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>532nm激光</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr"/>
@@ -7435,17 +7627,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>序列号(serial)</t>
+          <t>最近校准或维护日期</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>校准/维护日期</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -7458,225 +7650,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G49" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>PID(持久标识)</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>仪器持久标识（预留）</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
-      <c r="K50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>所在实验室/位置</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>物理位置</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>A305</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr"/>
-      <c r="K51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>关键固定配置</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>如激光波长/物镜/探测器</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>532nm激光</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr"/>
-      <c r="K52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>最近校准/维护</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>校准/维护日期</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J53" s="11" t="inlineStr"/>
-      <c r="K53" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7689,7 +7685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8661,28 +8657,94 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr"/>
-      <c r="B48" s="11" t="inlineStr"/>
-      <c r="C48" s="11" t="inlineStr"/>
-      <c r="D48" s="11" t="inlineStr"/>
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>§1–§4</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>按2026-07-24导师走查：温湿度与预检、目标形态升必填；删除粒子占位；批次引用升必填；前驱体与衬底处理改具名有序数组；衬底晶向、粗糙度、尺寸与倾角结构化</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>导师走查整改</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>§5–§6</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>11阶段收敛为预处理、反应条件、具名其他记录；温度程序、实测文件、多气体时序、时长、降温、实际外场与事件附件全部改为可校验结构</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>导师走查整改</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>实体</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Setup删除sccm参考值、加热区长度、泵、MFC和PID，坐标系固定，新增温度传感器；炉管材质与形状拆入具名对象；MaterialLot新增瓶身或包装标签附件</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>导师走查整改</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr"/>
+      <c r="B51" s="11" t="inlineStr"/>
+      <c r="C51" s="11" t="inlineStr"/>
+      <c r="D51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>硬必填核心(18项，含条件必填)</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>实验时间·合成方法·实验人·炉次编号·目标材料化学式·结构类型·组成明细(非本征)·装置·温区数·炉体方向·前驱体名称/化学式·前驱体用量(非气态)·衬底材料·阶段类型·设定温度程序·气体组分·流量·压力体系/工作压力(生长)</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>硬必填核心(30项，含条件必填)</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>v3.7新增环境温湿度、预检、目标形态、Setup测温传感器、前驱体与衬底批次、衬底化学式/晶向/粗糙度/尺寸放置、预处理操作；过程R0改为结构化温度程序、逐气体供气、绝对压力及时长循环</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>
@@ -8699,7 +8761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8906,15 +8968,100 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
+          <t>【问俊杰】实验前气体置换在组内统一采用“气路置换”“洗气”还是“吹扫”</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>待对齐(不阻塞结构实现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>【问俊杰】低压CVD的漏率是否逐炉记录，以及应归入装置校验还是实验过程</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>待对齐(本轮不记录漏率)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>【问俊杰】多气体比例的组内标准名称；系统当前由同时间段各气体流量派生</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>待对齐(不另存重复比例)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>【问俊杰】掺杂体系“基体/主体/本征材料”的最终角色术语与常见括号化学式示例</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>待对齐(结构已支持)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>【问俊杰】压片等前驱体处理方式的最小参数模板</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>待对齐(当前使用具名参数—值—单位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
           <t>已定/已改：一等实体字段表 · 记录单元=炉次+样品 · 掺杂→结构类型+components · 观察现象词表 · 降温参数 · R0条件化(相态判别) · AP/LP校验 · v3.4导师评审回改</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>见『v2→v3变更说明』</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1500,7 +1500,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>§2 实验装置与设计（每台装置只维护一次，实验中直接引用；壁型、温区数、炉体方向、管径和坐标系由所引用装置快照【只读投影】带出，不重录）</t>
+          <t>§2 实验装置与设计（装置固定配置由Setup快照只读带出；本炉的炉管使用履历由用户填写）</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -1824,22 +1824,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>炉管外径与壁厚</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>管径规格与壁厚（内径自动算）</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>{outer_diameter_mm, wall_thickness_mm}</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -1847,24 +1847,24 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>选择炉管材质与截面后必填</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>1″(25.4)，壁厚2</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>内径决定流速/分压</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>无/等离子/光/电</t>
+          <t>无/等离子体/光/电</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -2077,71 +2077,75 @@
       <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>炉管使用履历</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>当前炉管的累计重置次数，以及本次实验是最近一次重置后的第几次使用</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>使用履历对象</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>{reset_count, use_number_since_reset}</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>{reset_count: 1, use_number_since_reset: 7}</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>6/24决定·用户复核2026-07-24</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>每炉手填；清洗或更换炉管后重置次数加1，本次使用序号从1重新累计</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>§3 前驱体（用了哪些原料：主源、辅助剂等，可多个；每个一组）</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>前驱体标识（名称或化学式）</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>原料名称与化学式</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>受控+其他</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>MoO₃</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
-      <c r="K33" s="11" t="inlineStr"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -2151,22 +2155,22 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>化学标识（来自批次）</t>
+          <t>前驱体标识（来自批次）</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>从所选物料批次快照带出的 CAS 号和公共数据库标识</t>
+          <t>从所选物料批次快照带出的原料名称或化学式</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>CAS 或 InChI</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -2174,24 +2178,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>1313-27-5</t>
+          <t>MoO₃</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>由后端根据冻结物料批次快照重建，前端只读，不接受用户覆盖</t>
+          <t>选择物料批次后只读带出，不在炉次中建立第二套身份</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -2204,22 +2208,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>相态</t>
+          <t>化学标识（来自批次）</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
+          <t>从所选物料批次快照带出的 CAS 号和公共数据库标识</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>固/气/液</t>
+          <t>CAS 或 InChI</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -2227,24 +2231,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>固</t>
+          <t>1313-27-5</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
-        <is>
-          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>由后端根据冻结物料批次快照重建，前端只读，不接受用户覆盖</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr"/>
@@ -2257,22 +2261,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>外观描述</t>
+          <t>相态</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>使用时外观/性状——溯源时判断是否潮解、变质（湿度隐变量的可观察代理）</t>
+          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>白色粉末/白色晶粒/淡黄色粉末/结块或潮解/变色/其他</t>
+          <t>固/气/液</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -2280,24 +2284,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>推荐(固态源)</t>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>白色粉末</t>
+          <t>固</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>导师</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
+          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
@@ -2310,22 +2314,22 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>外观描述</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
+          <t>使用时外观/性状——溯源时判断是否潮解、变质（湿度隐变量的可观察代理）</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>白色粉末/白色晶粒/淡黄色粉末/结块或潮解/变色/其他</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -2333,24 +2337,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>推荐(固态源)</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>MoO₃-B202（锁 v1）</t>
+          <t>白色粉末</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>必须引用正确类别的物料批次并冻结版本，纯度、CAS和标签证据从快照带出</t>
+          <t>导师</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
@@ -2363,22 +2367,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>在反应里的角色</t>
+          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>主源/辅助剂/掺杂源/其他</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -2386,24 +2390,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>主源</t>
+          <t>MoO₃-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>界面中文(英文)</t>
+          <t>必须引用正确类别的物料批次并冻结版本，纯度、CAS和标签证据从快照带出</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -2416,54 +2420,50 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>投料量（只记投料，不记残余）</t>
+          <t>在反应里的角色</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>主源/辅助剂/掺杂源/其他</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>mg 或 µL（按相态）</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(非气态)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>主源</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
-        </is>
-      </c>
-      <c r="K39" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>界面中文(英文)</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -2473,50 +2473,54 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>用量</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>投料前处理（可多步，选了再展开参数）</t>
+          <t>投料量（只记投料，不记残余）</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>前驱体处理步骤数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>{type: 直接加载|熔融凝固|压片|旋涂|退火|研磨|其他, other_name?, parameters: 具名参数对象}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mg 或 µL（按相态）</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(非气态)</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>[{type: 旋涂, parameters: {speed_rpm: 3000, duration_s: 60}}]</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>有序可重复；已知方式使用具名参数和固定单位；压片及其他使用至少一项{name,value,unit}，不接受无单位自由文本</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="inlineStr"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -2526,27 +2530,27 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>舟或坩埚</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>盛装容器材质与尺寸</t>
+          <t>投料前处理（可多步，选了再展开参数）</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>前驱体处理步骤数组</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英舟|陶瓷(刚玉)舟|其他, material_other?, length_mm?, width_mm?, height_mm?, diameter_mm?}</t>
+          <t>{type: 直接加载|熔融凝固|压片|旋涂|退火|研磨|其他, other_name?, parameters: 具名参数对象}</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -2556,17 +2560,17 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>石英舟 90×15</t>
+          <t>[{type: 旋涂, parameters: {speed_rpm: 3000, duration_s: 60}}]</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>至少填写一个具名尺寸；material=其他时material_other必填</t>
+          <t>有序可重复；已知方式使用具名参数和固定单位；压片及其他使用至少一项{name,value,unit}，不接受无单位自由文本</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -2579,47 +2583,47 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>所在温区与源温</t>
+          <t>舟或坩埚</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>放第几温区、源温（若可设/可测）</t>
+          <t>本前驱体所用盛装容器的材质、尺寸和使用履历</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>温区温度对象</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, temperature_C}</t>
+          <t>{material: 石英舟|陶瓷(刚玉)舟|其他, material_other?, length_mm?, width_mm?, height_mm?, diameter_mm?, reset_count, use_number_since_reset}</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(非气态)</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>温区1，设定~620</t>
+          <t>石英舟 90×15；重置1次；本次为重置后第7次使用</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>按进气端编号</t>
+          <t>每个前驱体分别记录，避免多只舟共用一条履历；至少填写一个具名尺寸；其他材质须具名</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -2632,116 +2636,120 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
+          <t>前驱体位置</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>前驱体所在温区；仅在位置温度不同于温区设定程序或另有测量/估计时补充温度及依据</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>温区温度对象</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>{zone_index, temperature_C?, temperature_basis?: 实测值|估计}</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>推荐；填写距热电偶距离时必填</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>温区1；位置温度620；依据=估计</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>会议·用户复核2026-07-24</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>温区按进气端编号；温度程序仍是各温区设定值的权威记录；填写距热电偶距离时必须先选择所在温区</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>前驱体</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
           <t>距热电偶距离</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>距所在温区热电偶的水平距离</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr">
         <is>
           <t>上游为负、下游为正</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="K44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>§4 衬底（长在什么基底上，可多片）</t>
         </is>
       </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>衬底材料</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>衬底种类</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>SiO₂/Si</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr"/>
-      <c r="K45" s="11" t="inlineStr"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -2751,22 +2759,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>衬底材料（来自批次）</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>引用衬底批号并冻结当时版本、规格与证据</t>
+          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -2781,19 +2789,15 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Sapphire-B202（锁 v1）</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>必须引用衬底类别的不可变物料版本</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2804,22 +2808,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>衬底化学式</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>衬底材料的化学式；可从物料批次快照带出</t>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>标准化学式</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -2834,7 +2838,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Al₂O₃</t>
+          <t>Sapphire-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -2844,7 +2848,7 @@
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
+          <t>必须引用衬底类别的不可变物料版本</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr"/>
@@ -2857,12 +2861,12 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>晶面取向</t>
+          <t>衬底化学式（来自批次）</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>单晶衬底的晶面或晶轴取向</t>
+          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2872,7 +2876,7 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>例如 (100)、c面、a面</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -2887,7 +2891,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>(100)</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -2897,7 +2901,7 @@
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>不与化学式或偏转角合并</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr"/>
@@ -2910,27 +2914,27 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>偏转角</t>
+          <t>取向与抛光信息（来自批次）</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>晶面相对标称取向的偏转角</t>
+          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -2940,24 +2944,20 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>锁定前必须确认；无偏转填0，不得留空或揉入晶向字符串</t>
-        </is>
-      </c>
-      <c r="K49" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -2967,50 +2967,50 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度</t>
+          <t>晶面取向与抛光（来自批次）</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）</t>
+          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>例如 (100)、c面、a面</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>条件必填(批次有规格数值)</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>c面；单面抛</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>不与化学式或偏转角合并</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -3020,27 +3020,27 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>表面粗糙度指标与数值</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>表面粗糙度的指标类型和对应数值</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>{metric: Ra|RMS, value_nm}</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>{metric: RMS, value_nm: 0.5}</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>value_nm必须大于等于0；Ra和RMS不可省略</t>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr"/>
@@ -3073,50 +3073,54 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>尺寸与放置方式</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>几何尺寸、放置方式及条件角度</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(批次有规格数值)</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr"/>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3126,22 +3130,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -3149,24 +3153,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(偏切角&gt;0)</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr"/>
@@ -3179,12 +3183,12 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -3194,37 +3198,33 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>表面老化</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -3236,47 +3236,47 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>与时间间隔独立保存</t>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
@@ -3289,22 +3289,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>所在温区与热电偶距离</t>
+          <t>本片实际尺寸与放置方式</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>第几温区、距离(±)</t>
+          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>温区距离对象</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, distance_mm}</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -3312,122 +3312,162 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G56" s="15" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>预处理（有序步骤）</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>衬底预处理步骤数组</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>温区2，+15</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>上游为负、下游为正</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>预处理操作</t>
+          <t>暴露环境</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>抽气、气路置换等有序可重复的实验前操作</t>
+          <t>处理完成到放入实验装置期间所处环境</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>预处理操作数组</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
+          <t>空气/氮气/真空/其他</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -3435,24 +3475,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(预处理记录)</t>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
+          <t>空气</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
+          <t>与时间间隔独立保存</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr"/>
@@ -3460,148 +3500,112 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>所在温区与热电偶距离</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
-        </is>
-      </c>
-      <c r="G60" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
     </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>步·温度</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>实测温度文件与通道</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>温度时序文件引用</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G61" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H61" s="11" t="inlineStr">
-        <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
-        </is>
-      </c>
-      <c r="K61" s="11" t="inlineStr"/>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
-        </is>
-      </c>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -3611,7 +3615,7 @@
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr"/>
@@ -3619,42 +3623,42 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>压力体系与工作绝对压力</t>
+          <t>预处理操作</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>抽气、气路置换等有序可重复的实验前操作</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>条件必填(预处理记录)</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>常压；1.01325×10⁵ Pa</t>
+          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -3664,44 +3668,40 @@
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>填绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K63" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_value":true}</t>
-        </is>
-      </c>
+          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>时长与循环次数</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>反应条件持续时长及可选循环次数</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>{duration_min, cycle_count?}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>min·次</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45, cycle_count: 2}</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；cycle_count为可选正整数</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr"/>
@@ -3729,32 +3729,32 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
+          <t>℃ 随时间</t>
         </is>
       </c>
       <c r="G65" s="15" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
@@ -3782,42 +3782,42 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>实际外场程序</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与具名参数</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子|光|电, start_min, end_min, parameters: [{name, value, unit}]}</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>min·sccm</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子, start_min: 10, end_min: 40, parameters: [{name: power, value: 50, unit: W}]}]</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>field_type必须属于Setup能力；有记录时参数至少一项且不得使用混合单位单值</t>
+          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
@@ -3835,55 +3835,59 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>压力体系与工作绝对压力</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>条件必填(其他记录)</t>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>常压；1.01325×10⁵ Pa</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
-        </is>
-      </c>
-      <c r="K67" s="11" t="inlineStr"/>
+          <t>填绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -3893,117 +3897,153 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>其他记录说明</t>
+          <t>时长与循环次数</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>说明该记录的时间、操作和必要参数</t>
+          <t>反应条件持续时长及可选循环次数</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{duration_min, cycle_count?}</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>min·次</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>条件必填(其他记录)</t>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>第30分钟将源舟向下游移动10 mm</t>
+          <t>{duration_min: 45, cycle_count: 2}</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>必须持久化，绝不静默过滤</t>
+          <t>duration_min&gt;0；cycle_count为可选正整数</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
-      <c r="E69" s="8" t="n"/>
-      <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="n"/>
-      <c r="J69" s="8" t="n"/>
-      <c r="K69" s="8" t="n"/>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>步·降温</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>降温参数</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>降温参数对象</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>事件编号</t>
+          <t>实际外场程序</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>UUID</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>按参数</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440000</t>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
+          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
@@ -4011,27 +4051,27 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>其他记录名称</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>过程中发生的客观事件类型</t>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -4039,24 +4079,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(其他记录)</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>供气中断</t>
+          <t>临时移动源舟</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
+          <t>禁止仅保存“其他”</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4064,22 +4104,22 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>发生时刻</t>
+          <t>其他记录说明</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
+          <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>日期时间</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -4092,80 +4132,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(其他记录)</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24T10:28:00+08:00</t>
+          <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>相对时间可由t0算</t>
+          <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr"/>
     </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>是否导致实验终止</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>该事件是否导致本炉实验提前终止</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>复选</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="inlineStr">
-        <is>
-          <t>客观记录，不等同于成败判断</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="inlineStr"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -4175,22 +4179,22 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>终止原因</t>
+          <t>事件编号</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>事件导致实验终止时的客观原因</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划变更/其他</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -4198,24 +4202,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G74" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(导致实验终止)</t>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>设备报警</t>
+          <t>550e8400-e29b-41d4-a716-446655440000</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>正常计划结束不是异常终止原因</t>
+          <t>创建事件时生成，排序和编辑不得改变</t>
         </is>
       </c>
       <c r="K74" s="11" t="inlineStr"/>
@@ -4228,22 +4232,22 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>过程中发生的客观事件类型</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -4251,14 +4255,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G75" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(终止原因=其他)</t>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -4268,7 +4272,7 @@
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr"/>
@@ -4281,17 +4285,17 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>处理措施</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>事件发生后采取的操作</t>
+          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>日期时间</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -4304,14 +4308,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G76" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>更换气瓶后恢复供气</t>
+          <t>2026-07-24T10:28:00+08:00</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -4321,7 +4325,7 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>相对时间可由t0算</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4334,22 +4338,22 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>事件附件</t>
+          <t>是否导致实验终止</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>与本条事件直接关联的图片、日志或其他文件</t>
+          <t>该事件是否导致本炉实验提前终止</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用数组</t>
+          <t>复选</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>FileAsset UUID列表</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4357,14 +4361,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G77" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -4374,52 +4378,88 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
+          <t>客观记录，不等同于成败判断</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="8" t="n"/>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>终止原因</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>事件导致实验终止时的客观原因</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>设备报警/人工停止/计划变更/其他</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(导致实验终止)</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>设备报警</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>正常计划结束不是异常终止原因</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>表征方法与仪器</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>表征手段 + 引用仪器</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4427,24 +4467,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G79" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G79" s="16" t="inlineStr">
+        <is>
+          <t>选填；终止原因=其他时必填</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J79" s="13" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
@@ -4452,22 +4492,22 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>处理措施</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>事件发生后采取的操作</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -4480,24 +4520,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G80" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>532nm / 1mW / 100×</t>
+          <t>更换气瓶后恢复供气</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>随仪器导出</t>
+          <t>与事件说明独立保存</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr"/>
@@ -4505,27 +4545,27 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -4533,101 +4573,69 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G81" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J81" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
+        </is>
+      </c>
       <c r="K81" s="11" t="inlineStr"/>
     </row>
-    <row r="82">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>实测产物</t>
-        </is>
-      </c>
-      <c r="B82" s="11" t="inlineStr">
-        <is>
-          <t>观察到的现象</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>下拉+多选</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
-        </is>
-      </c>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H82" s="11" t="inlineStr">
-        <is>
-          <t>不连续覆盖</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J82" s="13" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
-        </is>
-      </c>
-      <c r="K82" s="11" t="inlineStr"/>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="8" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>表征方法</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -4635,24 +4643,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J83" s="13" t="inlineStr">
         <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr"/>
@@ -4660,22 +4668,22 @@
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -4685,54 +4693,50 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="G84" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
-        </is>
-      </c>
-      <c r="K84" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>随仪器导出</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -4742,34 +4746,26 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G85" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J85" s="11" t="inlineStr">
-        <is>
-          <t>量化口径仍须随表征条件记录</t>
-        </is>
-      </c>
-      <c r="K85" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"le":100}</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr"/>
+      <c r="K85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -4779,27 +4775,27 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="16" t="inlineStr">
@@ -4809,20 +4805,20 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J86" s="11" t="inlineStr"/>
-      <c r="K86" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J86" s="13" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -4832,17 +4828,17 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -4852,7 +4848,7 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr">
@@ -4862,20 +4858,20 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J87" s="11" t="inlineStr"/>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J87" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -4885,27 +4881,27 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>结构化指标数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>每条:{metric_code,value,unit}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>按指标</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G88" s="16" t="inlineStr">
@@ -4915,105 +4911,149 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J88" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="8" t="n"/>
-      <c r="J89" s="8" t="n"/>
-      <c r="K89" s="8" t="n"/>
+          <t>{"ge":0,"type":"integer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>覆盖率</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>明确视场或统计区域内材料面积占比</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"le":100}</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G90" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>μm</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>复审/科学契约审查</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
-      <c r="K90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>成核密度</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>指定统计区域内单位面积成核点数量</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -5028,132 +5068,104 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G91" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>复审/科学契约审查</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr"/>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>结构化指标数组</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
-        </is>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>按指标</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J92" s="11" t="inlineStr"/>
-      <c r="K92" s="11" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>等离子气氛与工作气压</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>溅射气体与气压</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>下拉+数值</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>Ar / Ar+N₂…</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H93" s="11" t="inlineStr">
-        <is>
-          <t>Ar，0.5 Pa</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J93" s="11" t="inlineStr"/>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J92" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="8" t="n"/>
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -5163,27 +5175,27 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -5193,7 +5205,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -5202,11 +5214,7 @@
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr"/>
-      <c r="K94" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -5216,12 +5224,12 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>沉积速率</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>速率（QCM 等）</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -5236,7 +5244,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>nm/s</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -5246,7 +5254,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -5261,17 +5269,225 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>功率与偏压</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>DC/RF 功率、基底偏压</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>DC/RF</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>W·V</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>RF 150W；偏压 -50V</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>等离子体气氛与工作气压</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>溅射气体与气压</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>下拉+数值</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Ar / Ar+N₂…</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>Ar，0.5 Pa</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr"/>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>预溅射与挡板时序</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>沉积速率</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>速率（QCM 等）</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>nm/s</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A61:K61"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A33:K33"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A89:K89"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="A45:K45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5283,7 +5499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5954,7 +6170,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>仅用于固体或液体化学前驱体的来料粒径；气瓶与衬底不适用</t>
+        </is>
+      </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
           <t>{"gt":0}</t>
@@ -6009,7 +6229,7 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>外观=性状</t>
+          <t>外观=性状；气瓶不使用粉末/箔/靶等物料形态</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr"/>
@@ -6332,22 +6552,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光</t>
+          <t>▸衬底·晶向与抛光信息</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -6355,22 +6575,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr"/>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
+        </is>
+      </c>
       <c r="K22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
@@ -6381,37 +6605,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·尺寸规格</t>
+          <t>▸衬底·晶向与抛光</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>出厂几何</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(有规格数值)</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -6419,8 +6643,16 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>实验引用批次后只读带出</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>{"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -6430,12 +6662,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸衬底·偏切信息</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -6445,7 +6677,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -6455,22 +6687,22 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>条件必填(气瓶)</t>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>分工：base纯度填数值%、此处填等级标签(Fable三轮B4)</t>
+          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr"/>
@@ -6483,127 +6715,175 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·气瓶编号</t>
+          <t>▸衬底·偏切角</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>钢瓶追溯号</t>
+          <t>实际晶面相对标称晶面的偏切角</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(有规格数值)</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24用户走查</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>大于0时必须同时填写substrate_miscut_direction</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>▸衬底·偏切方向</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>偏切角所指的晶轴或晶向</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>GC-Ar-07</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(偏切角&gt;0)</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>c面向a轴</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24用户走查</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>装置编号</t>
+          <t>▸衬底·标称表面粗糙度</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>供应商或批次规格中的标称粗糙度</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>{availability: not_provided}</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
+        </is>
+      </c>
       <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>▸衬底·来料尺寸规格</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -6613,56 +6893,60 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr"/>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>不替代每次实验的本片实际尺寸</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>▸气瓶·纯度等级</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6N/5N/4N/工业级</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -6670,24 +6954,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5N</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>对标 v1 setup_version_snapshot</t>
+          <t>base纯度的数值百分比为权威值；这里只保留供应商标签</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -6695,27 +6979,27 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>品牌与型号</t>
+          <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>设备品牌型号</t>
+          <t>钢瓶追溯号</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -6723,72 +7007,40 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>GC-Ar-07</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>壁型</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>热壁/冷壁</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>下拉</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>热壁/冷壁</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>热壁</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
-      <c r="K31" s="11" t="inlineStr"/>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -6798,17 +7050,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>装置编号</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -6818,7 +7070,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -6828,20 +7080,16 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>review§4.1B</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr"/>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+      <c r="K32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -6851,27 +7099,27 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>温度传感器与不确定度</t>
+          <t>装置名称</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>装置各温区的测温传感器、测量不确定度及其来源</t>
+          <t>人读名</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>{sensor_name, sensor_type, zone_index, uncertainty_C, uncertainty_source: 仪器|校准|重复性|估计}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -6881,19 +7129,15 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_name: 炉温热电偶1, sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1, uncertainty_source: 校准}]</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>随Setup版本冻结，实验选择装置后自动带出</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
       <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
@@ -6904,22 +7148,22 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -6934,15 +7178,19 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>对标 v1 setup_version_snapshot</t>
+        </is>
+      </c>
       <c r="K34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
@@ -6953,22 +7201,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>品牌与型号</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>设备品牌型号</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -6983,19 +7231,15 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>合肥科晶 OTF-1200X</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
@@ -7006,27 +7250,27 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>炉管外径与壁厚</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>管规格</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>{outer_diameter_mm, wall_thickness_mm}</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -7036,19 +7280,15 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>1″，壁厚2</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>内径由外径与壁厚派生显示</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
@@ -7059,50 +7299,50 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -7112,37 +7352,37 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>温度传感器与不确定度</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光、电或等离子体能力</t>
+          <t>装置各温区的测温传感器、测量不确定度及其来源</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子</t>
+          <t>{sensor_name, sensor_type, zone_index, uncertainty_C, uncertainty_source: 仪器|校准|重复性|估计}</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>[{sensor_name: 炉温热电偶1, sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1, uncertainty_source: 校准}]</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -7152,7 +7392,7 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+          <t>随Setup版本冻结，实验选择装置后自动带出</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -7165,22 +7405,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图及文字说明</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -7188,14 +7428,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -7206,96 +7446,136 @@
       <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr"/>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>炉管材质与截面</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>炉管材料与截面</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>管材质形状对象</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>{material: 石英, shape: 圆形}</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>选择炉管材质与截面后必填</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr"/>
+          <t>会议·用户复核2026-07-24</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
+        </is>
+      </c>
       <c r="K41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>仪器名称与类型</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>手段类型</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -7303,48 +7583,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+        </is>
+      </c>
       <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>装置具备的光、电或等离子体能力</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无/光/电/等离子体</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -7352,48 +7636,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+        </is>
+      </c>
       <c r="K43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -7408,65 +7696,33 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr"/>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>序列号</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>设备序列号</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr"/>
-      <c r="K45" s="11" t="inlineStr"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -7476,12 +7732,12 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -7499,26 +7755,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -7529,22 +7781,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -7552,22 +7804,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据</t>
+        </is>
+      </c>
       <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
@@ -7578,22 +7834,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>随仪器固定的参数（可变测试条件在实验§7填）</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>如激光波长/物镜/探测器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -7601,19 +7857,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>532nm激光</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr"/>
@@ -7627,17 +7883,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>最近校准或维护日期</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>校准/维护日期</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -7650,29 +7906,282 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>序列号</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>设备序列号</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>仪器持久标识</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>所在实验室与位置</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>物理位置</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>A305</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>最近校准或维护日期</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>校准/维护日期</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A31:K31"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7685,7 +8194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8723,28 +9232,160 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr"/>
-      <c r="B51" s="11" t="inlineStr"/>
-      <c r="C51" s="11" t="inlineStr"/>
-      <c r="D51" s="11" t="inlineStr"/>
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>v3.8</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>§1–§5</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>用户走查修复：炉管和各舟履历改为每炉手填；炉管尺寸按圆/方/矩形条件展开；前驱体源温改为可选位置温度及依据；外场按等离子体/光/电展开明确参数</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>用户走查修复</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
+          <t>v3.8</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>§4/实体</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>衬底稳定规格归MaterialLot：晶向抛光、偏切角与方向、氧化层及标称粗糙度由批次冻结带出；本片尺寸、放置、预处理和位置留在炉次；气瓶等级改为供应商原始标签选填</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>用户走查修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>v3.8</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>术语/表征</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>装置与实际外场统一显示“等离子体”；体相空间群改用内置230项检索；“表征方法”与仪器引用分开，固定配置只记录稳定硬件能力</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>用户走查修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>v3.9</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>§1/§4/实体</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>按会议逐字稿删除悬浮粒子浓度；粗糙度允许明确记录供应商未提供；旧批次缺稳定字段时禁止在实验回填；区分来料尺寸与本次实际切片尺寸</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>v3.10</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>§3/§4/实体</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>补齐温区距离参照、条件不适用后端约束与旧等离子别名；粒径/形态按物料类别展开；晶向抛光和偏切以有规格、未提供、不适用三态记录，禁止用伪值或0代替未知</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-25终审收口</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>v3.11</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>§6/实体</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>事件具体说明始终可选填写、终止原因=其他时升级为必填；仪器字段改称“适用表征方法”；补明热电偶距离与前驱体温区、炉管截面与尺寸的联动必填规则</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-25逐字稿与语义终审</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr"/>
+      <c r="B57" s="11" t="inlineStr"/>
+      <c r="C57" s="11" t="inlineStr"/>
+      <c r="D57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(30项，含条件必填)</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>v3.7新增环境温湿度、预检、目标形态、Setup测温传感器、前驱体与衬底批次、衬底化学式/晶向/粗糙度/尺寸放置、预处理操作；过程R0改为结构化温度程序、逐气体供气、绝对压力及时长循环</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -747,17 +747,17 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>本次用的气相沉积方法；顶层选择器，决定是否启用§8 PVD模块</t>
+          <t>本系统当前记录的顶层制备方法；压力、等离子体、金属有机源和盐辅助均由对应实验事实单独表达</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>CVD/APCVD/LPCVD/PECVD/MOCVD/盐辅助CVD/PVD-磁控溅射/PVD-热蒸发/PLD/其他</t>
+          <t>CVD/APCVD/LPCVD/PECVD/MOCVD/盐辅助CVD/PVD-磁控溅射/PVD-热蒸发/PLD</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>常压CVD(APCVD)</t>
+          <t>CVD</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>v3新增</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>★v3新增；可挂CHMO本体ID</t>
+          <t>2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>新记录固定为CVD；历史APCVD/LPCVD/PECVD/MOCVD/盐辅助CVD值继续兼容读取</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>规范显示串；复合体系须与组成明细一致、以组成明细为准（可自动生成）</t>
+          <t>本征、掺杂和合金体系的目标化学式；异质结构由材料层或区域自动生成显示式</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>逐组分结构化（复合体系的权威数据源）</t>
+          <t>按结构类型记录主体与掺杂元素、合金混合位点，或异质结构的材料层与区域</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>每条:化学式/角色(主体材料·掺杂剂·合金组分·上层·下层·横向域)/浓度(at%)/层序(整数)</t>
+          <t>每条:化学式/角色(主体材料·掺杂剂·合金组分·材料层·上层·下层·横向域)/名义含量或占位比例(%)/层序(整数)/体相空间群(1-230)</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>{WS2,上层,层序2};{MoS2,下层,层序1}</t>
+          <t>{MoS2,材料层,层序1,空间群194};{WS2,材料层,层序2,空间群194}</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>★v3.2b升为权威源+条件必填；数量拆浓度/层序；掺杂浓度已知时须0&lt;at%&lt;100，允许一个或多个掺杂剂，不强制“掺杂剂:主体材料”字符串；垂直结构下层层序须早于上层；杜绝退回字符串（复审N2）</t>
+          <t>复审·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>掺杂记录一条主体材料和一个或多个掺杂元素；合金组分只表示混合占位元素及比例；垂直结构按从衬底向上顺序记录材料层，横向结构逐区域记录；上层/下层只用于历史兼容</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>晶体对称性：International Tables 空间群号（1–230）</t>
+          <t>非异质结构目标材料的晶体对称性：International Tables 空间群号（1–230）；异质结构改在每层或区域填写</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1335,9 +1335,9 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>★v3：从『层群/点群/多型』改回体相空间群；手性/扭转角/堆垛→备注</t>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>本征、掺杂、合金和其他结构可选；垂直或横向异质结构在组成明细逐层或逐区域填写</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr"/>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>温度传感器与不确定度</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>所引用装置版本中各温区的测温传感器与不确定度，只读带出</t>
+          <t>所引用装置版本中每个温区的传感器类型和温度测量误差，只读带出</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>{sensor_name, sensor_type, zone_index, uncertainty_C, uncertainty_source: 仪器|校准|重复性|估计}</t>
+          <t>{sensor_type, zone_index, uncertainty_C；旧记录可含sensor_name与uncertainty_source}</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>K型热电偶，温区1，±1℃</t>
+          <t>温区1：K型热电偶，温度测量误差±1℃</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>实验中不重复填写，由Setup版本快照冻结</t>
+          <t>实验中不重复填写，由Setup版本快照冻结；旧名称和误差来源只读兼容，新表单不再要求</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>化学标识（来自批次）</t>
+          <t>CAS号（来自批次）</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>从所选物料批次快照带出的 CAS 号和公共数据库标识</t>
+          <t>从所选物料批次快照带出的 CAS 号</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>CAS 或 InChI</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -2443,9 +2443,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>衬底化学式（来自批次）</t>
+          <t>本次样片标记</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>标准化学式</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Al₂O₃</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
+          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr"/>
@@ -2914,22 +2914,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光信息（来自批次）</t>
+          <t>衬底化学式（来自批次）</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
+          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr"/>
@@ -2967,22 +2967,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>晶面取向与抛光（来自批次）</t>
+          <t>取向与抛光信息（来自批次）</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
+          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>例如 (100)、c面、a面</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -2990,24 +2990,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(批次有规格数值)</t>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>c面；单面抛</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>不与化学式或偏转角合并</t>
+          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr"/>
@@ -3020,22 +3020,22 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>偏切信息（来自批次）</t>
+          <t>晶面取向与抛光（来自批次）</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
+          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>例如 (100)、c面、a面</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -3043,24 +3043,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(批次有规格数值)</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>c面；单面抛</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
+          <t>不与化学式或偏转角合并</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr"/>
@@ -3073,37 +3073,37 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>偏切角（相对标称晶面，来自批次）</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(批次有规格数值)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -3113,14 +3113,10 @@
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3130,17 +3126,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>偏切方向（来自批次）</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -3150,30 +3146,34 @@
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>条件必填(偏切角&gt;0)</t>
+          <t>条件必填(批次有规格数值)</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴偏0.2°</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
-        </is>
-      </c>
-      <c r="K53" s="11" t="inlineStr"/>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -3183,50 +3183,50 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度（来自批次）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>条件必填(偏切角&gt;0)</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr"/>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24用户走查</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -3236,22 +3236,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>标称表面粗糙度（来自批次）</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -3259,27 +3259,27 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr">
-        <is>
-          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
-        </is>
-      </c>
-      <c r="K55" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -3289,27 +3289,27 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>本片实际尺寸与放置方式</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
@@ -3342,37 +3342,37 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>本片实际尺寸与放置方式</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
+          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr"/>
@@ -3395,54 +3395,50 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>预处理（有序步骤）</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -3452,27 +3448,27 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
@@ -3482,20 +3478,24 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>与时间间隔独立保存</t>
-        </is>
-      </c>
-      <c r="K59" s="11" t="inlineStr"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -3505,120 +3505,120 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
+          <t>暴露环境</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>处理完成到放入实验装置期间所处环境</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>空气/氮气/真空/其他</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>空气</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>与时间间隔独立保存</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
           <t>所在温区与热电偶距离</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>第几温区、距离(±)</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>温区距离对象</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>{zone_index, distance_mm}</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G60" s="15" t="inlineStr">
+      <c r="G61" s="15" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="H61" s="11" t="inlineStr">
         <is>
           <t>温区2，+15</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr">
         <is>
           <t>上游为负、下游为正</t>
         </is>
       </c>
-      <c r="K60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="K61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
         </is>
       </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="8" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>记录类型</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>下拉</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>预处理/反应条件/其他记录</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>反应条件</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -3628,22 +3628,22 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>预处理操作</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>抽气、气路置换等有序可重复的实验前操作</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>预处理操作数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -3651,14 +3651,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G63" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(预处理记录)</t>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr"/>
@@ -3676,42 +3676,42 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>预处理操作</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>抽气、气路置换等有序可重复的实验前操作</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>条件必填(预处理记录)</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr"/>
@@ -3734,37 +3734,37 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min·℃</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
@@ -3782,42 +3782,42 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
@@ -3835,32 +3835,32 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>压力体系与工作绝对压力</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>常压；1.01325×10⁵ Pa</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -3880,44 +3880,40 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>填绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K67" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_value":true}</t>
-        </is>
-      </c>
+          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>时长与循环次数</t>
+          <t>压力体系与工作绝对压力</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>反应条件持续时长及可选循环次数</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>{duration_min, cycle_count?}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>min·次</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -3927,7 +3923,7 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45, cycle_count: 2}</t>
+          <t>常压；1.01325×10⁵ Pa</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -3937,60 +3933,64 @@
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；cycle_count为可选正整数</t>
-        </is>
-      </c>
-      <c r="K68" s="11" t="inlineStr"/>
+          <t>填绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
-        </is>
-      </c>
-      <c r="G69" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
@@ -3998,42 +3998,42 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>实际外场程序</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
-        </is>
-      </c>
-      <c r="G70" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
@@ -4051,52 +4051,52 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>实际外场程序</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(其他记录)</t>
+          <t>按参数</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4109,120 +4109,120 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
+          <t>其他记录名称</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(其他记录)</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>临时移动源舟</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>禁止仅保存“其他”</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
           <t>其他记录说明</t>
         </is>
       </c>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>自由</t>
         </is>
       </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="14" t="inlineStr">
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>条件必填(其他记录)</t>
         </is>
       </c>
-      <c r="H72" s="11" t="inlineStr">
+      <c r="H73" s="11" t="inlineStr">
         <is>
           <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J72" s="11" t="inlineStr">
+      <c r="J73" s="11" t="inlineStr">
         <is>
           <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
-      <c r="K72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="K73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
         </is>
       </c>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="8" t="n"/>
-      <c r="J73" s="8" t="n"/>
-      <c r="K73" s="8" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t>事件编号</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="F74" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H74" s="11" t="inlineStr">
-        <is>
-          <t>550e8400-e29b-41d4-a716-446655440000</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24整改</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr">
-        <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
-        </is>
-      </c>
-      <c r="K74" s="11" t="inlineStr"/>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="8" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="8" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -4232,22 +4232,22 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>事件编号</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>过程中发生的客观事件类型</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>供气中断</t>
+          <t>550e8400-e29b-41d4-a716-446655440000</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
+          <t>创建事件时生成，排序和编辑不得改变</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr"/>
@@ -4285,22 +4285,22 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>发生时刻</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
+          <t>过程中发生的客观事件类型</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>日期时间</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24T10:28:00+08:00</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>相对时间可由t0算</t>
+          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4338,22 +4338,22 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>是否导致实验终止</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>该事件是否导致本炉实验提前终止</t>
+          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>复选</t>
+          <t>日期时间</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>2026-07-24T10:28:00+08:00</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>客观记录，不等同于成败判断</t>
+          <t>相对时间可由t0算</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
@@ -4391,22 +4391,22 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>终止原因</t>
+          <t>是否导致实验终止</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>事件导致实验终止时的客观原因</t>
+          <t>该事件是否导致本炉实验提前终止</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>复选</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划变更/其他</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -4414,14 +4414,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(导致实验终止)</t>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>设备报警</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>正常计划结束不是异常终止原因</t>
+          <t>客观记录，不等同于成败判断</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr"/>
@@ -4444,22 +4444,22 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>终止原因</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>事件导致实验终止时的客观原因</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设备报警/人工停止/计划变更/其他</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4467,14 +4467,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G79" s="16" t="inlineStr">
-        <is>
-          <t>选填；终止原因=其他时必填</t>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(导致实验终止)</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>设备报警</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+          <t>正常计划结束不是异常终止原因</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>处理措施</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>事件发生后采取的操作</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="G80" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选填；终止原因=其他时必填</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>更换气瓶后恢复供气</t>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr"/>
@@ -4550,120 +4550,120 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
+          <t>处理措施</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>事件发生后采取的操作</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>更换气瓶后恢复供气</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>与事件说明独立保存</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
           <t>事件附件</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>FileAsset引用数组</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>FileAsset UUID列表</t>
         </is>
       </c>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="16" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H81" s="11" t="inlineStr">
+      <c r="H82" s="11" t="inlineStr">
         <is>
           <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>2026-07-24导师走查</t>
         </is>
       </c>
-      <c r="J81" s="11" t="inlineStr">
+      <c r="J82" s="11" t="inlineStr">
         <is>
           <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
-      <c r="K81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="K82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
         </is>
       </c>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-      <c r="J82" s="8" t="n"/>
-      <c r="K82" s="8" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>表征方法</t>
-        </is>
-      </c>
-      <c r="C83" s="11" t="inlineStr">
-        <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
-        </is>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J83" s="13" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
-        </is>
-      </c>
-      <c r="K83" s="11" t="inlineStr"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -4673,22 +4673,22 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>表征方法</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -4696,14 +4696,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G84" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -4711,9 +4711,9 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J84" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
+      <c r="J84" s="13" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr"/>
@@ -4726,17 +4726,17 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -4756,41 +4756,45 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J85" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
+        </is>
+      </c>
       <c r="K85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -4798,26 +4802,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G86" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J86" s="13" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4828,22 +4828,22 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J87" s="13" t="inlineStr">
         <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr"/>
@@ -4881,17 +4881,17 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G88" s="16" t="inlineStr">
@@ -4911,24 +4911,20 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J88" s="11" t="inlineStr">
-        <is>
-          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
-        </is>
-      </c>
-      <c r="K88" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J88" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
@@ -4938,12 +4934,12 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -4958,7 +4954,7 @@
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G89" s="16" t="inlineStr">
@@ -4968,7 +4964,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -4978,12 +4974,12 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>量化口径仍须随表征条件记录</t>
+          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0,"le":100}</t>
+          <t>{"ge":0,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -4995,12 +4991,12 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
@@ -5015,7 +5011,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G90" s="16" t="inlineStr">
@@ -5025,7 +5021,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -5033,10 +5029,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J90" s="11" t="inlineStr"/>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"le":100}</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>μm</t>
         </is>
       </c>
       <c r="G91" s="16" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -5089,7 +5089,7 @@
       <c r="J91" s="11" t="inlineStr"/>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -5101,120 +5101,124 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
+          <t>成核密度</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>指定统计区域内单位面积成核点数量</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
           <t>关键谱学指标</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="D93" s="11" t="inlineStr">
         <is>
           <t>结构化指标数组</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr">
+      <c r="E93" s="11" t="inlineStr">
         <is>
           <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
-      <c r="F92" s="11" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>按指标</t>
         </is>
       </c>
-      <c r="G92" s="16" t="inlineStr">
+      <c r="G93" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H92" s="11" t="inlineStr">
+      <c r="H93" s="11" t="inlineStr">
         <is>
           <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr">
+      <c r="I93" s="11" t="inlineStr">
         <is>
           <t>复审/导师</t>
         </is>
       </c>
-      <c r="J92" s="13" t="inlineStr">
+      <c r="J93" s="13" t="inlineStr">
         <is>
           <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
         </is>
       </c>
-      <c r="K92" s="11" t="inlineStr">
+      <c r="K93" s="11" t="inlineStr">
         <is>
           <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
         </is>
       </c>
-      <c r="B93" s="8" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
-      <c r="E93" s="8" t="n"/>
-      <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="8" t="n"/>
-      <c r="J93" s="8" t="n"/>
-      <c r="K93" s="8" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t>靶材（批次）</t>
-        </is>
-      </c>
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t>靶材化学身份 + 批次</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>批次库</t>
-        </is>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H94" s="11" t="inlineStr">
-        <is>
-          <t>MoS₂ 靶-T01</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J94" s="11" t="inlineStr"/>
-      <c r="K94" s="11" t="inlineStr"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -5224,27 +5228,27 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -5254,7 +5258,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -5263,11 +5267,7 @@
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr"/>
-      <c r="K95" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K95" s="11" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -5316,7 +5316,11 @@
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr"/>
-      <c r="K96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -5326,27 +5330,27 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -5356,7 +5360,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -5365,11 +5369,7 @@
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr"/>
-      <c r="K97" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
+      <c r="K97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
@@ -5379,27 +5379,27 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -5420,7 +5420,7 @@
       <c r="J98" s="11" t="inlineStr"/>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"gt":0,"require_value":true}</t>
         </is>
       </c>
     </row>
@@ -5432,12 +5432,12 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>沉积速率</t>
+          <t>预溅射与挡板时序</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>速率（QCM 等）</t>
+          <t>预溅射时长、挡板开合时序</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>nm/s</t>
+          <t>min·s</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>预溅 5 min</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -5477,16 +5477,69 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>沉积速率</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>速率（QCM 等）</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>nm/s</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr"/>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A82:K82"/>
-    <mergeCell ref="A73:K73"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="A94:K94"/>
     <mergeCell ref="A45:K45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5499,7 +5552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5720,12 +5773,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>物质名称</t>
+          <t>物质名称（中文）</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>化学身份：名称</t>
+          <t>物料标签或CoA上的中文名称；与化学式、CAS号分别记录</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -5758,7 +5811,11 @@
           <t>review§4.1A</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>不用化学式代替名称；英文标签可按课题组常用中文名填写</t>
+        </is>
+      </c>
       <c r="K6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
@@ -5867,22 +5924,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>公共数据库标识</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>可选唯一标识</t>
+          <t>商业批次：厂商</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他(可扩展)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -5890,14 +5947,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>阿拉丁</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -5905,11 +5962,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>可填写 InChIKey 或 PubChem CID；没有可靠值时留空</t>
-        </is>
-      </c>
+      <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5920,22 +5973,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>供应商货号</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>商业批次：厂商</t>
+          <t>商业批次：产品号</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他(可扩展)</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -5943,14 +5996,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>阿拉丁</t>
+          <t>M112056</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -5958,7 +6011,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>供应商产品规格编号，标签上常写作 Cat. No.；同一货号可有多个生产批号</t>
+        </is>
+      </c>
       <c r="K10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
@@ -5969,12 +6026,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>供应商货号</t>
+          <t>生产批号</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>商业批次：产品号</t>
+          <t>商业批次：生产批号（同名不同批的区分键）</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -5992,14 +6049,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>M112056</t>
+          <t>B202405</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -6009,7 +6066,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>供应商产品规格编号，标签上常写作 Cat. No.；同一货号可有多个生产批号</t>
+          <t>GMP法定术语『批号』；标签上常写作 Lot No. 或 Batch No.</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr"/>
@@ -6022,37 +6079,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>生产批号</t>
+          <t>纯度</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>商业批次：生产批号（同名不同批的区分键）</t>
+          <t>仅存质量百分数；N值由质量百分数派生显示，不作为独立存储值</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>质量百分数（N值仅派生显示）</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(化学品或气瓶)</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>B202405</t>
+          <t>99.995（派生显示4N5）</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -6062,10 +6119,14 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>GMP法定术语『批号』；标签上常写作 Lot No. 或 Batch No.</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr"/>
+          <t>原始证书中的N值或其他纯度表述保留在CoA/附件说明中</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"le":100}</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -6075,37 +6136,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>纯度</t>
+          <t>形态与性状</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>仅存质量百分数；N值由质量百分数派生显示，不作为独立存储值</t>
+          <t>试剂外观</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>质量百分数（N值仅派生显示）</t>
+          <t>粉末/颗粒/块/箔/靶/其他</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(化学品或气瓶)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>99.995（派生显示4N5）</t>
+          <t>粉末</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -6115,14 +6176,10 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>原始证书中的N值或其他纯度表述保留在CoA/附件说明中</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"le":100}</t>
-        </is>
-      </c>
+          <t>外观=性状；气瓶不使用粉末/箔/靶等物料形态</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -6137,7 +6194,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>中位径（影响挥发/成核）</t>
+          <t>供应商或CoA报告的来料中位粒径；影响挥发和成核</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -6147,7 +6204,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>x50严谨；目数可接受</t>
+          <t>供应商或CoA报告的D50</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -6157,7 +6214,7 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(粉末或颗粒)</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -6172,7 +6229,7 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>仅用于固体或液体化学前驱体的来料粒径；气瓶与衬底不适用</t>
+          <t>仅在来料形态为粉末或颗粒且供应商/CoA有报告时填写；无报告留空，不用目数或猜测值代替</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
@@ -6189,22 +6246,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>形态与性状</t>
+          <t>开封日期</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>试剂外观</t>
+          <t>影响吸潮/氧化</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>粉末/颗粒/块/箔/靶/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -6219,7 +6276,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>粉末</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -6227,11 +6284,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>外观=性状；气瓶不使用粉末/箔/靶等物料形态</t>
-        </is>
-      </c>
+      <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
@@ -6242,22 +6295,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>开封日期</t>
+          <t>存储方式</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>影响吸潮/氧化</t>
+          <t>存放条件</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -6272,7 +6325,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>干燥器</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -6280,7 +6333,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>desiccator=干燥器</t>
+        </is>
+      </c>
       <c r="K16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
@@ -6291,22 +6348,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>存储方式</t>
+          <t>证书附件(CoA)</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>存放条件</t>
+          <t>质检证书</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>FileAsset引用</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
+          <t>{file_asset_id, sha256}</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -6321,7 +6378,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>干燥器</t>
+          <t>coa.pdf</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -6329,11 +6386,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>desiccator=干燥器</t>
-        </is>
-      </c>
+      <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
@@ -6344,12 +6397,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>证书附件(CoA)</t>
+          <t>瓶身或包装标签附件</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>质检证书</t>
+          <t>试剂瓶身、气瓶或衬底包装标签的原始照片，用于追溯批号与规格</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -6367,22 +6420,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>coa.pdf</t>
+          <t>bottle-label.jpg</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>与CoA分开；同一物料版本至少上传一次并可预览、下载</t>
+        </is>
+      </c>
       <c r="K18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
@@ -6393,22 +6450,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>瓶身或包装标签附件</t>
+          <t>▸衬底·材料</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>试剂瓶身、气瓶或衬底包装标签的原始照片，用于追溯批号与规格</t>
+          <t>子类(批次类别=衬底)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256}</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -6416,24 +6473,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>bottle-label.jpg</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>与CoA分开；同一物料版本至少上传一次并可预览、下载</t>
+          <t>与§4衬底材料词表一致</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr"/>
@@ -6446,37 +6503,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·材料</t>
+          <t>▸衬底·氧化层厚度</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=衬底)</t>
+          <t>仅SiO₂/Si</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>条件必填(衬底)</t>
+          <t>条件必填(SiO₂/Si)</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -6484,12 +6541,12 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>与§4衬底材料词表一致</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -6499,50 +6556,50 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·氧化层厚度</t>
+          <t>▸衬底·晶向与抛光信息</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>仅SiO₂/Si</t>
+          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>条件必填(SiO₂/Si)</t>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -6552,22 +6609,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光信息</t>
+          <t>▸衬底·晶向与抛光</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -6577,25 +6634,29 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>条件必填(衬底)</t>
+          <t>条件必填(有规格数值)</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr"/>
+          <t>实验引用批次后只读带出</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>{"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -6605,22 +6666,22 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光</t>
+          <t>▸衬底·偏切信息</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -6630,29 +6691,25 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>条件必填(有规格数值)</t>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>实验引用批次后只读带出</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>{"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -6662,50 +6719,54 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切信息</t>
+          <t>▸衬底·偏切角</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
+          <t>实际晶面相对标称晶面的偏切角</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>条件必填(衬底)</t>
+          <t>条件必填(有规格数值)</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr"/>
+          <t>大于0时必须同时填写substrate_miscut_direction</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -6715,17 +6776,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切角</t>
+          <t>▸衬底·偏切方向</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角</t>
+          <t>偏切角所指的晶轴或晶向</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -6735,17 +6796,17 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>条件必填(有规格数值)</t>
+          <t>条件必填(偏切角&gt;0)</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>c面向a轴</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -6755,14 +6816,10 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>大于0时必须同时填写substrate_miscut_direction</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -6772,47 +6829,47 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切方向</t>
+          <t>▸衬底·标称表面粗糙度</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向</t>
+          <t>供应商或批次规格中的标称粗糙度</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>条件必填(偏切角&gt;0)</t>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴</t>
+          <t>{availability: not_provided}</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr"/>
@@ -6825,47 +6882,47 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·标称表面粗糙度</t>
+          <t>▸衬底·来料尺寸规格</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度</t>
+          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>{availability: not_provided}</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
+          <t>不替代每次实验的本片实际尺寸</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -6878,27 +6935,27 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·来料尺寸规格</t>
+          <t>▸气瓶·纯度等级</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>6N/5N/4N/工业级</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
@@ -6908,7 +6965,7 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>5N</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -6918,7 +6975,7 @@
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>不替代每次实验的本片实际尺寸</t>
+          <t>base纯度的数值百分比为权威值；这里只保留供应商标签</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -6931,22 +6988,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>钢瓶追溯号</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -6961,7 +7018,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>GC-Ar-07</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -6969,78 +7026,74 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>base纯度的数值百分比为权威值；这里只保留供应商标签</t>
-        </is>
-      </c>
+      <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr"/>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>MaterialLot</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>▸气瓶·气瓶编号</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>钢瓶追溯号</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>装置名称</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>人读名</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>GC-Ar-07</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr"/>
-      <c r="K30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>1号双温区管式炉</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -7050,17 +7103,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>装置编号</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -7080,15 +7133,19 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>对标 v1 setup_version_snapshot</t>
+        </is>
+      </c>
       <c r="K32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
@@ -7099,22 +7156,22 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>品牌与型号</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>设备品牌型号</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -7122,14 +7179,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>合肥科晶 OTF-1200X</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -7148,17 +7205,17 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>实验室装置编号</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>课题组在实验室内唯一识别这台装置的固定编号</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -7178,17 +7235,17 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
+          <t>review§4.1B·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>对标 v1 setup_version_snapshot</t>
+          <t>登记后作为装置身份使用；版本更新不应改成另一台装置的编号</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -7201,22 +7258,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>品牌与型号</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>设备品牌型号</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -7231,12 +7288,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr"/>
@@ -7250,46 +7307,50 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr"/>
-      <c r="K36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -7299,27 +7360,27 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>装置每个温区的传感器类型和用户可直接理解的温度测量误差</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{sensor_type, zone_index, uncertainty_C；旧记录可含sensor_name与uncertainty_source}</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -7329,20 +7390,20 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[{sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1}]</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>温区数决定卡片数量；不让用户另起传感器名称，不要求填写难以理解的误差来源；旧字段只读兼容</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -7352,27 +7413,27 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>温度传感器与不确定度</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>装置各温区的测温传感器、测量不确定度及其来源</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>{sensor_name, sensor_type, zone_index, uncertainty_C, uncertainty_source: 仪器|校准|重复性|估计}</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -7382,19 +7443,15 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_name: 炉温热电偶1, sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1, uncertainty_source: 校准}]</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>随Setup版本冻结，实验选择装置后自动带出</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
@@ -7405,22 +7462,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -7428,22 +7485,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+        </is>
+      </c>
       <c r="K39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
@@ -7454,47 +7515,47 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>选择炉管材质与截面后必填</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr"/>
@@ -7507,47 +7568,47 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>选择炉管材质与截面后必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -7560,22 +7621,22 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>装置具备的光、电或等离子体能力</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>无/光/电/等离子体</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -7583,14 +7644,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -7600,7 +7661,7 @@
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -7613,22 +7674,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光、电或等离子体能力</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子体</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -7636,93 +7697,89 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>装置示意图与描述</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>装置照片或示意图及文字说明</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset引用+自由</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>{file_asset_id, sha256, note}</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>setup.png</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr"/>
-      <c r="K44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
         </is>
       </c>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>仪器编号</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>唯一编号</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>RAMAN-1</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -7732,22 +7789,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -7762,15 +7819,19 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据</t>
+        </is>
+      </c>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -7781,22 +7842,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -7804,26 +7865,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
@@ -7834,12 +7891,12 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -7864,7 +7921,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -7883,12 +7940,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -7906,14 +7963,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -7932,12 +7989,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -7967,10 +8024,14 @@
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
       <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
@@ -7981,12 +8042,12 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -8011,19 +8072,15 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
@@ -8034,22 +8091,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>关键固定配置</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -8064,15 +8121,19 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
       <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
@@ -8083,22 +8144,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>最近校准或维护日期</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>校准/维护日期</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -8113,7 +8174,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -8121,67 +8182,14 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
-        <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
-        </is>
-      </c>
+      <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>最近校准或维护日期</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>校准/维护日期</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr"/>
-      <c r="K54" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8194,7 +8202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9364,28 +9372,50 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="inlineStr"/>
-      <c r="B57" s="11" t="inlineStr"/>
-      <c r="C57" s="11" t="inlineStr"/>
-      <c r="D57" s="11" t="inlineStr"/>
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>v3.12</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>§1–§5/实体</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>制备终版整改：新记录固定CVD顶层方法；目标产物按掺杂、合金、材料层和区域填写；Setup逐温区只填传感器类型与温度测量误差；前驱体角色与样片标记必填；压力类别和值成对；反应删除伪循环派生</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-27终版整改</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr"/>
+      <c r="B58" s="11" t="inlineStr"/>
+      <c r="C58" s="11" t="inlineStr"/>
+      <c r="D58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(30项，含条件必填)</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>v3.7新增环境温湿度、预检、目标形态、Setup测温传感器、前驱体与衬底批次、衬底化学式/晶向/粗糙度/尺寸放置、预处理操作；过程R0改为结构化温度程序、逐气体供气、绝对压力及时长循环</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>v3.7新增环境温湿度、预检、目标形态、Setup测温传感器、前驱体与衬底批次、衬底化学式/晶向/粗糙度/尺寸放置、预处理操作；过程R0改为结构化温度程序、逐气体供气、绝对压力及反应时长</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -1121,7 +1121,7 @@
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>★R0；复合体系权威在『组成明细』；录入使用普通数字；允许常见圆括号、组成分组与结晶水点号</t>
+          <t>★R0；复合体系权威在『组成明细』；系统静默归一化粘贴的下标数字；允许常见圆括号、组成分组与结晶水点号</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>按结构类型记录主体与掺杂元素、合金混合位点，或异质结构的材料层与区域</t>
+          <t>按结构类型记录掺杂元素、合金混合位点，或异质结构的材料层与区域；掺杂主体直接取上方主体材料化学式</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>每条:化学式/角色(主体材料·掺杂剂·合金组分·材料层·上层·下层·横向域)/名义含量或占位比例(%)/层序(整数)/体相空间群(1-230)</t>
+          <t>掺杂=掺杂元素+名义含量；合金=混合占位元素+占位比例；垂直异质结=材料层+层序+体相空间群；横向异质结=材料区域+体相空间群；其他=组成材料+适用属性；机器角色(主体材料·掺杂剂·合金组分·材料层·上层·下层·横向域)</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>掺杂记录一条主体材料和一个或多个掺杂元素；合金组分只表示混合占位元素及比例；垂直结构按从衬底向上顺序记录材料层，横向结构逐区域记录；上层/下层只用于历史兼容</t>
+          <t>掺杂界面只填一个或多个掺杂元素，保存时由主体材料化学式自动加入主体记录；合金组分只表示混合占位元素及比例；垂直结构按从衬底向上顺序记录材料层，横向结构逐区域记录；上层/下层只用于历史兼容</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr"/>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>目标层数</t>
+          <t>目标原子层数</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>期望层数</t>
+          <t>单一材料体系期望的原子层数；异质结构按材料层或区域记录，不显示本全局字段</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>体相空间群</t>
+          <t>目标体相空间群</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1320,9 +1320,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>本征、掺杂、合金和其他结构可选；垂直或横向异质结构在组成明细逐层或逐区域填写</t>
+          <t>本征、掺杂、合金和其他结构推荐填写；垂直或横向异质结构在组成明细逐层或逐区域填写；常见体相候选仅作快速录入，不自动判定物相</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>样品形态</t>
+          <t>目标形态</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -8202,7 +8202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9394,28 +9394,50 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr"/>
-      <c r="B58" s="11" t="inlineStr"/>
-      <c r="C58" s="11" t="inlineStr"/>
-      <c r="D58" s="11" t="inlineStr"/>
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>v3.13</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>§1b</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>目标产物复核：化学式示例按结构类型变化；删除“普通数字”用户文案；掺杂区只显示掺杂元素；空间群按化学式给出经核对的常见体相候选并保留230项搜索；异质结构逐层或逐区域填写空间群</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr"/>
+      <c r="B59" s="11" t="inlineStr"/>
+      <c r="C59" s="11" t="inlineStr"/>
+      <c r="D59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(30项，含条件必填)</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>v3.7新增环境温湿度、预检、目标形态、Setup测温传感器、前驱体与衬底批次、衬底化学式/晶向/粗糙度/尺寸放置、预处理操作；过程R0改为结构化温度程序、逐气体供气、绝对压力及反应时长</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>装置（引用）</t>
+          <t>实验装置</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>当前炉管的累计重置次数，以及本次实验是最近一次重置后的第几次使用</t>
+          <t>当前炉管的累计清洗或更换次数，以及本次实验是最近一次清洗或更换后的第几次使用</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>每炉手填；清洗或更换炉管后重置次数加1，本次使用序号从1重新累计</t>
+          <t>每炉手填；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -7258,46 +7258,50 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr"/>
-      <c r="K35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -7307,27 +7311,27 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>装置每个温区的传感器类型和用户可直接理解的温度测量误差</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{sensor_type: k_thermocouple|s_thermocouple|r_thermocouple|b_thermocouple|infrared_pyrometer|other, sensor_type_other?, zone_index, uncertainty_C；旧记录可含sensor_name与uncertainty_source}</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -7337,20 +7341,20 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[{sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1}]</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr"/>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>温区数决定卡片数量；不让用户另起传感器名称，不要求填写难以理解的误差来源；旧字段只读兼容</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -7360,27 +7364,27 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>装置每个温区的传感器类型和用户可直接理解的温度测量误差</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type, zone_index, uncertainty_C；旧记录可含sensor_name与uncertainty_source}</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -7390,19 +7394,15 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1}]</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>温区数决定卡片数量；不让用户另起传感器名称，不要求填写难以理解的误差来源；旧字段只读兼容</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
@@ -7413,22 +7413,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -7443,15 +7443,19 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+        </is>
+      </c>
       <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
@@ -7462,47 +7466,47 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr"/>
@@ -7515,47 +7519,47 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>选择炉管材质与截面后必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr"/>
@@ -7644,9 +7648,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>品牌与型号</t>
+          <t>装置来源</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>设备品牌与型号</t>
+          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>商业设备/实验室自制/改造设备</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -1594,22 +1594,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>商业设备</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr"/>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>由所引用Setup版本只读带出</t>
+        </is>
+      </c>
       <c r="K22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1620,22 +1624,22 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>制造商或品牌</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>热壁炉还是冷壁炉（影响生长机理）</t>
+          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -1643,22 +1647,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>合肥科晶</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr"/>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>由所引用Setup版本只读带出</t>
+        </is>
+      </c>
       <c r="K23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1669,50 +1677,50 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>独立控温的温区数量</t>
+          <t>制造商给出的设备型号</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>1/2/3…</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>OTF-1200X</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>由所引用Setup版本只读带出</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -1722,12 +1730,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>炉管水平还是竖直</t>
+          <t>热壁炉还是冷壁炉（影响生长机理）</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1737,7 +1745,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -1745,19 +1753,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
@@ -1771,50 +1779,50 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面形状</t>
+          <t>独立控温的温区数量</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>1/2/3…</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>材质与形状独立保存，禁止从斜杠或分隔符猜测</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -1824,49 +1832,45 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>炉管水平还是竖直</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>选择炉管材质与截面后必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr"/>
       <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1877,22 +1881,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>坐标系</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>本装置位置参照；全局固定、不可编辑</t>
+          <t>炉管材料与截面形状</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -1900,24 +1904,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>材质与形状独立保存，禁止从斜杠或分隔符猜测</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -1930,47 +1934,47 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>所引用装置版本中每个温区的传感器类型和温度测量误差，只读带出</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type, zone_index, uncertainty_C；旧记录可含sensor_name与uncertainty_source}</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>必填(装置登记)</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>选择炉管材质与截面后必填</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>温区1：K型热电偶，温度测量误差±1℃</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>实验中不重复填写，由Setup版本快照冻结；旧名称和误差来源只读兼容，新表单不再要求</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -1983,22 +1987,22 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>坐标系</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>所引用装置是否具备等离子体、光或电场能力；本炉实际使用情况在反应条件中记录</t>
+          <t>本装置位置参照；全局固定、不可编辑</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>无/等离子体/光/电</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -2006,24 +2010,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>只读投影；不得当成本炉实际使用记录</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -2036,45 +2040,49 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图 + 文字批注</t>
+          <t>所引用装置版本中每个温区的传感器类别和资料标明的标称测温精度，只读带出</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>附件+自由</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{sensor_type, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>必填(装置登记)</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>setup.png + 卧式双温区</t>
+          <t>温区1：热电偶，标称测温精度±1℃</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>实验中不重复填写，由Setup版本快照冻结</t>
+        </is>
+      </c>
       <c r="K31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2085,97 +2093,129 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>炉管使用履历</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>当前炉管的累计清洗或更换次数，以及本次实验是最近一次清洗或更换后的第几次使用</t>
+          <t>所引用装置是否具备等离子体、光或电场能力；本炉实际使用情况在反应条件中记录</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>使用履历对象</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>{reset_count, use_number_since_reset}</t>
+          <t>无/等离子体/光/电</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>次</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>{reset_count: 1, use_number_since_reset: 7}</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>6/24决定·用户复核2026-07-24</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>每炉手填；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
+          <t>只读投影；不得当成本炉实际使用记录</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>§3 前驱体（用了哪些原料：主源、辅助剂等，可多个；每个一组）</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>装置示意图与描述</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>装置照片或示意图 + 文字批注</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>附件+自由</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>setup.png + 卧式双温区</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>前驱体</t>
+          <t>设备</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>前驱体标识（来自批次）</t>
+          <t>炉管使用履历</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>从所选物料批次快照带出的原料名称或化学式</t>
+          <t>当前炉管的累计清洗或更换次数，以及本次实验是最近一次清洗或更换后的第几次使用</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>使用履历对象</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>{reset_count, use_number_since_reset}</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>次</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -2185,73 +2225,37 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>MoO₃</t>
+          <t>{reset_count: 1, use_number_since_reset: 7}</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>6/24决定·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>选择物料批次后只读带出，不在炉次中建立第二套身份</t>
+          <t>每炉手填；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>CAS号（来自批次）</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>从所选物料批次快照带出的 CAS 号</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>CAS</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>1313-27-5</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24整改</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>由后端根据冻结物料批次快照重建，前端只读，不接受用户覆盖</t>
-        </is>
-      </c>
-      <c r="K35" s="11" t="inlineStr"/>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>§3 前驱体（用了哪些原料：主源、辅助剂等，可多个；每个一组）</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -2261,22 +2265,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>相态</t>
+          <t>前驱体标识（来自批次）</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
+          <t>从所选物料批次快照带出的原料名称或化学式</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>固/气/液</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -2291,17 +2295,17 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>固</t>
+          <t>MoO₃</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>选择物料批次后只读带出，不在炉次中建立第二套身份</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
@@ -2314,22 +2318,22 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>外观描述</t>
+          <t>CAS号（来自批次）</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>使用时外观/性状——溯源时判断是否潮解、变质（湿度隐变量的可观察代理）</t>
+          <t>从所选物料批次快照带出的 CAS 号</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>白色粉末/白色晶粒/淡黄色粉末/结块或潮解/变色/其他</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -2337,24 +2341,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>推荐(固态源)</t>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>白色粉末</t>
+          <t>1313-27-5</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>导师</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>由后端根据冻结物料批次快照重建，前端只读，不接受用户覆盖</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
@@ -2367,22 +2371,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>相态</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
+          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>固/气/液</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -2397,17 +2401,17 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>MoO₃-B202（锁 v1）</t>
+          <t>固</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>必须引用正确类别的物料批次并冻结版本，纯度、CAS和标签证据从快照带出</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -2420,22 +2424,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>外观描述</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>在反应里的角色</t>
+          <t>使用时外观/性状——溯源时判断是否潮解、变质（湿度隐变量的可观察代理）</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>主源/辅助剂/掺杂源/其他</t>
+          <t>白色粉末/白色晶粒/淡黄色粉末/结块或潮解/变色/其他</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -2443,24 +2447,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>推荐(固态源)</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>主源</t>
+          <t>白色粉末</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>界面中文(英文)</t>
+          <t>导师</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr"/>
@@ -2473,54 +2477,50 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>投料量（只记投料，不记残余）</t>
+          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>mg 或 µL（按相态）</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(非气态)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>MoO₃-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
-        <is>
-          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>必须引用正确类别的物料批次并冻结版本，纯度、CAS和标签证据从快照带出</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -2530,22 +2530,22 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>投料前处理（可多步，选了再展开参数）</t>
+          <t>在反应里的角色</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>前驱体处理步骤数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>{type: 直接加载|熔融凝固|压片|旋涂|退火|研磨|其他, other_name?, parameters: 具名参数对象}</t>
+          <t>主源/辅助剂/掺杂源/其他</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -2553,24 +2553,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>[{type: 旋涂, parameters: {speed_rpm: 3000, duration_s: 60}}]</t>
+          <t>主源</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>有序可重复；已知方式使用具名参数和固定单位；压片及其他使用至少一项{name,value,unit}，不接受无单位自由文本</t>
+          <t>界面中文(英文)</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -2583,27 +2583,27 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>舟或坩埚</t>
+          <t>用量</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>本前驱体所用盛装容器的材质、尺寸和使用履历</t>
+          <t>投料量（只记投料，不记残余）</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英舟|陶瓷(刚玉)舟|其他, material_other?, length_mm?, width_mm?, height_mm?, diameter_mm?, reset_count, use_number_since_reset}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mg 或 µL（按相态）</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -2613,20 +2613,24 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>石英舟 90×15；重置1次；本次为重置后第7次使用</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>复审·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>每个前驱体分别记录，避免多只舟共用一条履历；至少填写一个具名尺寸；其他材质须具名</t>
-        </is>
-      </c>
-      <c r="K42" s="11" t="inlineStr"/>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -2636,47 +2640,47 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>前驱体位置</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>前驱体所在温区；仅在位置温度不同于温区设定程序或另有测量/估计时补充温度及依据</t>
+          <t>投料前处理（可多步，选了再展开参数）</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>温区温度对象</t>
+          <t>前驱体处理步骤数组</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, temperature_C?, temperature_basis?: 实测值|估计}</t>
+          <t>{type: 直接加载|熔融凝固|压片|旋涂|退火|研磨|其他, other_name?, parameters: 具名参数对象}</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>推荐；填写距热电偶距离时必填</t>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>温区1；位置温度620；依据=估计</t>
+          <t>[{type: 旋涂, parameters: {speed_rpm: 3000, duration_s: 60}}]</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>温区按进气端编号；温度程序仍是各温区设定值的权威记录；填写距热电偶距离时必须先选择所在温区</t>
+          <t>有序可重复；已知方式使用具名参数和固定单位；压片及其他使用至少一项{name,value,unit}，不接受无单位自由文本</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
@@ -2689,22 +2693,22 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>距热电偶距离</t>
+          <t>舟或坩埚</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>距所在温区热电偶的水平距离</t>
+          <t>本前驱体所用盛装容器的材质、尺寸和使用履历</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>具名尺寸对象</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{material: 石英舟|陶瓷(刚玉)舟|其他, material_other?, length_mm?, width_mm?, height_mm?, diameter_mm?, reset_count, use_number_since_reset}</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -2712,84 +2716,120 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(非气态)</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>石英舟 90×15；重置1次；本次为重置后第7次使用</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>上游为负、下游为正</t>
+          <t>每个前驱体分别记录，避免多只舟共用一条履历；至少填写一个具名尺寸；其他材质须具名</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>§4 衬底（长在什么基底上，可多片）</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>前驱体</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>前驱体位置</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>前驱体所在温区；仅在位置温度不同于温区设定程序或另有测量/估计时补充温度及依据</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>温区温度对象</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>{zone_index, temperature_C?, temperature_basis?: 实测值|估计}</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>推荐；填写距热电偶距离时必填</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>温区1；位置温度620；依据=估计</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>会议·用户复核2026-07-24</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>温区按进气端编号；温度程序仍是各温区设定值的权威记录；填写距热电偶距离时必须先选择所在温区</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>衬底</t>
+          <t>前驱体</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>衬底材料（来自批次）</t>
+          <t>距热电偶距离</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>距所在温区热电偶的水平距离</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -2797,61 +2837,29 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>上游为负、下游为正</t>
+        </is>
+      </c>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>物料批次（引用）</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>引用衬底批号并冻结当时版本、规格与证据</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>实体版本引用</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>{entity_id, version, snapshot}</t>
-        </is>
-      </c>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>Sapphire-B202（锁 v1）</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr">
-        <is>
-          <t>必须引用衬底类别的不可变物料版本</t>
-        </is>
-      </c>
-      <c r="K47" s="11" t="inlineStr"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>§4 衬底（长在什么基底上，可多片）</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -2861,22 +2869,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>本次样片标记</t>
+          <t>衬底材料（来自批次）</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
+          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -2891,19 +2899,15 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2914,22 +2918,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>衬底化学式（来自批次）</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>标准化学式</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -2944,7 +2948,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Al₂O₃</t>
+          <t>Sapphire-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -2954,7 +2958,7 @@
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
+          <t>必须引用衬底类别的不可变物料版本</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr"/>
@@ -2967,22 +2971,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光信息（来自批次）</t>
+          <t>本次样片标记</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
+          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -2997,17 +3001,17 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
+          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr"/>
@@ -3020,12 +3024,12 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>晶面取向与抛光（来自批次）</t>
+          <t>衬底化学式（来自批次）</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
+          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -3035,7 +3039,7 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>例如 (100)、c面、a面</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -3043,14 +3047,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(批次有规格数值)</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>c面；单面抛</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -3060,7 +3064,7 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>不与化学式或偏转角合并</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr"/>
@@ -3073,12 +3077,12 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>偏切信息（来自批次）</t>
+          <t>取向与抛光信息（来自批次）</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
+          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -3103,7 +3107,7 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -3113,7 +3117,7 @@
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
+          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr"/>
@@ -3126,27 +3130,27 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>偏切角（相对标称晶面，来自批次）</t>
+          <t>晶面取向与抛光（来自批次）</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
+          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>例如 (100)、c面、a面</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -3156,24 +3160,20 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>c面；单面抛</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
-        </is>
-      </c>
-      <c r="K53" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>不与化学式或偏转角合并</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>偏切方向（来自批次）</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -3206,24 +3206,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(偏切角&gt;0)</t>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴偏0.2°</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度（来自批次）</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -3251,33 +3251,37 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>条件必填(批次有规格数值)</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr"/>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"lt":90}</t>
         </is>
       </c>
     </row>
@@ -3289,47 +3293,47 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>标称表面粗糙度（来自批次）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(偏切角&gt;0)</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
@@ -3342,50 +3346,50 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>本片实际尺寸与放置方式</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr">
-        <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
-        </is>
-      </c>
-      <c r="K57" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -3395,37 +3399,37 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -3435,7 +3439,7 @@
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -3448,54 +3452,50 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>本片实际尺寸与放置方式</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G59" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K59" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -3505,22 +3505,22 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>预处理（有序步骤）</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -3528,24 +3528,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>与时间间隔独立保存</t>
+          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -3558,213 +3558,217 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>所在温区与热电偶距离</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>第几温区、距离(±)</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>温区距离对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, distance_mm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G61" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>温区2，+15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>上游为负、下游为正</t>
-        </is>
-      </c>
-      <c r="K61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>暴露环境</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>处理完成到放入实验装置期间所处环境</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>空气/氮气/真空/其他</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>空气</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>与时间间隔独立保存</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>所在温区与热电偶距离</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr"/>
     </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>预处理操作</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>抽气、气路置换等有序可重复的实验前操作</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>预处理操作数组</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(预处理记录)</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="8" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -3774,7 +3778,7 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
@@ -3782,42 +3786,42 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>预处理操作</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>抽气、气路置换等有序可重复的实验前操作</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G66" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(预处理记录)</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -3827,7 +3831,7 @@
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
@@ -3835,32 +3839,32 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -3870,7 +3874,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -3880,7 +3884,7 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr"/>
@@ -3888,42 +3892,42 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>压力体系与工作绝对压力</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>常压；1.01325×10⁵ Pa</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -3933,44 +3937,40 @@
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>填绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K68" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -3980,17 +3980,17 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
@@ -3998,42 +3998,42 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>压力体系与工作绝对压力</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
-        </is>
-      </c>
-      <c r="G70" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>常压；1.01325×10⁵ Pa</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -4043,60 +4043,64 @@
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
-        </is>
-      </c>
-      <c r="K70" s="11" t="inlineStr"/>
+          <t>填绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>实际外场程序</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
-        </is>
-      </c>
-      <c r="G71" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4104,52 +4108,52 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(其他记录)</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr"/>
@@ -4157,97 +4161,133 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
+          <t>步·外场</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>实际外场程序</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>实际外场数组</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>按参数</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
           <t>过程步</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>其他记录说明</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>说明该记录的时间、操作和必要参数</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="14" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>其他记录名称</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
         <is>
           <t>条件必填(其他记录)</t>
         </is>
       </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>第30分钟将源舟向下游移动10 mm</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr">
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>临时移动源舟</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J73" s="11" t="inlineStr">
-        <is>
-          <t>必须持久化，绝不静默过滤</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="n"/>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
-      <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="8" t="n"/>
-      <c r="J74" s="8" t="n"/>
-      <c r="K74" s="8" t="n"/>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>禁止仅保存“其他”</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>事件编号</t>
+          <t>其他记录说明</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+          <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>UUID</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -4255,14 +4295,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(其他记录)</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440000</t>
+          <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -4272,63 +4312,27 @@
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
+          <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr"/>
     </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>过程中发生的客观事件类型</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
-        </is>
-      </c>
-      <c r="F76" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H76" s="11" t="inlineStr">
-        <is>
-          <t>供气中断</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J76" s="11" t="inlineStr">
-        <is>
-          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
-        </is>
-      </c>
-      <c r="K76" s="11" t="inlineStr"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="8" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -4338,22 +4342,22 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>发生时刻</t>
+          <t>事件编号</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>日期时间</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4368,17 +4372,17 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24T10:28:00+08:00</t>
+          <t>550e8400-e29b-41d4-a716-446655440000</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>相对时间可由t0算</t>
+          <t>创建事件时生成，排序和编辑不得改变</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
@@ -4391,22 +4395,22 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>是否导致实验终止</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>该事件是否导致本炉实验提前终止</t>
+          <t>过程中发生的客观事件类型</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>复选</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -4421,7 +4425,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -4431,7 +4435,7 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>客观记录，不等同于成败判断</t>
+          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr"/>
@@ -4444,22 +4448,22 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>终止原因</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>事件导致实验终止时的客观原因</t>
+          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>日期时间</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划变更/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4467,14 +4471,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G79" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(导致实验终止)</t>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>设备报警</t>
+          <t>2026-07-24T10:28:00+08:00</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>正常计划结束不是异常终止原因</t>
+          <t>相对时间可由t0算</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
@@ -4497,22 +4501,22 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>是否导致实验终止</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>该事件是否导致本炉实验提前终止</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>复选</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -4520,14 +4524,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G80" s="16" t="inlineStr">
-        <is>
-          <t>选填；终止原因=其他时必填</t>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -4537,7 +4541,7 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+          <t>客观记录，不等同于成败判断</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr"/>
@@ -4550,22 +4554,22 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>处理措施</t>
+          <t>终止原因</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>事件发生后采取的操作</t>
+          <t>事件导致实验终止时的客观原因</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设备报警/人工停止/计划变更/其他</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -4573,14 +4577,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G81" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(导致实验终止)</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>更换气瓶后恢复供气</t>
+          <t>设备报警</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -4590,7 +4594,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>正常计划结束不是异常终止原因</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -4603,22 +4607,22 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>事件附件</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>与本条事件直接关联的图片、日志或其他文件</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用数组</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>FileAsset UUID列表</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -4628,67 +4632,103 @@
       </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
+          <t>选填；终止原因=其他时必填</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>处理措施</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>事件发生后采取的操作</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H82" s="11" t="inlineStr">
-        <is>
-          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>更换气瓶后恢复供气</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>2026-07-24导师走查</t>
         </is>
       </c>
-      <c r="J82" s="11" t="inlineStr">
-        <is>
-          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
-        </is>
-      </c>
-      <c r="K82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
-      <c r="J83" s="8" t="n"/>
-      <c r="K83" s="8" t="n"/>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>与事件说明独立保存</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>表征方法</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -4696,80 +4736,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J84" s="13" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr"/>
     </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>测试条件</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr">
-        <is>
-          <t>该表征的测试参数</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>文本/自由</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G85" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H85" s="11" t="inlineStr">
-        <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J85" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
-        </is>
-      </c>
-      <c r="K85" s="11" t="inlineStr"/>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -4779,22 +4783,22 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>表征方法</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -4802,48 +4806,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G86" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J86" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J86" s="13" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+        </is>
+      </c>
       <c r="K86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -4851,24 +4859,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G87" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G87" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J87" s="13" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr"/>
@@ -4876,22 +4884,22 @@
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -4904,26 +4912,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G88" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J88" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr"/>
       <c r="K88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4934,27 +4938,27 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G89" s="16" t="inlineStr">
@@ -4964,24 +4968,20 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J89" s="11" t="inlineStr">
-        <is>
-          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
-        </is>
-      </c>
-      <c r="K89" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J89" s="13" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G90" s="16" t="inlineStr">
@@ -5021,24 +5021,20 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J90" s="11" t="inlineStr">
-        <is>
-          <t>量化口径仍须随表征条件记录</t>
-        </is>
-      </c>
-      <c r="K90" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"le":100}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J90" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -5048,12 +5044,12 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -5068,7 +5064,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G91" s="16" t="inlineStr">
@@ -5078,7 +5074,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -5086,10 +5082,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J91" s="11" t="inlineStr"/>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
+        </is>
+      </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -5101,12 +5101,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G92" s="16" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -5139,10 +5139,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J92" s="11" t="inlineStr"/>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"ge":0,"le":100}</t>
         </is>
       </c>
     </row>
@@ -5154,27 +5158,27 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>结构化指标数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>每条:{metric_code,value,unit}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>按指标</t>
+          <t>μm</t>
         </is>
       </c>
       <c r="G93" s="16" t="inlineStr">
@@ -5184,143 +5188,147 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J93" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
-        </is>
-      </c>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr"/>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="8" t="n"/>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="8" t="n"/>
-      <c r="J94" s="8" t="n"/>
-      <c r="K94" s="8" t="n"/>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>成核密度</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>指定统计区域内单位面积成核点数量</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr"/>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>结构化指标数组</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>按指标</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J95" s="11" t="inlineStr"/>
-      <c r="K95" s="11" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B96" s="11" t="inlineStr">
-        <is>
-          <t>靶基距</t>
-        </is>
-      </c>
-      <c r="C96" s="11" t="inlineStr">
-        <is>
-          <t>靶到衬底距离</t>
-        </is>
-      </c>
-      <c r="D96" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G96" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H96" s="11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J96" s="11" t="inlineStr"/>
-      <c r="K96" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J95" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -5330,27 +5338,27 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -5360,7 +5368,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -5379,27 +5387,27 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -5409,7 +5417,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -5420,7 +5428,7 @@
       <c r="J98" s="11" t="inlineStr"/>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0,"require_value":true}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -5432,12 +5440,12 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -5447,12 +5455,12 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -5462,7 +5470,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -5471,11 +5479,7 @@
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -5485,27 +5489,27 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>沉积速率</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>速率（QCM 等）</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>nm/s</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -5515,7 +5519,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -5526,21 +5530,127 @@
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr">
         <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>预溅射与挡板时序</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr"/>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>沉积速率</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>速率（QCM 等）</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>nm/s</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
           <t>{"gt":0}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A74:K74"/>
-    <mergeCell ref="A83:K83"/>
-    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="A35:K35"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A96:K96"/>
+    <mergeCell ref="A64:K64"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A94:K94"/>
-    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="A76:K76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5552,7 +5662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7156,22 +7266,22 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>品牌与型号</t>
+          <t>装置来源</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>设备品牌型号</t>
+          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>商业设备/实验室自制/改造设备</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -7179,19 +7289,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶 OTF-1200X</t>
+          <t>商业设备</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr"/>
@@ -7205,12 +7315,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>实验室装置编号</t>
+          <t>制造商或品牌</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>课题组在实验室内唯一识别这台装置的固定编号</t>
+          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -7228,26 +7338,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>合肥科晶</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B·2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
-          <t>登记后作为装置身份使用；版本更新不应改成另一台装置的编号</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
@@ -7258,17 +7364,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>制造商给出的设备型号</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -7278,30 +7384,26 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>OTF-1200X</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr"/>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+      <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -7311,27 +7413,27 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>实验室装置编号（资产编号）</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>装置每个温区的传感器类型和用户可直接理解的温度测量误差</t>
+          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type: k_thermocouple|s_thermocouple|r_thermocouple|b_thermocouple|infrared_pyrometer|other, sensor_type_other?, zone_index, uncertainty_C；旧记录可含sensor_name与uncertainty_source}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -7341,17 +7443,17 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_type: K型热电偶, zone_index: 1, uncertainty_C: 1}]</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>review§4.1B·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>温区数决定卡片数量；不让用户另起传感器名称，不要求填写难以理解的误差来源；旧字段只读兼容</t>
+          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
@@ -7364,27 +7466,27 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -7394,7 +7496,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -7403,7 +7505,11 @@
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -7413,27 +7519,27 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -7443,17 +7549,17 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -7466,49 +7572,45 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>必填；按炉管截面填写</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
@@ -7519,22 +7621,22 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -7542,24 +7644,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr"/>
@@ -7572,47 +7674,47 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -7625,22 +7727,22 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光、电或等离子体能力</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子体</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -7648,24 +7750,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -7678,22 +7780,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图及文字说明</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -7701,65 +7803,105 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+        </is>
+      </c>
       <c r="K43" s="11" t="inlineStr"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>外场能力</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>装置具备的光、电或等离子体能力</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>多选</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>无/光/电/等离子体</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -7767,76 +7909,40 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr"/>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>适用表征方法</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="inlineStr"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -7846,12 +7952,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -7869,19 +7975,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr"/>
@@ -7895,22 +8001,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -7918,22 +8024,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据</t>
+        </is>
+      </c>
       <c r="K48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
@@ -7944,12 +8054,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -7967,14 +8077,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -7993,12 +8103,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -8016,26 +8126,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
@@ -8046,12 +8152,12 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -8076,12 +8182,12 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr"/>
@@ -8095,22 +8201,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -8125,17 +8231,17 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>★NXfabrication/PIDINST</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr"/>
@@ -8148,17 +8254,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>最近校准或维护日期</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>校准/维护日期</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -8178,21 +8284,123 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>最近校准或维护日期</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>校准/维护日期</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A46:K46"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
@@ -8206,7 +8414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9420,28 +9628,66 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr"/>
-      <c r="B59" s="11" t="inlineStr"/>
-      <c r="C59" s="11" t="inlineStr"/>
-      <c r="D59" s="11" t="inlineStr"/>
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>v3.15</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>实体/设备</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>温度传感器由热电偶分型号改为按测温原理选择类别：热电偶、热电阻（RTD）、红外测温仪、光纤温度传感器、热敏电阻、其他</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
+          <t>v3.16</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>实体/设备</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Setup拆分制造商或品牌与型号，增加装置来源；实验室装置编号保持唯一但允许管理员通过新版本纠错；温区标称测温精度改为选填</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(30项，含条件必填)</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>v3.7新增环境温湿度、预检、目标形态、Setup测温传感器、前驱体与衬底批次、衬底化学式/晶向/粗糙度/尺寸放置、预处理操作；过程R0改为结构化温度程序、逐气体供气、绝对压力及反应时长</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1594,9 +1594,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>设计或建造单位</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>热壁炉还是冷壁炉（影响生长机理）</t>
+          <t>实验室自制装置的设计或建造单位</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -1753,22 +1753,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>二维材料课题组</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr"/>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>由所引用Setup版本只读带出</t>
+        </is>
+      </c>
       <c r="K25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1779,50 +1783,50 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>内部型号</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>独立控温的温区数量</t>
+          <t>实验室自制装置使用的内部型号或版本名称</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>1/2/3…</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>CVD-LAB-A</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>由所引用Setup版本只读带出</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -1832,22 +1836,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>改造内容</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>炉管水平还是竖直</t>
+          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -1855,22 +1859,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(改造设备)</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>更换三温区加热模块并增加独立控温</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>由所引用Setup版本只读带出</t>
+        </is>
+      </c>
       <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1881,22 +1889,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面形状</t>
+          <t>热壁炉还是冷壁炉（影响生长机理）</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -1911,19 +1919,15 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>材质与形状独立保存，禁止从斜杠或分隔符猜测</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr"/>
       <c r="K28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1934,50 +1938,50 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>独立控温的温区数量</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>1/2/3…</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>选择炉管材质与截面后必填</t>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -1987,22 +1991,22 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>坐标系</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>本装置位置参照；全局固定、不可编辑</t>
+          <t>炉管水平还是竖直</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -2010,26 +2014,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2040,37 +2040,37 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>所引用装置版本中每个温区的传感器类别和资料标明的标称测温精度，只读带出</t>
+          <t>炉管材料与截面形状</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type, zone_index, nominal_accuracy_C?}</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>必填(装置登记)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>温区1：热电偶，标称测温精度±1℃</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>实验中不重复填写，由Setup版本快照冻结</t>
+          <t>材质与形状独立保存，禁止从斜杠或分隔符猜测</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr"/>
@@ -2093,47 +2093,47 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>所引用装置是否具备等离子体、光或电场能力；本炉实际使用情况在反应条件中记录</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>无/等离子体/光/电</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选择炉管材质与截面后必填</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>只读投影；不得当成本炉实际使用记录</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -2146,22 +2146,22 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>坐标系</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图 + 文字批注</t>
+          <t>本装置位置参照；全局固定、不可编辑</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>附件+自由</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -2169,22 +2169,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>setup.png + 卧式双温区</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>★v3：从逐次填『原点+轴向』改为全局定死，防选反</t>
+        </is>
+      </c>
       <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2195,92 +2199,128 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>炉管使用履历</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>当前炉管的累计清洗或更换次数，以及本次实验是最近一次清洗或更换后的第几次使用</t>
+          <t>所引用装置版本中每个温区的传感器类别和资料标明的标称测温精度，只读带出</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>使用履历对象</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>{reset_count, use_number_since_reset}</t>
+          <t>{sensor_type, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>次</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>必填</t>
+          <t>必填(装置登记)</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>{reset_count: 1, use_number_since_reset: 7}</t>
+          <t>温区1：热电偶，标称测温精度±1℃</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>6/24决定·用户复核2026-07-24</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>每炉手填；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
+          <t>实验中不重复填写，由Setup版本快照冻结</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>§3 前驱体（用了哪些原料：主源、辅助剂等，可多个；每个一组）</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>外场能力</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>所引用装置是否具备等离子体、光或电场能力；本炉实际使用情况在反应条件中记录</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>多选</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>无/等离子体/光/电</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>只读投影；不得当成本炉实际使用记录</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>前驱体</t>
+          <t>设备</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>前驱体标识（来自批次）</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>从所选物料批次快照带出的原料名称或化学式</t>
+          <t>装置照片或示意图 + 文字批注</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>附件+自由</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -2288,14 +2328,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>MoO₃</t>
+          <t>setup.png + 卧式双温区</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -2303,118 +2343,78 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>选择物料批次后只读带出，不在炉次中建立第二套身份</t>
-        </is>
-      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>前驱体</t>
+          <t>设备</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>CAS号（来自批次）</t>
+          <t>炉管使用履历</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>从所选物料批次快照带出的 CAS 号</t>
+          <t>当前炉管的累计清洗或更换次数，以及本次实验是最近一次清洗或更换后的第几次使用</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>使用履历对象</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>{reset_count, use_number_since_reset}</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>1313-27-5</t>
+          <t>{reset_count: 1, use_number_since_reset: 7}</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>6/24决定·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>由后端根据冻结物料批次快照重建，前端只读，不接受用户覆盖</t>
+          <t>每炉手填；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>相态</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>前驱体物态（决定用量单位、是否有投料mg）</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>下拉</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>固/气/液</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>固</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
-        <is>
-          <t>★v3.2b补：为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
-        </is>
-      </c>
-      <c r="K38" s="11" t="inlineStr"/>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>§3 前驱体（用了哪些原料：主要前驱体、辅助剂等，可多个；每个一组）</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -2424,22 +2424,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>外观描述</t>
+          <t>本次使用形态</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>使用时外观/性状——溯源时判断是否潮解、变质（湿度隐变量的可观察代理）</t>
+          <t>本次实验实际使用时的形态；先据此筛选可引用的化学品或气瓶批次</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>白色粉末/白色晶粒/淡黄色粉末/结块或潮解/变色/其他</t>
+          <t>固/气/液</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -2447,24 +2447,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>推荐(固态源)</t>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>白色粉末</t>
+          <t>固</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>导师</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审新增(K35)；记『使用时』状态（随时间变化），故放每炉次而非MaterialLot；词表待与俊杰确认</t>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>位于批次选择之前；固态和液态只允许引用化学品批次，气态只允许引用气瓶批次</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr"/>
@@ -2477,12 +2477,12 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>物料批次</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>引用批号（纯度/粒径自动带出），锁定当时版本</t>
+          <t>引用与本次使用形态匹配的物料批次并冻结当时版本</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>必须引用正确类别的物料批次并冻结版本，纯度、CAS和标签证据从快照带出</t>
+          <t>批次摘要直接展示名称、化学式、CAS、供应商、生产批号、纯度和适用的D50，不再渲染重复只读输入框</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr"/>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>本次用途</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>在反应里的角色</t>
+          <t>本前驱体在本次反应中的用途</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>主源/辅助剂/掺杂源/其他</t>
+          <t>主要前驱体/辅助剂/掺杂源/其他</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>主源</t>
+          <t>主要前驱体</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>会议·导师复核2026-07-28</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>界面中文(英文)</t>
+          <t>使用完整名称，避免“主源”“角色”等需要解释的内部术语</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -2583,17 +2583,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>其他用途</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>投料量（只记投料，不记残余）</t>
+          <t>本次用途选择其他时填写</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -2603,34 +2603,30 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>mg 或 µL（按相态）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>条件必填(非气态)</t>
+          <t>条件必填(本次用途=其他)</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>成核促进剂</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>★相态≠气时必填；固态mg、液态µL/质量（Fable三轮B3）</t>
-        </is>
-      </c>
-      <c r="K42" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-28前驱体复核</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>仅在选择其他用途时显示</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -2640,50 +2636,54 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>使用量</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>投料前处理（可多步，选了再展开参数）</t>
+          <t>投料量（只记投料，不记残余）</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>前驱体处理步骤数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>{type: 直接加载|熔融凝固|压片|旋涂|退火|研磨|其他, other_name?, parameters: 具名参数对象}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mg 或 µL（按相态）</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(非气态)</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>[{type: 旋涂, parameters: {speed_rpm: 3000, duration_s: 60}}]</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>有序可重复；已知方式使用具名参数和固定单位；压片及其他使用至少一项{name,value,unit}，不接受无单位自由文本</t>
-        </is>
-      </c>
-      <c r="K43" s="11" t="inlineStr"/>
+          <t>相态≠气时必填；固态按mg、液态按µL；气体流量归实验过程</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -2693,47 +2693,47 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>舟或坩埚</t>
+          <t>使用前状态</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>本前驱体所用盛装容器的材质、尺寸和使用履历</t>
+          <t>固态前驱体在本次使用前是否存在潮解、结块或变色等可观察变化</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>具名尺寸对象</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英舟|陶瓷(刚玉)舟|其他, material_other?, length_mm?, width_mm?, height_mm?, diameter_mm?, reset_count, use_number_since_reset}</t>
+          <t>正常/结块或潮解/变色/其他</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(非气态)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>推荐(固态源)</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>石英舟 90×15；重置1次；本次为重置后第7次使用</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>复审·用户复核2026-07-24</t>
+          <t>导师·2026-07-28前驱体复核</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>每个前驱体分别记录，避免多只舟共用一条履历；至少填写一个具名尺寸；其他材质须具名</t>
+          <t>粉末、晶粒等稳定物理形态归物料批次；本字段只记每次使用时的状态变化</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr"/>
@@ -2746,47 +2746,47 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>前驱体位置</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>前驱体所在温区；仅在位置温度不同于温区设定程序或另有测量/估计时补充温度及依据</t>
+          <t>投料前处理（可多步，选了再展开参数）</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>温区温度对象</t>
+          <t>前驱体处理步骤数组</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, temperature_C?, temperature_basis?: 实测值|估计}</t>
+          <t>{type: 直接加载|熔融凝固|压片|旋涂|退火|研磨|其他, other_name?, parameters: 固定参数对象}</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>推荐；填写距热电偶距离时必填</t>
+          <t>推荐(非气态)</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>温区1；位置温度620；依据=估计</t>
+          <t>[{type: 旋涂, parameters: {speed_rpm: 3000, duration_s: 60}}]</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
+          <t>2026-07-24导师走查·2026-07-28前驱体复核</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>温区按进气端编号；温度程序仍是各温区设定值的权威记录；填写距热电偶距离时必须先选择所在温区</t>
+          <t>有序可重复；直接加载与其他处理互斥；压片暂用压力、保压时间、模具直径三个固定参数，待俊杰和博研试填确认</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr"/>
@@ -2799,92 +2799,128 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>距热电偶距离</t>
+          <t>装载方式</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>距所在温区热电偶的水平距离</t>
+          <t>非气态前驱体实际进入反应器的方式，决定是否展开源容器与炉内位置</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>舟/坩埚/衬底表面/其他容器</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(非气态)</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>舟</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28前驱体复核</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>选择衬底表面表示该前驱体涂覆在衬底上，不再填写源容器和独立源区位置</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>前驱体</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>源容器</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>舟、坩埚或其他源容器的材质、条件化尺寸与每炉使用履历</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>前驱体源容器对象</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>{material: 石英|刚玉|其他, material_other?, length_mm?, width_mm?, height_mm?, diameter_mm?, description?, reset_count, use_number_since_reset}</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>-20</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>上游为负、下游为正</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>§4 衬底（长在什么基底上，可多片）</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(装载方式=舟/坩埚/其他容器)</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>舟；石英；90×15×10 mm；重置1次；本次为重置后第7次使用</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>复审·用户复核2026-07-24·2026-07-28前驱体复核</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>舟显示长宽高；坩埚显示直径和高度；其他容器填写简短尺寸说明；每个前驱体分别记录</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>衬底</t>
+          <t>前驱体</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>衬底材料（来自批次）</t>
+          <t>前驱体放置位置</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>源容器所在温区、相对该区热电偶的有符号距离，以及可选的独立位置温度</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>前驱体位置对象</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>{zone_index, distance_mm, temperature_C?, temperature_basis?: 实测值|估计}</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -2892,76 +2928,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(装载方式=舟/坩埚/其他容器)</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>温区1；相对热电偶-20 mm；该位置温度620 ℃；依据=估计</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr"/>
+          <t>会议·用户复核2026-07-24·2026-07-28前驱体复核</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>温区按装置定义；相对热电偶沿气流上游为负、下游为正；位置温度仅在实测或估计时填写</t>
+        </is>
+      </c>
       <c r="K48" s="11" t="inlineStr"/>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>物料批次（引用）</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>引用衬底批号并冻结当时版本、规格与证据</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>实体版本引用</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>{entity_id, version, snapshot}</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>Sapphire-B202（锁 v1）</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>必须引用衬底类别的不可变物料版本</t>
-        </is>
-      </c>
-      <c r="K49" s="11" t="inlineStr"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>§4 衬底（长在什么基底上，可多片）</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -2971,22 +2975,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>本次样片标记</t>
+          <t>衬底材料（来自批次）</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
+          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -3001,19 +3005,15 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
@@ -3024,22 +3024,22 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>衬底化学式（来自批次）</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>标准化学式</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Al₂O₃</t>
+          <t>Sapphire-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
+          <t>必须引用衬底类别的不可变物料版本</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr"/>
@@ -3077,22 +3077,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光信息（来自批次）</t>
+          <t>本次样片标记</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
+          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
+          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr"/>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>晶面取向与抛光（来自批次）</t>
+          <t>衬底化学式（来自批次）</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
+          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>例如 (100)、c面、a面</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -3153,14 +3153,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(批次有规格数值)</t>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>c面；单面抛</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>不与化学式或偏转角合并</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr"/>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>偏切信息（来自批次）</t>
+          <t>取向与抛光信息（来自批次）</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
+          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
+          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
@@ -3236,27 +3236,27 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>偏切角（相对标称晶面，来自批次）</t>
+          <t>晶面取向与抛光（来自批次）</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
+          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>例如 (100)、c面、a面</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -3266,24 +3266,20 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>c面；单面抛</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
-        </is>
-      </c>
-      <c r="K55" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>不与化学式或偏转角合并</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -3293,22 +3289,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>偏切方向（来自批次）</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -3316,24 +3312,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(偏切角&gt;0)</t>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴偏0.2°</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
@@ -3346,12 +3342,12 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度（来自批次）</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -3361,33 +3357,37 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>条件必填(批次有规格数值)</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr"/>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"lt":90}</t>
         </is>
       </c>
     </row>
@@ -3399,47 +3399,47 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>标称表面粗糙度（来自批次）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(偏切角&gt;0)</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -3452,50 +3452,50 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>本片实际尺寸与放置方式</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="inlineStr">
-        <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
-        </is>
-      </c>
-      <c r="K59" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -3505,37 +3505,37 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -3558,54 +3558,50 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>本片实际尺寸与放置方式</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>{length_mm: 10, width_mm: 10, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: 15}</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K61" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -3615,22 +3611,22 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>预处理（有序步骤）</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>{type: 丙酮清洗|异丙醇清洗|氮气吹干|退火|等离子体|亲水处理|其他, other_name?, parameters: 具名参数对象}</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -3638,24 +3634,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>[{type: 丙酮清洗}, {type: 异丙醇清洗}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>与时间间隔独立保存</t>
+          <t>有序可重复；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr"/>
@@ -3668,213 +3664,217 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>所在温区与热电偶距离</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>第几温区、距离(±)</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>温区距离对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, distance_mm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G63" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>温区2，+15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>上游为负、下游为正</t>
-        </is>
-      </c>
-      <c r="K63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>暴露环境</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>处理完成到放入实验装置期间所处环境</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>空气/氮气/真空/其他</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>空气</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>与时间间隔独立保存</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>所在温区与热电偶距离</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>预处理操作</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>抽气、气路置换等有序可重复的实验前操作</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>预处理操作数组</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(预处理记录)</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
-        </is>
-      </c>
-      <c r="K66" s="11" t="inlineStr"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr"/>
@@ -3892,42 +3892,42 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>预处理操作</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>抽气、气路置换等有序可重复的实验前操作</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G68" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(预处理记录)</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
@@ -3945,32 +3945,32 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
@@ -3998,42 +3998,42 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>压力体系与工作绝对压力</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>常压；1.01325×10⁵ Pa</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -4043,44 +4043,40 @@
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>填绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -4090,17 +4086,17 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4108,42 +4104,42 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>压力体系与工作绝对压力</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
-        </is>
-      </c>
-      <c r="G72" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>常压；1.01325×10⁵ Pa</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -4153,60 +4149,64 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr"/>
+          <t>填绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>实际外场程序</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
-        </is>
-      </c>
-      <c r="G73" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
         </is>
       </c>
       <c r="K73" s="11" t="inlineStr"/>
@@ -4214,52 +4214,52 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(其他记录)</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K74" s="11" t="inlineStr"/>
@@ -4267,97 +4267,133 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
+          <t>步·外场</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>实际外场程序</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>实际外场数组</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>按参数</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
           <t>过程步</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>其他记录说明</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>说明该记录的时间、操作和必要参数</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="14" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>其他记录名称</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
         <is>
           <t>条件必填(其他记录)</t>
         </is>
       </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>第30分钟将源舟向下游移动10 mm</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>临时移动源舟</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J75" s="11" t="inlineStr">
-        <is>
-          <t>必须持久化，绝不静默过滤</t>
-        </is>
-      </c>
-      <c r="K75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
-      <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
-      <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="n"/>
-      <c r="I76" s="8" t="n"/>
-      <c r="J76" s="8" t="n"/>
-      <c r="K76" s="8" t="n"/>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>禁止仅保存“其他”</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>事件编号</t>
+          <t>其他记录说明</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+          <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>UUID</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4365,14 +4401,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(其他记录)</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440000</t>
+          <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -4382,63 +4418,27 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
+          <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
     </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>过程中发生的客观事件类型</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>供气中断</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J78" s="11" t="inlineStr">
-        <is>
-          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
-        </is>
-      </c>
-      <c r="K78" s="11" t="inlineStr"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="8" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -4448,22 +4448,22 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>发生时刻</t>
+          <t>事件编号</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>日期时间</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4478,17 +4478,17 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24T10:28:00+08:00</t>
+          <t>550e8400-e29b-41d4-a716-446655440000</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>相对时间可由t0算</t>
+          <t>创建事件时生成，排序和编辑不得改变</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
@@ -4501,22 +4501,22 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>是否导致实验终止</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>该事件是否导致本炉实验提前终止</t>
+          <t>过程中发生的客观事件类型</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>复选</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>客观记录，不等同于成败判断</t>
+          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr"/>
@@ -4554,22 +4554,22 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>终止原因</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>事件导致实验终止时的客观原因</t>
+          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>日期时间</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划变更/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -4577,14 +4577,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G81" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(导致实验终止)</t>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>设备报警</t>
+          <t>2026-07-24T10:28:00+08:00</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>正常计划结束不是异常终止原因</t>
+          <t>相对时间可由t0算</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -4607,22 +4607,22 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>是否导致实验终止</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>该事件是否导致本炉实验提前终止</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>复选</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -4630,14 +4630,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G82" s="16" t="inlineStr">
-        <is>
-          <t>选填；终止原因=其他时必填</t>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+          <t>客观记录，不等同于成败判断</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr"/>
@@ -4660,22 +4660,22 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>处理措施</t>
+          <t>终止原因</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>事件发生后采取的操作</t>
+          <t>事件导致实验终止时的客观原因</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设备报警/人工停止/计划变更/其他</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -4683,14 +4683,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(导致实验终止)</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>更换气瓶后恢复供气</t>
+          <t>设备报警</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>正常计划结束不是异常终止原因</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr"/>
@@ -4713,22 +4713,22 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>事件附件</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>与本条事件直接关联的图片、日志或其他文件</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用数组</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>FileAsset UUID列表</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -4738,67 +4738,103 @@
       </c>
       <c r="G84" s="16" t="inlineStr">
         <is>
+          <t>选填；终止原因=其他时必填</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>处理措施</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>事件发生后采取的操作</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
+        <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>更换气瓶后恢复供气</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
         <is>
           <t>2026-07-24导师走查</t>
         </is>
       </c>
-      <c r="J84" s="11" t="inlineStr">
-        <is>
-          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
-        </is>
-      </c>
-      <c r="K84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
-      <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
-      <c r="I85" s="8" t="n"/>
-      <c r="J85" s="8" t="n"/>
-      <c r="K85" s="8" t="n"/>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>与事件说明独立保存</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>表征方法</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -4806,80 +4842,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J86" s="13" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr"/>
     </row>
-    <row r="87">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>测试条件</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>该表征的测试参数</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>文本/自由</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G87" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H87" s="11" t="inlineStr">
-        <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J87" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="8" t="n"/>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="8" t="n"/>
+      <c r="H87" s="8" t="n"/>
+      <c r="I87" s="8" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -4889,22 +4889,22 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>表征方法</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -4912,48 +4912,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G88" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J88" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J88" s="13" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+        </is>
+      </c>
       <c r="K88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -4961,24 +4965,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J89" s="13" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
@@ -4986,22 +4990,22 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -5014,26 +5018,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G90" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J90" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr"/>
       <c r="K90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
@@ -5044,27 +5044,27 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="16" t="inlineStr">
@@ -5074,24 +5074,20 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="inlineStr">
-        <is>
-          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
-        </is>
-      </c>
-      <c r="K91" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J91" s="13" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
@@ -5101,17 +5097,17 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -5121,7 +5117,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G92" s="16" t="inlineStr">
@@ -5131,24 +5127,20 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J92" s="11" t="inlineStr">
-        <is>
-          <t>量化口径仍须随表征条件记录</t>
-        </is>
-      </c>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"le":100}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J92" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -5158,12 +5150,12 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -5178,7 +5170,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G93" s="16" t="inlineStr">
@@ -5188,7 +5180,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -5196,10 +5188,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J93" s="11" t="inlineStr"/>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
+        </is>
+      </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5207,12 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
@@ -5231,7 +5227,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G94" s="16" t="inlineStr">
@@ -5241,7 +5237,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -5249,10 +5245,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J94" s="11" t="inlineStr"/>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"ge":0,"le":100}</t>
         </is>
       </c>
     </row>
@@ -5264,27 +5264,27 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>结构化指标数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>每条:{metric_code,value,unit}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>按指标</t>
+          <t>μm</t>
         </is>
       </c>
       <c r="G95" s="16" t="inlineStr">
@@ -5294,143 +5294,147 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J95" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
-        </is>
-      </c>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr"/>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="n"/>
-      <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="8" t="n"/>
-      <c r="J96" s="8" t="n"/>
-      <c r="K96" s="8" t="n"/>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>成核密度</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>指定统计区域内单位面积成核点数量</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>结构化指标数组</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G97" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+          <t>按指标</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J97" s="11" t="inlineStr"/>
-      <c r="K97" s="11" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t>靶基距</t>
-        </is>
-      </c>
-      <c r="C98" s="11" t="inlineStr">
-        <is>
-          <t>靶到衬底距离</t>
-        </is>
-      </c>
-      <c r="D98" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G98" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J98" s="11" t="inlineStr"/>
-      <c r="K98" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J97" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="8" t="n"/>
+      <c r="G98" s="8" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -5440,27 +5444,27 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -5470,7 +5474,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -5489,27 +5493,27 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -5519,7 +5523,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -5530,7 +5534,7 @@
       <c r="J100" s="11" t="inlineStr"/>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0,"require_value":true}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5546,12 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
@@ -5557,12 +5561,12 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -5572,7 +5576,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -5581,11 +5585,7 @@
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr"/>
-      <c r="K101" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -5595,27 +5595,27 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>沉积速率</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>速率（QCM 等）</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>nm/s</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -5636,21 +5636,127 @@
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>预溅射与挡板时序</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr"/>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>沉积速率</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>速率（QCM 等）</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>nm/s</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(PVD)</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr"/>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
           <t>{"gt":0}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A35:K35"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A96:K96"/>
-    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="A87:K87"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A85:K85"/>
-    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A66:K66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5662,7 +5768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5883,12 +5989,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>物质名称（中文）</t>
+          <t>物料名称（按标签）</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>物料标签或CoA上的中文名称；与化学式、CAS号分别记录</t>
+          <t>物料标签或CoA上的名称，允许中文或英文；与化学式、CAS号分别记录</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -5923,7 +6029,7 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>不用化学式代替名称；英文标签可按课题组常用中文名填写</t>
+          <t>按标签记录，不要求用户自行翻译；不用化学式代替名称</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr"/>
@@ -6261,7 +6367,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>粉末/颗粒/块/箔/靶/其他</t>
+          <t>粉末/颗粒/块/液体/箔/靶/其他</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -7289,9 +7395,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -7340,7 +7446,7 @@
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -7389,7 +7495,7 @@
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -7413,12 +7519,12 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>实验室装置编号（资产编号）</t>
+          <t>设计或建造单位</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
+          <t>实验室自制装置的设计或建造单位</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -7436,26 +7542,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>二维材料课题组</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B·2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
@@ -7466,17 +7568,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>内部型号</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>实验室自制装置使用的内部型号或版本名称</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -7486,30 +7588,26 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>CVD-LAB-A</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+      <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -7519,49 +7617,45 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>改造内容</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
+          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(改造设备)</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
+          <t>更换三温区加热模块并增加独立控温</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
@@ -7572,22 +7666,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>实验室装置编号（资产编号）</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -7602,15 +7696,19 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr"/>
+          <t>review§4.1B·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
+        </is>
+      </c>
       <c r="K39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
@@ -7621,27 +7719,27 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -7651,20 +7749,20 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -7674,47 +7772,47 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>必填；按炉管截面填写</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
+          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -7727,12 +7825,12 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -7742,7 +7840,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -7750,26 +7848,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
@@ -7780,22 +7874,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -7803,14 +7897,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -7820,7 +7914,7 @@
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
@@ -7833,47 +7927,47 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光、电或等离子体能力</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子体</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>必填</t>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr"/>
@@ -7886,22 +7980,22 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图及文字说明</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -7916,58 +8010,98 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
+        </is>
+      </c>
       <c r="K45" s="11" t="inlineStr"/>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>坐标系定义</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>固定定义</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>上游为负；下游为正；原点固定</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>上游(-)←原点→下游(+)</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>装置具备的光、电或等离子体能力</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无/光/电/等离子体</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -7982,41 +8116,45 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+        </is>
+      </c>
       <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -8024,14 +8162,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -8039,61 +8177,25 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据</t>
-        </is>
-      </c>
+      <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>厂商</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>品牌</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>Horiba</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr"/>
-      <c r="K49" s="11" t="inlineStr"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -8103,12 +8205,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -8126,19 +8228,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr"/>
@@ -8152,22 +8254,22 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -8175,22 +8277,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据</t>
+        </is>
+      </c>
       <c r="K51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
@@ -8201,12 +8307,12 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -8224,26 +8330,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
@@ -8254,12 +8356,12 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -8277,19 +8379,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
@@ -8303,22 +8405,22 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -8333,19 +8435,15 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
@@ -8356,51 +8454,206 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
+          <t>仪器持久标识</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>所在实验室与位置</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>物理位置</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>A305</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
           <t>最近校准或维护日期</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>校准/维护日期</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="H58" s="11" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr"/>
-      <c r="K55" s="11" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A49:K49"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
@@ -8414,7 +8667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9674,20 +9927,64 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
+          <t>v3.17</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>实体/设备</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>装置来源改为必填；商业设备显示制造商与型号，实验室自制显示设计或建造单位与内部型号，改造设备显示原设备制造商、原设备型号与改造内容；公共技术字段不变</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>v3.18</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>§3/实体</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>前驱体先选本次使用形态再筛选批次；删除炉次中重复的名称化学式和CAS；用途、使用量、使用前状态、处理步骤按实际语义收敛；非气态按舟、坩埚、衬底表面或其他容器展开容器尺寸、履历与炉内位置</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28前驱体首版复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>硬必填核心(30项，含条件必填)</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>v3.7新增环境温湿度、预检、目标形态、Setup测温传感器、前驱体与衬底批次、衬底化学式/晶向/粗糙度/尺寸放置、预处理操作；过程R0改为结构化温度程序、逐气体供气、绝对压力及反应时长</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>硬必填核心(29项，含条件必填)</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>v3.18删除炉次内重复的前驱体化学式R0；物料身份仍由必填的批次版本快照冻结；其余R0定义不变</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>CVD/APCVD/LPCVD/PECVD/MOCVD/盐辅助CVD/PVD-磁控溅射/PVD-热蒸发/PLD</t>
+          <t>CVD</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>新记录固定为CVD；历史APCVD/LPCVD/PECVD/MOCVD/盐辅助CVD值继续兼容读取</t>
+          <t>新记录固定为CVD；压力、等离子体、金属有机源和盐辅助均在正交事实字段中表达；PVD未发布</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr"/>
@@ -4867,7 +4867,7 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>§7 产物表征 + 实测产物（★独立表，用编号与实验记录关联；只记事实，不判好坏）</t>
+          <t>§7 旧扁平结果字段（未发布；由 MeasurementRun → AnalysisRun → PropertyValue / MaterialAssertion 替代）</t>
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
@@ -4912,9 +4912,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
@@ -4965,9 +4965,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G89" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -5018,9 +5018,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G90" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G91" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="G92" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="G93" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G94" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G95" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="G96" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G97" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -5467,9 +5467,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+      <c r="G99" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -5516,9 +5516,9 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G100" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+      <c r="G100" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -5569,9 +5569,9 @@
           <t>W·V</t>
         </is>
       </c>
-      <c r="G101" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+      <c r="G101" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
@@ -5618,9 +5618,9 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="G102" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+      <c r="G102" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
@@ -5671,9 +5671,9 @@
           <t>min·s</t>
         </is>
       </c>
-      <c r="G103" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+      <c r="G103" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -5724,9 +5724,9 @@
           <t>nm/s</t>
         </is>
       </c>
-      <c r="G104" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(PVD)</t>
+      <c r="G104" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -5768,7 +5768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6140,22 +6140,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>物质同义名</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>商业批次：厂商</t>
+          <t>用于检索的稳定同义名，不替代标签名称</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他(可扩展)</t>
+          <t>文本数组</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>JSON字符串数组</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -6163,22 +6163,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>阿拉丁</t>
+          <t>["Molybdenum trioxide"]</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>归一化到Substance实体</t>
+        </is>
+      </c>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6189,22 +6193,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>供应商货号</t>
+          <t>物质标识符</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>商业批次：产品号</t>
+          <t>CAS、InChIKey等标识符及其类型</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[{type,value}]</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -6219,17 +6223,17 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>M112056</t>
+          <t>[{"type":"CAS","value":"1313-27-5"}]</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>供应商产品规格编号，标签上常写作 Cat. No.；同一货号可有多个生产批号</t>
+          <t>归一化到Substance实体</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr"/>
@@ -6242,22 +6246,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>生产批号</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>商业批次：生产批号（同名不同批的区分键）</t>
+          <t>商业批次：厂商</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他(可扩展)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -6265,14 +6269,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>B202405</t>
+          <t>阿拉丁</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -6280,11 +6284,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>GMP法定术语『批号』；标签上常写作 Lot No. 或 Batch No.</t>
-        </is>
-      </c>
+      <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -6295,37 +6295,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>纯度</t>
+          <t>供应商货号</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>仅存质量百分数；N值由质量百分数派生显示，不作为独立存储值</t>
+          <t>商业批次：产品号</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>质量百分数（N值仅派生显示）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(化学品或气瓶)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>99.995（派生显示4N5）</t>
+          <t>M112056</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -6335,14 +6335,10 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>原始证书中的N值或其他纯度表述保留在CoA/附件说明中</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"le":100}</t>
-        </is>
-      </c>
+          <t>供应商产品规格编号，标签上常写作 Cat. No.；同一货号可有多个生产批号</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -6352,22 +6348,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>形态与性状</t>
+          <t>供应商等级</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>试剂外观</t>
+          <t>供应商给出的产品等级或规格名称</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>粉末/颗粒/块/液体/箔/靶/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -6382,17 +6378,17 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>粉末</t>
+          <t>ACS reagent</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>外观=性状；气瓶不使用粉末/箔/靶等物料形态</t>
+          <t>与实测纯度分开</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr"/>
@@ -6405,54 +6401,50 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>粒径D50</t>
+          <t>商业产品规格</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>供应商或CoA报告的来料中位粒径；影响挥发和成核</t>
+          <t>随货号稳定的商业产品规格</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>JSON对象</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>供应商或CoA报告的D50</t>
+          <t>具名规格键值</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>µm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>条件选填(粉末或颗粒)</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>{"mesh":"100"}</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>仅在来料形态为粉末或颗粒且供应商/CoA有报告时填写；无报告留空，不用目数或猜测值代替</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>归一化到CommercialProduct实体</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -6462,17 +6454,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>开封日期</t>
+          <t>生产批号</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>影响吸潮/氧化</t>
+          <t>商业批次：生产批号（同名不同批的区分键）</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -6485,14 +6477,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>B202405</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -6500,7 +6492,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>GMP法定术语『批号』；标签上常写作 Lot No. 或 Batch No.</t>
+        </is>
+      </c>
       <c r="K15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
@@ -6511,37 +6507,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>存储方式</t>
+          <t>纯度</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>存放条件</t>
+          <t>仅存质量百分数；N值由质量百分数派生显示，不作为独立存储值</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
+          <t>质量百分数（N值仅派生显示）</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(化学品或气瓶)</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>干燥器</t>
+          <t>99.995（派生显示4N5）</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -6551,10 +6547,14 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>desiccator=干燥器</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr"/>
+          <t>原始证书中的N值或其他纯度表述保留在CoA/附件说明中</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"le":100}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -6564,22 +6564,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>证书附件(CoA)</t>
+          <t>纯度基准</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>质检证书</t>
+          <t>纯度数值所采用的组成基准</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256}</t>
+          <t>质量分数/原子分数/体积分数</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -6587,22 +6587,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(填写纯度时)</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>coa.pdf</t>
+          <t>质量分数</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr"/>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>禁止只存没有基准的百分数</t>
+        </is>
+      </c>
       <c r="K17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
@@ -6613,22 +6617,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>瓶身或包装标签附件</t>
+          <t>纯度来源</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>试剂瓶身、气瓶或衬底包装标签的原始照片，用于追溯批号与规格</t>
+          <t>纯度数值来自供应商声明还是CoA实测</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256}</t>
+          <t>供应商声明/CoA实测</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -6636,24 +6640,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(填写纯度时)</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>bottle-label.jpg</t>
+          <t>CoA实测</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>与CoA分开；同一物料版本至少上传一次并可预览、下载</t>
+          <t>来源文件仍由CoA附件保存</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr"/>
@@ -6666,12 +6670,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·材料</t>
+          <t>形态与性状</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=衬底)</t>
+          <t>试剂外观</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -6681,7 +6685,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>粉末/颗粒/块/液体/箔/靶/其他</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -6689,14 +6693,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>粉末</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -6706,7 +6710,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>与§4衬底材料词表一致</t>
+          <t>外观=性状；气瓶不使用粉末/箔/靶等物料形态</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr"/>
@@ -6719,12 +6723,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·氧化层厚度</t>
+          <t>粒径D50</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>仅SiO₂/Si</t>
+          <t>供应商或CoA报告的来料中位粒径；影响挥发和成核</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -6734,22 +6738,22 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>供应商或CoA报告的D50</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(SiO₂/Si)</t>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(粉末或颗粒)</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -6757,7 +6761,11 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>仅在来料形态为粉末或颗粒且供应商/CoA有报告时填写；无报告留空，不用目数或猜测值代替</t>
+        </is>
+      </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
           <t>{"gt":0}</t>
@@ -6772,22 +6780,22 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光信息</t>
+          <t>D50测量方法</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
+          <t>得到D50数值所用的方法</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>激光衍射/筛分/图像分析/其他</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -6795,24 +6803,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(填写D50时)</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>激光衍射</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
+          <t>未报告时留空，不猜测</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr"/>
@@ -6825,22 +6833,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光</t>
+          <t>D50统计基准</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>粒径分布按体积、数目或质量统计</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>体积分数/数目基准/质量基准</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -6848,31 +6856,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(有规格数值)</t>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(填写D50时)</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>体积分数</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>实验引用批次后只读带出</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>{"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>与测量方法共同决定可比性</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -6882,12 +6886,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切信息</t>
+          <t>D50来源</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
+          <t>D50数值的来源</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -6897,7 +6901,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>供应商声明/CoA实测</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -6905,24 +6909,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(填写D50时)</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>CoA实测</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
+          <t>来源文件仍由CoA附件保存</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr"/>
@@ -6935,17 +6939,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切角</t>
+          <t>开封日期</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角</t>
+          <t>影响吸潮/氧化</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -6955,34 +6959,26 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(有规格数值)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>大于0时必须同时填写substrate_miscut_direction</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -6992,22 +6988,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切方向</t>
+          <t>存储方式</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向</t>
+          <t>存放条件</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -7015,24 +7011,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(偏切角&gt;0)</t>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴</t>
+          <t>干燥器</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>desiccator=干燥器</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr"/>
@@ -7045,49 +7041,45 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·标称表面粗糙度</t>
+          <t>证书附件(CoA)</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度</t>
+          <t>质检证书</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>FileAsset引用</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>{file_asset_id, sha256}</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>{availability: not_provided}</t>
+          <t>coa.pdf</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
@@ -7098,47 +7090,47 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·来料尺寸规格</t>
+          <t>瓶身或包装标签附件</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
+          <t>试剂瓶身、气瓶或衬底包装标签的原始照片，用于追溯批号与规格</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>FileAsset引用</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>{file_asset_id, sha256}</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>bottle-label.jpg</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>不替代每次实验的本片实际尺寸</t>
+          <t>与CoA分开；同一物料版本至少上传一次并可预览、下载</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -7151,22 +7143,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸衬底·材料</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>子类(批次类别=衬底)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -7174,14 +7166,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -7191,7 +7183,7 @@
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>base纯度的数值百分比为权威值；这里只保留供应商标签</t>
+          <t>与§4衬底材料词表一致</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -7204,17 +7196,17 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·气瓶编号</t>
+          <t>▸衬底·氧化层厚度</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>钢瓶追溯号</t>
+          <t>仅SiO₂/Si</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -7224,17 +7216,17 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(SiO₂/Si)</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>GC-Ar-07</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -7243,49 +7235,89 @@
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr"/>
-      <c r="K29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>▸衬底·晶向与抛光信息</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>有规格数值·供应商未提供·不适用</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>有规格数值</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>▸衬底·晶向与抛光</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -7293,48 +7325,56 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(有规格数值)</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
-      <c r="K31" s="11" t="inlineStr"/>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>实验引用批次后只读带出</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>{"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>▸衬底·偏切信息</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -7342,24 +7382,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>对标 v1 setup_version_snapshot</t>
+          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -7367,66 +7407,74 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>装置来源</t>
+          <t>▸衬底·偏切角</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
+          <t>实际晶面相对标称晶面的偏切角</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>商业设备/实验室自制/改造设备</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(有规格数值)</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>商业设备</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
-      <c r="K33" s="11" t="inlineStr"/>
+          <t>2026-07-24用户走查</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>大于0时必须同时填写substrate_miscut_direction</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>制造商或品牌</t>
+          <t>▸衬底·偏切方向</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
+          <t>偏切角所指的晶轴或晶向</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -7444,87 +7492,95 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(商业设备或改造设备)</t>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(偏切角&gt;0)</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶</t>
+          <t>c面向a轴</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
+          <t>2026-07-24用户走查</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
       <c r="K34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>▸衬底·标称表面粗糙度</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>制造商给出的设备型号</t>
+          <t>供应商或批次规格中的标称粗糙度</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(商业设备或改造设备)</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>OTF-1200X</t>
+          <t>{availability: not_provided}</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr"/>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
+        </is>
+      </c>
       <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>设计或建造单位</t>
+          <t>▸衬底·来料尺寸规格</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置的设计或建造单位</t>
+          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -7534,95 +7590,103 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>条件选填(实验室自制)</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>二维材料课题组</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr"/>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>不替代每次实验的本片实际尺寸</t>
+        </is>
+      </c>
       <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>内部型号</t>
+          <t>▸衬底·层堆栈</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置使用的内部型号或版本名称</t>
+          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>条件选填(实验室自制)</t>
+          <t>条件选填(多层衬底)</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>CVD-LAB-A</t>
+          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr"/>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
+        </is>
+      </c>
       <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>改造内容</t>
+          <t>▸衬底·顶表面</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
+          <t>实验放样时实际暴露的最上层表面</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -7642,46 +7706,50 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>条件选填(改造设备)</t>
+          <t>条件选填(多层衬底)</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>更换三温区加热模块并增加独立控温</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr"/>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>与层堆栈配套</t>
+        </is>
+      </c>
       <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>实验室装置编号（资产编号）</t>
+          <t>▸气瓶·纯度等级</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6N/5N/4N/工业级</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -7689,24 +7757,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>5N</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B·2026-07-27终版整改</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
+          <t>base纯度的数值百分比为权威值；这里只保留供应商标签</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr"/>
@@ -7714,22 +7782,22 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>钢瓶追溯号</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -7739,83 +7807,43 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>GC-Ar-07</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr"/>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>各温区温度传感器</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>温度传感器数组</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr">
-        <is>
-          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
-        </is>
-      </c>
-      <c r="K41" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -7825,22 +7853,22 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>装置名称</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>人读名</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -7855,7 +7883,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -7874,22 +7902,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -7904,17 +7932,17 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>★锁版使能(Fable三轮B2)</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+          <t>对标 v1 setup_version_snapshot</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
@@ -7927,49 +7955,45 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>装置来源</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>商业设备/实验室自制/改造设备</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>必填；按炉管截面填写</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>商业设备</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
@@ -7980,22 +8004,22 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>制造商或品牌</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -8003,26 +8027,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>合肥科晶</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr">
-        <is>
-          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
@@ -8033,22 +8053,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>制造商给出的设备型号</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -8056,26 +8076,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>OTF-1200X</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -8086,22 +8102,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>设计或建造单位</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光、电或等离子体能力</t>
+          <t>实验室自制装置的设计或建造单位</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子体</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -8109,26 +8125,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>二维材料课题组</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr">
-        <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
@@ -8139,22 +8151,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>内部型号</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图及文字说明</t>
+          <t>实验室自制装置使用的内部型号或版本名称</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -8162,55 +8174,87 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>CVD-LAB-A</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>改造内容</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>条件选填(改造设备)</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>更换三温区加热模块并增加独立控温</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>实验室装置编号（资产编号）</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -8235,46 +8279,50 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
+          <t>review§4.1B·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
+        </is>
+      </c>
       <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -8284,7 +8332,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -8292,86 +8340,90 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据</t>
-        </is>
-      </c>
-      <c r="K51" s="11" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
+        </is>
+      </c>
       <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -8379,19 +8431,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
@@ -8400,27 +8452,27 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -8428,73 +8480,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+        </is>
+      </c>
       <c r="K54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
@@ -8502,27 +8558,27 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -8530,48 +8586,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
+        </is>
+      </c>
       <c r="K56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -8579,24 +8639,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr"/>
@@ -8604,57 +8664,686 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>外场能力</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>装置具备的光、电或等离子体能力</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>多选</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>无/光/电/等离子体</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>装置示意图与描述</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>装置照片或示意图及文字说明</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>FileAsset引用+自由</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>{file_asset_id, sha256, note}</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>setup.png</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>可更换部件绑定</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>当前Setup版本实际安装的炉管、传感器、MFC、压力计等部件</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>JSON数组</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>[{component_id,role,position?}]</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>[{"component_id":"UUID","role":"furnace_tube"}]</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>部件身份、校准和维护走独立生命周期事件</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
           <t>表征仪器</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>仪器编号</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>唯一编号</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>RAMAN-1</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>适用表征方法</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Raman</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>厂商</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>Horiba</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>LabRAM HR</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr"/>
+      <c r="K65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>序列号</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>设备序列号</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>仪器持久标识</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>所在实验室与位置</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>物理位置</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>A305</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>测量能力配置</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>仪器版本支持的测量方法及其可选固定配置</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>JSON数组</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>[{code,configuration}]</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>[{"code":"Raman","configuration":{"lasers_nm":[532]}}]</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>本次MeasurementRun只能选择这里声明的能力</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>最近校准或维护日期</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>校准/维护日期</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D71" s="11" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
+      <c r="H71" s="11" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr"/>
-      <c r="K58" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A61:K61"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8667,7 +9356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9971,20 +10660,42 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
+          <t>v4.0-rc.1</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>科学对象/实体/结果</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>引入正交TargetSpec、物理SourceLoad、统一ProcessTimeline、不可变RunRevision、样品转换图及MeasurementRun→AnalysisRun→PropertyValue/MaterialAssertion溯源链；物料、装置部件和仪器能力补齐归一化字段；PVD不进入发布契约</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28深度审查整改</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(29项，含条件必填)</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>v3.18删除炉次内重复的前驱体化学式R0；物料身份仍由必填的批次版本快照冻结；其余R0定义不变</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -9356,7 +9356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10682,20 +10682,42 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.2</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>科学完整性复核</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>关闭旧结果写入与手工派生入口；收紧审阅和转化权限；修正跨炉次转化溯源、过程单位归一化、不可变修订导出及数据集查询语义；冻结装料容器、测量时校准和样品—修订关联快照；状态降为内部验证</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-29二次复核整改</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(29项，含条件必填)</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>v3.18删除炉次内重复的前驱体化学式R0；物料身份仍由必填的批次版本快照冻结；其余R0定义不变</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -5190,7 +5190,7 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>与覆盖率拆分，0 表示在该测点未检出层状产物</t>
+          <t>仅作为 MaterialAssertion.layer_count 录入，不生成 PropertyValue；与覆盖率拆分，0 表示在该测点未检出层状产物</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3819,47 +3819,83 @@
       </c>
       <c r="K65" s="11" t="inlineStr"/>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="n"/>
-      <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="8" t="n"/>
-      <c r="J66" s="8" t="n"/>
-      <c r="K66" s="8" t="n"/>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>轴向位置</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>本片衬底相对装置轴向原点的位置</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-30产品简化</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>普通用户只填写装置轴向位置；不暴露三维坐标</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>本片衬底摆放或处理的补充说明</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -3867,120 +3903,80 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>靠近气体入口</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
-        </is>
-      </c>
+          <t>2026-07-30产品简化</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr"/>
       <c r="K67" s="11" t="inlineStr"/>
     </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>预处理操作</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>抽气、气路置换等有序可重复的实验前操作</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>预处理操作数组</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(预处理记录)</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr">
-        <is>
-          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
-        </is>
-      </c>
-      <c r="K68" s="11" t="inlineStr"/>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="8" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -3990,7 +3986,7 @@
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
@@ -3998,42 +3994,42 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>预处理操作</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>抽气、气路置换等有序可重复的实验前操作</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{operation_type: 抽气|气路置换|其他, target_absolute_pressure_Pa?, duration_min, cycle_count?, gases?, other_name?, parameters?}</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
-        </is>
-      </c>
-      <c r="G70" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(预处理记录)</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>[{operation_type: 抽气, target_absolute_pressure_Pa: 100, duration_min: 15}]</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -4043,7 +4039,7 @@
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>漏率是否逐炉记录待组内确认，本轮不混入抽气字段</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
@@ -4051,32 +4047,32 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -4086,7 +4082,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -4096,7 +4092,7 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4104,42 +4100,42 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>压力体系与工作绝对压力</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G72" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(反应条件记录)</t>
+          <t>℃ 随时间</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>常压；1.01325×10⁵ Pa</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -4149,44 +4145,40 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>填绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -4196,17 +4188,17 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
         </is>
       </c>
       <c r="K73" s="11" t="inlineStr"/>
@@ -4214,42 +4206,42 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>压力体系与工作绝对压力</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
-        </is>
-      </c>
-      <c r="G74" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>常压；1.01325×10⁵ Pa</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -4259,60 +4251,64 @@
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
-        </is>
-      </c>
-      <c r="K74" s="11" t="inlineStr"/>
+          <t>填绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>实际外场程序</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
-        </is>
-      </c>
-      <c r="G75" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr"/>
@@ -4320,52 +4316,52 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(其他记录)</t>
+          <t>℃·℃/min</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4373,97 +4369,133 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
+          <t>步·外场</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>实际外场程序</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>实际外场数组</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>按参数</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
           <t>过程步</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t>其他记录说明</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>说明该记录的时间、操作和必要参数</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="14" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>其他记录名称</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
         <is>
           <t>条件必填(其他记录)</t>
         </is>
       </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>第30分钟将源舟向下游移动10 mm</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>临时移动源舟</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J77" s="11" t="inlineStr">
-        <is>
-          <t>必须持久化，绝不静默过滤</t>
-        </is>
-      </c>
-      <c r="K77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="8" t="n"/>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>禁止仅保存“其他”</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>事件编号</t>
+          <t>其他记录说明</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+          <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>UUID</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4471,14 +4503,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(其他记录)</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440000</t>
+          <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -4488,63 +4520,27 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
+          <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
     </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>过程中发生的客观事件类型</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
-        </is>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>供气中断</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr">
-        <is>
-          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
-        </is>
-      </c>
-      <c r="K80" s="11" t="inlineStr"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="8" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="8" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -4554,22 +4550,22 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>发生时刻</t>
+          <t>事件编号</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>日期时间</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -4584,17 +4580,17 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24T10:28:00+08:00</t>
+          <t>550e8400-e29b-41d4-a716-446655440000</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>相对时间可由t0算</t>
+          <t>创建事件时生成，排序和编辑不得改变</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -4607,22 +4603,22 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>是否导致实验终止</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>该事件是否导致本炉实验提前终止</t>
+          <t>过程中发生的客观事件类型</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>复选</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/信号异常/人工干预/设备报警/其他</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -4637,7 +4633,7 @@
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -4647,7 +4643,7 @@
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>客观记录，不等同于成败判断</t>
+          <t>选择其他时必须填写明确事件名称；不再把事件与部位揉成一个值</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr"/>
@@ -4660,22 +4656,22 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>终止原因</t>
+          <t>发生时刻</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>事件导致实验终止时的客观原因</t>
+          <t>何时发生（带 UTC offset 的绝对日期时间，可跨午夜）</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>日期时间</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>设备报警/人工停止/计划变更/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -4683,14 +4679,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G83" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(导致实验终止)</t>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>设备报警</t>
+          <t>2026-07-24T10:28:00+08:00</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -4700,7 +4696,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>正常计划结束不是异常终止原因</t>
+          <t>相对时间可由t0算</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr"/>
@@ -4713,22 +4709,22 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>是否导致实验终止</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>该事件是否导致本炉实验提前终止</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>复选</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -4736,14 +4732,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G84" s="16" t="inlineStr">
-        <is>
-          <t>选填；终止原因=其他时必填</t>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -4753,7 +4749,7 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+          <t>客观记录，不等同于成败判断</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr"/>
@@ -4766,22 +4762,22 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>处理措施</t>
+          <t>终止原因</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>事件发生后采取的操作</t>
+          <t>事件导致实验终止时的客观原因</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设备报警/人工停止/计划变更/其他</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -4789,14 +4785,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G85" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(导致实验终止)</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>更换气瓶后恢复供气</t>
+          <t>设备报警</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -4806,7 +4802,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>正常计划结束不是异常终止原因</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr"/>
@@ -4819,22 +4815,22 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>事件附件</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>与本条事件直接关联的图片、日志或其他文件</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用数组</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>FileAsset UUID列表</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -4844,67 +4840,103 @@
       </c>
       <c r="G86" s="16" t="inlineStr">
         <is>
+          <t>选填；终止原因=其他时必填</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>始终可选填写事件上下文，不与处理措施或附件拼接；终止原因选择“其他”时必须具名说明</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>处理措施</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>事件发生后采取的操作</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="inlineStr">
+        <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H86" s="11" t="inlineStr">
-        <is>
-          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>更换气瓶后恢复供气</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
         <is>
           <t>2026-07-24导师走查</t>
         </is>
       </c>
-      <c r="J86" s="11" t="inlineStr">
-        <is>
-          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
-        </is>
-      </c>
-      <c r="K86" s="11" t="inlineStr"/>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>§7 旧扁平结果字段（未发布；由 MeasurementRun → AnalysisRun → PropertyValue / MaterialAssertion 替代）</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n"/>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
-      <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
-      <c r="J87" s="8" t="n"/>
-      <c r="K87" s="8" t="n"/>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>与事件说明独立保存</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>表征方法</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -4914,78 +4946,42 @@
       </c>
       <c r="G88" s="16" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J88" s="13" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr"/>
     </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>测试条件</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr">
-        <is>
-          <t>该表征的测试参数</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>文本/自由</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H89" s="11" t="inlineStr">
-        <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J89" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
-        </is>
-      </c>
-      <c r="K89" s="11" t="inlineStr"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>§7 旧扁平结果字段（未发布；由 MeasurementRun → AnalysisRun → PropertyValue / MaterialAssertion 替代）</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -4995,22 +4991,22 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>表征方法</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -5025,41 +5021,45 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J90" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J90" s="13" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+        </is>
+      </c>
       <c r="K90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J91" s="13" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr"/>
@@ -5092,22 +5092,22 @@
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -5127,19 +5127,15 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J92" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr"/>
       <c r="K92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
@@ -5150,27 +5146,27 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G93" s="16" t="inlineStr">
@@ -5180,24 +5176,20 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J93" s="11" t="inlineStr">
-        <is>
-          <t>仅作为 MaterialAssertion.layer_count 录入，不生成 PropertyValue；与覆盖率拆分，0 表示在该测点未检出层状产物</t>
-        </is>
-      </c>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J93" s="13" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -5207,17 +5199,17 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -5227,7 +5219,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="16" t="inlineStr">
@@ -5237,24 +5229,20 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J94" s="11" t="inlineStr">
-        <is>
-          <t>量化口径仍须随表征条件记录</t>
-        </is>
-      </c>
-      <c r="K94" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"le":100}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J94" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -5264,12 +5252,12 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -5284,7 +5272,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G95" s="16" t="inlineStr">
@@ -5294,7 +5282,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -5302,10 +5290,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J95" s="11" t="inlineStr"/>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>仅作为 MaterialAssertion.layer_count 录入，不生成 PropertyValue；与覆盖率拆分，0 表示在该测点未检出层状产物</t>
+        </is>
+      </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -5317,12 +5309,12 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -5337,7 +5329,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G96" s="16" t="inlineStr">
@@ -5347,7 +5339,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -5355,10 +5347,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J96" s="11" t="inlineStr"/>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"ge":0,"le":100}</t>
         </is>
       </c>
     </row>
@@ -5370,27 +5366,27 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>结构化指标数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>每条:{metric_code,value,unit}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>按指标</t>
+          <t>μm</t>
         </is>
       </c>
       <c r="G97" s="16" t="inlineStr">
@@ -5400,71 +5396,103 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J97" s="13" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
-        </is>
-      </c>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr"/>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="8" t="n"/>
-      <c r="F98" s="8" t="n"/>
-      <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-      <c r="J98" s="8" t="n"/>
-      <c r="K98" s="8" t="n"/>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>成核密度</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>指定统计区域内单位面积成核点数量</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>结构化指标数组</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>按指标</t>
         </is>
       </c>
       <c r="G99" s="16" t="inlineStr">
@@ -5474,69 +5502,41 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J99" s="11" t="inlineStr"/>
-      <c r="K99" s="11" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t>靶基距</t>
-        </is>
-      </c>
-      <c r="C100" s="11" t="inlineStr">
-        <is>
-          <t>靶到衬底距离</t>
-        </is>
-      </c>
-      <c r="D100" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F100" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G100" s="16" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H100" s="11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J100" s="11" t="inlineStr"/>
-      <c r="K100" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J99" s="13" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
@@ -5546,27 +5546,27 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G101" s="16" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -5595,27 +5595,27 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G102" s="16" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -5636,7 +5636,7 @@
       <c r="J102" s="11" t="inlineStr"/>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0,"require_value":true}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G103" s="16" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -5687,11 +5687,7 @@
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr"/>
-      <c r="K103" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K103" s="11" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
@@ -5701,27 +5697,27 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>沉积速率</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>速率（QCM 等）</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>nm/s</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G104" s="16" t="inlineStr">
@@ -5731,7 +5727,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -5742,21 +5738,127 @@
       <c r="J104" s="11" t="inlineStr"/>
       <c r="K104" s="11" t="inlineStr">
         <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>预溅射与挡板时序</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>预溅射时长、挡板开合时序</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G105" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>预溅 5 min</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>沉积速率</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>速率（QCM 等）</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>nm/s</t>
+        </is>
+      </c>
+      <c r="G106" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr"/>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
           <t>{"gt":0}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A100:K100"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="A87:K87"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A98:K98"/>
-    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A80:K80"/>
+    <mergeCell ref="A89:K89"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9356,7 +9458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10704,20 +10806,42 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.3</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>§4 衬底</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>产品简化界面增加本片轴向位置与备注；轴向位置为普通用户提交前必填，不暴露三维坐标</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-30产品简化</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(29项，含条件必填)</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>v3.18删除炉次内重复的前驱体化学式R0；物料身份仍由必填的批次版本快照冻结；其余R0定义不变</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -9458,7 +9458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10828,20 +10828,42 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.4</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>§7 表征</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>表征方法拆分最小必填与更多测量参数，固定各方法常用结果项，并增加“其他”方法说明；科学对象仍由后端统一落库</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-30产品简化</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(29项，含条件必填)</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>v3.18删除炉次内重复的前驱体化学式R0；物料身份仍由必填的批次版本快照冻结；其余R0定义不变</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -3206,9 +3206,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -3259,9 +3259,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(批次有规格数值)</t>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>选填（批次有明确规格时只读带出）</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -3312,9 +3312,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -3365,9 +3365,9 @@
           <t>°</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(批次有规格数值)</t>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -3422,9 +3422,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(偏切角&gt;0)</t>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -3528,9 +3528,9 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；批次来料规格另存于MaterialLot</t>
+          <t>本次实验实际放入炉内的这一片衬底尺寸、放置方式及条件角度；长度为沿气流方向的边长，宽度为垂直气流方向的边长</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|两片生长面相对|倾角|竖放|其他, tilt_angle_deg?, placement_other?}</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填；placement=其他时placement_other条件必填</t>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；placement=倾角时tilt_angle_deg条件必填且相对水平放置平面大于0°、小于90°；placement=其他时placement_other条件必填</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr"/>
@@ -3797,9 +3797,9 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -3850,9 +3850,9 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>普通用户只填写装置轴向位置；不暴露三维坐标</t>
+          <t>仅兼容旧记录；新记录统一填写所在温区与热电偶距离，不再使用未定义物理原点的全局轴向位置</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>purity从lot_ref.snapshot带出；区间end_min必须大于start_min；同时间段体积流量占比由各气体流量派生</t>
+          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
         </is>
       </c>
       <c r="K73" s="11" t="inlineStr"/>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>压力体系与工作绝对压力</t>
+          <t>反应压力条件与工作绝对压力</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>常压；1.01325×10⁵ Pa</t>
+          <t>常压；或低压 500 Pa</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>填绝对压力，不填相对大气压的表压</t>
+          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
         </is>
       </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":true}</t>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -4344,9 +4344,9 @@
           <t>℃·℃/min</t>
         </is>
       </c>
-      <c r="G76" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(反应条件记录)</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=其他时method_other必填</t>
+          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>field_type必须属于Setup能力；界面按类型显示明确字段，其他参数仍使用具名值和单位</t>
+          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
@@ -5870,7 +5870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5963,7 +5963,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>实体① 物料批次库 MaterialLot（统一维护前驱体、衬底与气瓶批次；实验中只引用批次，纯度和粒径自动带出并锁版）</t>
+          <t>实体① 物料批次库 MaterialLot（统一维护前驱体、衬底与气瓶批次；实验中只引用批次并冻结所引用版本）</t>
         </is>
       </c>
       <c r="B3" s="8" t="n"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>物料名称（按标签）</t>
+          <t>物料名称</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>按标签记录，不要求用户自行翻译；不用化学式代替名称</t>
+          <t>按标签记录，不要求用户自行翻译；不用化学式代替名称；已知类型的衬底由系统根据“衬底材料”生成</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr"/>
@@ -6174,15 +6174,19 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>MoO₃</t>
+          <t>MoO3</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr"/>
+          <t>2026-08-06用户界面复核</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>复用目标产物的化学式输入与即时校验；已知类型的衬底由系统生成生长表面化学式，仅云母或其他衬底需人工填写</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
@@ -6193,12 +6197,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>CAS号</t>
+          <t>CAS 号</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>唯一化学标识</t>
+          <t>标签或CoA明确提供时抄录的CAS登记号</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -6216,9 +6220,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(化学品或气瓶)</t>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -6228,10 +6232,14 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr"/>
+          <t>2026-08-02供应商标签/CoA公开资料复核</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>自研、复配或供应商资料未提供时留空</t>
+        </is>
+      </c>
       <c r="K8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
@@ -6242,22 +6250,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>物质同义名</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>用于检索的稳定同义名，不替代标签名称</t>
+          <t>商业批次：厂商</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>文本数组</t>
+          <t>下拉+其他(可扩展)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>JSON字符串数组</t>
+          <t>受控+其他</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -6265,24 +6273,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>["Molybdenum trioxide"]</t>
+          <t>阿拉丁</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-08-06用户界面复核</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>归一化到Substance实体</t>
+          <t>历史供应商可复用；新增时按包装标签原文填写名称</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr"/>
@@ -6295,22 +6303,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>物质标识符</t>
+          <t>货号（Cat. No. / Product No.）</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>CAS、InChIKey等标识符及其类型</t>
+          <t>供应商用于识别产品与规格的编号</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>[{type,value}]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -6325,17 +6333,17 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>[{"type":"CAS","value":"1313-27-5"}]</t>
+          <t>M112056</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-08-06用户界面复核</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>归一化到Substance实体</t>
+          <t>同一货号可对应多个批号</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr"/>
@@ -6348,22 +6356,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>产品等级（标签原文）</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>商业批次：厂商</t>
+          <t>包装标签、产品页或CoA给出的产品等级原文</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他(可扩展)</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>受控+其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -6371,22 +6379,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>阿拉丁</t>
+          <t>99.98% trace metals basis</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr"/>
+          <t>2026-08-02供应商标签/CoA公开资料复核</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>按供应商资料原文记录；未提供时留空</t>
+        </is>
+      </c>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -6397,12 +6409,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>供应商货号</t>
+          <t>批号（Lot No. / Batch No.）</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>商业批次：产品号</t>
+          <t>识别当前这批实物的批次编号</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -6420,24 +6432,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>M112056</t>
+          <t>B202405</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-08-06用户界面复核</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>供应商产品规格编号，标签上常写作 Cat. No.；同一货号可有多个生产批号</t>
+          <t>同一货号下用于区分不同生产批次</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr"/>
@@ -6450,27 +6462,27 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>供应商等级</t>
+          <t>纯度</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>供应商给出的产品等级或规格名称</t>
+          <t>标签或CoA明确给出的数值纯度百分比</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>百分数</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -6480,20 +6492,24 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>ACS reagent</t>
+          <t>99.995</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-08-02供应商标签/CoA公开资料复核</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>与实测纯度分开</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr"/>
+          <t>未明确标示百分数时留空；等级原文记录于“产品等级（标签原文）”，原始依据由标签或CoA附件保留</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"le":100}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -6503,22 +6519,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>商业产品规格</t>
+          <t>物料形态</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>随货号稳定的商业产品规格</t>
+          <t>试剂外观</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>JSON对象</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>具名规格键值</t>
+          <t>粉末/颗粒/块/液体/箔/靶/其他</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -6533,17 +6549,17 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>{"mesh":"100"}</t>
+          <t>粉末</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>归一化到CommercialProduct实体</t>
+          <t>外观=性状；气瓶不使用粉末/箔/靶等物料形态</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr"/>
@@ -6556,17 +6572,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>生产批号</t>
+          <t>开封日期</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>商业批次：生产批号（同名不同批的区分键）</t>
+          <t>影响吸潮/氧化</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -6579,14 +6595,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>B202405</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -6594,11 +6610,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>GMP法定术语『批号』；标签上常写作 Lot No. 或 Batch No.</t>
-        </is>
-      </c>
+      <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
@@ -6609,37 +6621,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>纯度</t>
+          <t>存储方式</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>仅存质量百分数；N值由质量百分数派生显示，不作为独立存储值</t>
+          <t>存放条件</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>质量百分数（N值仅派生显示）</t>
+          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(化学品或气瓶)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>99.995（派生显示4N5）</t>
+          <t>干燥器</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -6649,14 +6661,10 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>原始证书中的N值或其他纯度表述保留在CoA/附件说明中</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"le":100}</t>
-        </is>
-      </c>
+          <t>desiccator=干燥器</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -6666,22 +6674,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>纯度基准</t>
+          <t>分析证书（CoA）</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>纯度数值所采用的组成基准</t>
+          <t>质检证书</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>FileAsset引用</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>质量分数/原子分数/体积分数</t>
+          <t>{file_asset_id, sha256}</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -6689,26 +6697,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(填写纯度时)</t>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>质量分数</t>
+          <t>coa.pdf</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>禁止只存没有基准的百分数</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
@@ -6719,22 +6723,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>纯度来源</t>
+          <t>包装标签附件</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>纯度数值来自供应商声明还是CoA实测</t>
+          <t>试剂瓶身、气瓶或衬底包装标签的原始照片，用于追溯批号与规格</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>FileAsset引用</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>供应商声明/CoA实测</t>
+          <t>{file_asset_id, sha256}</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -6742,24 +6746,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(填写纯度时)</t>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>CoA实测</t>
+          <t>bottle-label.jpg</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>来源文件仍由CoA附件保存</t>
+          <t>与CoA分开；同一物料版本至少上传一次并可预览、下载</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr"/>
@@ -6772,12 +6776,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>形态与性状</t>
+          <t>▸衬底·材料</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>试剂外观</t>
+          <t>子类(批次类别=衬底)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -6787,7 +6791,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>粉末/颗粒/块/液体/箔/靶/其他</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -6795,14 +6799,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(衬底)</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>粉末</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -6812,7 +6816,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>外观=性状；气瓶不使用粉末/箔/靶等物料形态</t>
+          <t>与§4衬底材料词表一致</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr"/>
@@ -6825,12 +6829,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>粒径D50</t>
+          <t>▸衬底·氧化层厚度</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>供应商或CoA报告的来料中位粒径；影响挥发和成核</t>
+          <t>仅SiO₂/Si</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -6840,22 +6844,22 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>供应商或CoA报告的D50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>µm</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(粉末或颗粒)</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>条件必填(SiO₂/Si)</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -6863,11 +6867,7 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>仅在来料形态为粉末或颗粒且供应商/CoA有报告时填写；无报告留空，不用目数或猜测值代替</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr">
         <is>
           <t>{"gt":0}</t>
@@ -6882,22 +6882,22 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>D50测量方法</t>
+          <t>▸衬底·晶向与抛光信息</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>得到D50数值所用的方法</t>
+          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>激光衍射/筛分/图像分析/其他</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -6907,22 +6907,22 @@
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>条件选填(填写D50时)</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>激光衍射</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>未报告时留空，不猜测</t>
+          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr"/>
@@ -6935,22 +6935,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>D50统计基准</t>
+          <t>▸衬底·晶向与抛光</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>粒径分布按体积、数目或质量统计</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>体积分数/数目基准/质量基准</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -6960,25 +6960,29 @@
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>条件选填(填写D50时)</t>
+          <t>选填(仅供应商明确提供时)</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>体积分数</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>与测量方法共同决定可比性</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr"/>
+          <t>供应商资料明确给出且实验需要区分时填写；实验引用批次后只读带出</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>{"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -6988,12 +6992,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>D50来源</t>
+          <t>▸衬底·偏切信息</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>D50数值的来源</t>
+          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -7003,7 +7007,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>供应商声明/CoA实测</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -7013,22 +7017,22 @@
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>条件选填(填写D50时)</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>CoA实测</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>来源文件仍由CoA附件保存</t>
+          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr"/>
@@ -7041,17 +7045,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>开封日期</t>
+          <t>▸衬底·偏切角</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>影响吸潮/氧化</t>
+          <t>实际晶面相对标称晶面的偏切角</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -7061,26 +7065,34 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="11" t="inlineStr"/>
+          <t>2026-07-24用户走查</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>大于0时必须同时填写substrate_miscut_direction</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -7090,22 +7102,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>存储方式</t>
+          <t>▸衬底·偏切方向</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>存放条件</t>
+          <t>偏切角所指的晶轴或晶向</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>干燥器/手套箱/常温避光/冷藏/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -7115,22 +7127,22 @@
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>干燥器</t>
+          <t>c面向a轴</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>desiccator=干燥器</t>
+          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr"/>
@@ -7143,45 +7155,49 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>证书附件(CoA)</t>
+          <t>▸衬底·标称表面粗糙度</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>质检证书</t>
+          <t>供应商或批次规格中的标称粗糙度</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256}</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>coa.pdf</t>
+          <t>{availability: not_provided}</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
+          <t>2026-07-25用户复核</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
+        </is>
+      </c>
       <c r="K26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
@@ -7192,47 +7208,47 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>瓶身或包装标签附件</t>
+          <t>▸衬底·来料尺寸规格</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>试剂瓶身、气瓶或衬底包装标签的原始照片，用于追溯批号与规格</t>
+          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256}</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>bottle-label.jpg</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>与CoA分开；同一物料版本至少上传一次并可预览、下载</t>
+          <t>不替代每次实验的本片实际尺寸</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -7245,47 +7261,47 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·材料</t>
+          <t>▸衬底·层堆栈</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=衬底)</t>
+          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>与§4衬底材料词表一致</t>
+          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -7298,17 +7314,17 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·氧化层厚度</t>
+          <t>▸衬底·顶表面</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>仅SiO₂/Si</t>
+          <t>实验放样时实际暴露的最上层表面</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -7318,30 +7334,30 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(SiO₂/Si)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr"/>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>与层堆栈配套</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -7351,12 +7367,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光信息</t>
+          <t>▸气瓶·纯度等级</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -7366,7 +7382,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>6N/5N/4N/工业级</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -7374,24 +7390,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>5N</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
+          <t>有供应商等级标签可照录；没有则留空</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -7404,22 +7420,22 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光</t>
+          <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>钢瓶追溯号</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -7427,14 +7443,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(有规格数值)</t>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>GC-Ar-07</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -7442,89 +7458,45 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>实验引用批次后只读带出</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>{"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>MaterialLot</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>▸衬底·偏切信息</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>下拉</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>有规格数值·供应商未提供·不适用</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>供应商未提供</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-25用户复核</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切角</t>
+          <t>装置名称</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角</t>
+          <t>人读名</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -7534,54 +7506,46 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(有规格数值)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>大于0时必须同时填写substrate_miscut_direction</t>
-        </is>
-      </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切方向</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -7594,24 +7558,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(偏切角&gt;0)</t>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>★锁版使能(Fable三轮B2)</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>对标 v1 setup_version_snapshot</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -7619,70 +7583,66 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·标称表面粗糙度</t>
+          <t>装置来源</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度</t>
+          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>商业设备/实验室自制/改造设备</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>条件必填(衬底)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>{availability: not_provided}</t>
+          <t>商业设备</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·来料尺寸规格</t>
+          <t>制造商或品牌</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
+          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -7692,103 +7652,95 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>合肥科晶</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>不替代每次实验的本片实际尺寸</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·层堆栈</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
+          <t>制造商给出的设备型号</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>条件选填(多层衬底)</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
+          <t>OTF-1200X</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·顶表面</t>
+          <t>设计或建造单位</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>实验放样时实际暴露的最上层表面</t>
+          <t>实验室自制装置的设计或建造单位</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -7808,50 +7760,46 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>条件选填(多层衬底)</t>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>二维材料课题组</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>与层堆栈配套</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>内部型号</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>实验室自制装置使用的内部型号或版本名称</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -7861,40 +7809,36 @@
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>CVD-LAB-A</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>base纯度的数值百分比为权威值；这里只保留供应商标签</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·气瓶编号</t>
+          <t>改造内容</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>钢瓶追溯号</t>
+          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -7914,38 +7858,74 @@
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>条件选填(改造设备)</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>GC-Ar-07</t>
+          <t>更换三温区加热模块并增加独立控温</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr"/>
       <c r="K40" s="11" t="inlineStr"/>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>实验室装置编号（资产编号）</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>CVD-炉1</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>review§4.1B·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -7955,17 +7935,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -7975,7 +7955,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -7985,7 +7965,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -7994,7 +7974,11 @@
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr"/>
-      <c r="K42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -8004,27 +7988,27 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -8034,17 +8018,17 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>对标 v1 setup_version_snapshot</t>
+          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
@@ -8057,12 +8041,12 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>装置来源</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -8072,7 +8056,7 @@
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>商业设备/实验室自制/改造设备</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -8087,12 +8071,12 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>商业设备</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr"/>
@@ -8106,22 +8090,22 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>制造商或品牌</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -8129,22 +8113,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(商业设备或改造设备)</t>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+        </is>
+      </c>
       <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
@@ -8155,45 +8143,49 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>制造商给出的设备型号</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(商业设备或改造设备)</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>OTF-1200X</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr"/>
+          <t>会议·用户复核2026-07-24</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
+        </is>
+      </c>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -8204,22 +8196,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>设计或建造单位</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置的设计或建造单位</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -8227,22 +8219,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(实验室自制)</t>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>二维材料课题组</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
+        </is>
+      </c>
       <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
@@ -8253,22 +8249,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>内部型号</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置使用的内部型号或版本名称</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -8276,22 +8272,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(实验室自制)</t>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>CVD-LAB-A</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+        </is>
+      </c>
       <c r="K48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
@@ -8302,22 +8302,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>改造内容</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
+          <t>装置具备的光、电或等离子体能力</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无/光/电/等离子体</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -8325,22 +8325,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>条件选填(改造设备)</t>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>更换三温区加热模块并增加独立控温</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+        </is>
+      </c>
       <c r="K49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
@@ -8351,22 +8355,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>实验室装置编号（资产编号）</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -8374,26 +8378,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B·2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
@@ -8404,128 +8404,92 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>可更换部件绑定</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>当前Setup版本实际安装的炉管、传感器、MFC、压力计等部件</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[{component_id,role,position?}]</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[{"component_id":"UUID","role":"furnace_tube"}]</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr"/>
-      <c r="K51" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>各温区温度传感器</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>温度传感器数组</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr"/>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>部件身份、校准和维护走独立生命周期事件</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -8540,12 +8504,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr"/>
@@ -8554,27 +8518,27 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -8589,17 +8553,17 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+          <t>API key 保持 name_type 以兼容现有数据</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
@@ -8607,80 +8571,76 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>必填；按炉管截面填写</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr">
-        <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -8695,45 +8655,41 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -8741,52 +8697,48 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr">
-        <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr"/>
       <c r="K57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光、电或等离子体能力</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子体</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
@@ -8794,24 +8746,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>★NXfabrication/PIDINST</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -8819,27 +8771,27 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图及文字说明</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -8847,19 +8799,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr"/>
@@ -8868,72 +8820,108 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>表征仪器</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>可更换部件绑定</t>
+          <t>关键固定配置</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>当前Setup版本实际安装的炉管、传感器、MFC、压力计等部件</t>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>测量能力配置</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>仪器版本支持的测量方法及其可选固定配置</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
           <t>JSON数组</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>[{component_id,role,position?}]</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>[{"component_id":"UUID","role":"furnace_tube"}]</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>[{code,configuration}]</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>[{"code":"Raman","configuration":{"lasers_nm":[532]}}]</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>2026-07-28深度审查</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>部件身份、校准和维护走独立生命周期事件</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="8" t="n"/>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>本次MeasurementRun只能选择这里声明的能力</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -8943,17 +8931,17 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>最近校准或维护日期</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>校准/维护日期</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -8966,486 +8954,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>适用表征方法</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
-        </is>
-      </c>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据</t>
-        </is>
-      </c>
-      <c r="K63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>厂商</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>品牌</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>Horiba</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr"/>
-      <c r="K64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>型号</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>型号</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>LabRAM HR</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr"/>
-      <c r="K65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>序列号</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>设备序列号</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr"/>
-      <c r="K66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>仪器持久标识</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr">
-        <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
-      <c r="K67" s="11" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>所在实验室与位置</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>物理位置</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>A305</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>关键固定配置</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr">
-        <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
-        </is>
-      </c>
-      <c r="K69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>测量能力配置</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>仪器版本支持的测量方法及其可选固定配置</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>JSON数组</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>[{code,configuration}]</t>
-        </is>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>[{"code":"Raman","configuration":{"lasers_nm":[532]}}]</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>本次MeasurementRun只能选择这里声明的能力</t>
-        </is>
-      </c>
-      <c r="K70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>最近校准或维护日期</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>校准/维护日期</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="16" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr"/>
-      <c r="K71" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A32:K32"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9458,7 +8989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10070,7 +9601,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>AP/LP 冗余二选一敲定：保留合成方法 AP/LP，以校验规则强制与压力体系一致（不再悬置）</t>
+          <t>AP/LP 冗余二选一敲定：保留合成方法 AP/LP，以校验规则强制与反应压力条件一致（不再悬置）</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -10850,20 +10381,218 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.5</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>实体/物料批次</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>CAS号与数值纯度改为有来源才选填；删除同义名、标识符、商业规格JSON、纯度基准/来源及D50四字段；供应商规格或等级按标签原文照录</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-02供应商资料复核与减负</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.6</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>实体/物料批次</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>物料表单文案正式化：常规字段说明改为简短占位示例，仅为纯度及衬底规格等易误录字段保留必要说明；统一字段名称、中文标点和中英文术语</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-02用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.7</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>实体/物料批次</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>化学式复用目标产物输入控件并提示元素与语法；货号与批号直接对应包装上的 Cat./Product No. 和 Lot/Batch No.，说明两者的产品与实物批次分工</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-06用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.8</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>实体/物料批次</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>删除化学式格式说明，只保留示例与即时元素/语法反馈</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-06用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.9</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>实体/物料批次</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>供应商“其他”改为明确的新增供应商与名称输入；供应商规格或等级改为产品等级（标签原文），说明资料未标注时留空</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-06用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.12</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>§5 生长条件</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>统一实验时间零点与有效生长窗口；补齐气体批次、流量来源、绝对压力、受控降温速率、实际外场参数和多条异常事件，并自动覆盖生长后的实验过程</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-06用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.13</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>§5 生长条件</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>将容易误解为管理制度的“压力制度/压力体系”统一改为“反应压力条件”，数据字段与校验规则不变</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.14</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>§5 生长条件</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>改为按实际操作和持续时间录入，系统自动生成系统准备、升温与预处理、反应、反应后处理和降温时间轴；气体优先选择使用阶段，仅自定义时填写起止时间</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.15</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>§5 生长条件</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>删除缺乏统一文献定义且无法直接观测的反应计时起点、反应开始前用时、反应时长及重复的反应后处理；实际过程由温度步骤、气体时段、系统准备、压力与降温记录</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07用户界面复核与原始论文核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>硬必填核心(29项，含条件必填)</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>v3.18删除炉次内重复的前驱体化学式R0；物料身份仍由必填的批次版本快照冻结；其余R0定义不变</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D76" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -10330,7 +10330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11986,20 +11986,42 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.19</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>表征科学属性</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>PropertyValue 补齐数值/文本表示类型与物理范围，并统一后端和前端的单一源校验</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-31表征全链路独立审查</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>最小可复现核心(27项，含条件必填)</t>
         </is>
       </c>
-      <c r="C79" s="11" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
         </is>
       </c>
-      <c r="D79" s="11" t="inlineStr">
+      <c r="D80" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4744,17 +4744,17 @@
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>过程通道</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>反应压力类别</t>
+          <t>异常情况确认</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>本炉是常压、低压、超高真空或其他压力条件</t>
+          <t>明确确认本炉是否发生异常，避免将未填写误判为无异常</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>atmospheric/low_pressure/ultra_high_vacuum/other</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>low_pressure</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-09-01用户试填反馈</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
+          <t>选择是时至少填写一条过程异常事件</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr"/>
@@ -4797,17 +4797,17 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>降温方式</t>
+          <t>反应压力类别</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>本炉实际采用的降温方式</t>
+          <t>本炉是常压、低压、超高真空或其他压力条件</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/other</t>
+          <t>atmospheric/low_pressure/ultra_high_vacuum/other</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling</t>
+          <t>low_pressure</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>随炉冷却和移炉快速冷却不额外要求虚构参数</t>
+          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr"/>
@@ -4855,22 +4855,22 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>其他降温方式</t>
+          <t>降温方式</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>降温方式选择其他时的具体操作</t>
+          <t>本炉实际采用的降温方式</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/other</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
@@ -4878,14 +4878,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=other)</t>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>打开保温层自然冷却</t>
+          <t>furnace_cooling</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>仅选择其他时保存</t>
+          <t>随炉冷却和移炉快速冷却不额外要求虚构参数</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr"/>
@@ -4908,17 +4908,17 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>受控降温速率</t>
+          <t>其他降温方式</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>受控降温时的设定降温速率</t>
+          <t>降温方式选择其他时的具体操作</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -4928,17 +4928,17 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>℃/min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G87" s="17" t="inlineStr">
         <is>
-          <t>条件必填(降温方式=controlled_cooling)</t>
+          <t>条件必填(降温方式=other)</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>打开保温层自然冷却</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -4948,14 +4948,10 @@
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>仅受控降温时保存</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>仅选择其他时保存</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -4965,12 +4961,12 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>开盖温度</t>
+          <t>受控降温速率</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>开盖冷却时实际开盖的温度</t>
+          <t>受控降温时的设定降温速率</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
@@ -4985,17 +4981,17 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>℃/min</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
         <is>
-          <t>条件必填(降温方式=open_lid_cooling)</t>
+          <t>条件必填(降温方式=controlled_cooling)</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -5005,60 +5001,64 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>仅开盖冷却时保存</t>
-        </is>
-      </c>
-      <c r="K88" s="11" t="inlineStr"/>
+          <t>仅受控降温时保存</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>开盖温度</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>开盖冷却时实际开盖的温度</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G89" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=open_lid_cooling)</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
+          <t>仅开盖冷却时保存</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
@@ -5071,22 +5071,22 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>预处理操作</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>选填的实验前操作；每项记录实际持续时间，气路置换引用实际气瓶版本</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>预处理操作数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: pump_down|gas_exchange|leak_check|other, duration_min, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, snapshot?}], other_name?}</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -5096,22 +5096,22 @@
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: gas_exchange, duration_min: 10, cycle_count: 3, gas_sources: [{material_lot_id: UUID, material_lot_version: 2}]}]</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13师兄试填复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>置换可引用一瓶预混气或多瓶现场混合气；固定组成仅在气瓶版本登记</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr"/>
@@ -5119,52 +5119,52 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>预处理操作</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>选填的实验前操作；每项记录实际持续时间，气路置换引用实际气瓶版本</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>{operation_type: pump_down|gas_exchange|leak_check|other, duration_min, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, snapshot?}], other_name?}</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>[{operation_type: gas_exchange, duration_min: 10, cycle_count: 3, gas_sources: [{material_lot_id: UUID, material_lot_version: 2}]}]</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-08-13师兄试填复核</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>置换可引用一瓶预混气或多瓶现场混合气；固定组成仅在气瓶版本登记</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr"/>
@@ -5177,27 +5177,27 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G92" s="13" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr"/>
@@ -5225,32 +5225,32 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>℃ 随时间</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr"/>
@@ -5278,32 +5278,32 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件与工作绝对压力</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>常压；或低压 500 Pa</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -5323,44 +5323,40 @@
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K94" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
-        </is>
-      </c>
+          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>反应压力条件与工作绝对压力</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -5370,50 +5366,54 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>常压；或低压 500 Pa</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
-        </is>
-      </c>
-      <c r="K95" s="11" t="inlineStr"/>
+          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
@@ -5423,17 +5423,17 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr"/>
@@ -5441,42 +5441,42 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>实际外场程序</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
+          <t>℃·℃/min</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数</t>
+          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr"/>
@@ -5494,52 +5494,52 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>实际外场程序</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{field_type: 等离子体|光|电, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；other_parameters?}</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>按参数</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr"/>
@@ -5552,120 +5552,120 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
+          <t>其他记录名称</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>未发布（旧过程步兼容）</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>临时移动源舟</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>禁止仅保存“其他”</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
           <t>其他记录说明</t>
         </is>
       </c>
-      <c r="C99" s="11" t="inlineStr">
+      <c r="C100" s="11" t="inlineStr">
         <is>
           <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
-      <c r="D99" s="11" t="inlineStr">
+      <c r="D100" s="11" t="inlineStr">
         <is>
           <t>自由</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="13" t="inlineStr">
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
         <is>
           <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr">
+      <c r="H100" s="11" t="inlineStr">
         <is>
           <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="I100" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J99" s="11" t="inlineStr">
+      <c r="J100" s="11" t="inlineStr">
         <is>
           <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr"/>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="K100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>§6 过程事件 Process Events（记录异常、中断与人工干预等客观事件；只记客观事实，不判成败）</t>
         </is>
       </c>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="8" t="n"/>
-      <c r="J100" s="8" t="n"/>
-      <c r="K100" s="8" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="inlineStr">
-        <is>
-          <t>事件标识</t>
-        </is>
-      </c>
-      <c r="C101" s="11" t="inlineStr">
-        <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>系统生成键</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="F101" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G101" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr">
-        <is>
-          <t>event_1</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24整改</t>
-        </is>
-      </c>
-      <c r="J101" s="11" t="inlineStr">
-        <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
-        </is>
-      </c>
-      <c r="K101" s="11" t="inlineStr"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差</t>
+          <t>事件标识</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>过程中直接观察到的异常或人工干预，可同时选择多项</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>多选+其他</t>
+          <t>系统生成键</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>管路堵塞/压力超限/信号异常/人工干预/设备报警/人工停止/供电中断/供水中断/供气中断/计划改变/其他</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -5705,17 +5705,17 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>供气中断</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>异常现象、怀疑原因、干预动作和受影响对象分开表达</t>
+          <t>创建事件时生成，排序和编辑不得改变</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr"/>
@@ -5728,22 +5728,22 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>受影响对象</t>
+          <t>观察到的偏差</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差涉及的实验对象</t>
+          <t>过程中直接观察到的异常或人工干预，可同时选择多项</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>多选+其他</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
+          <t>管路堵塞/压力超限/信号异常/人工干预/设备报警/人工停止/供电中断/供水中断/供气中断/计划改变/其他</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -5751,14 +5751,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G103" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>气路</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
+          <t>异常现象、怀疑原因、干预动作和受影响对象分开表达</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr"/>
@@ -5781,37 +5781,37 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>开始时间</t>
+          <t>受影响对象</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件开始时间</t>
+          <t>观察到的偏差涉及的实验对象</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G104" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>气路</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
+          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr"/>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>结束时间</t>
+          <t>开始时间</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件结束时间</t>
+          <t>相对本炉实验开始时刻的事件开始时间</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
@@ -5857,14 +5857,14 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G105" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>填写时不得早于开始时间</t>
+          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr"/>
@@ -5887,27 +5887,27 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>处理结果</t>
+          <t>结束时间</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>异常发生后过程是否恢复或终止</t>
+          <t>相对本炉实验开始时刻的事件结束时间</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>已恢复/部分恢复/实验终止/未知</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>已恢复</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="J106" s="11" t="inlineStr">
         <is>
-          <t>未知可显式记录，不等同于对产物成败的判定</t>
+          <t>填写时不得早于开始时间</t>
         </is>
       </c>
       <c r="K106" s="11" t="inlineStr"/>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>对数据有效性的影响</t>
+          <t>处理结果</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
+          <t>异常发生后过程是否恢复或终止</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>不影响/部分影响/数据无效/未知</t>
+          <t>已恢复/部分恢复/实验终止/未知</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>部分影响</t>
+          <t>已恢复</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>只判断过程数据有效性，不判定产物成败</t>
+          <t>未知可显式记录，不等同于对产物成败的判定</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr"/>
@@ -5993,22 +5993,22 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因</t>
+          <t>对数据有效性的影响</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
+          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
+          <t>不影响/部分影响/数据无效/未知</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>设备故障</t>
+          <t>部分影响</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
+          <t>只判断过程数据有效性，不判定产物成败</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr"/>
@@ -6046,22 +6046,22 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>怀疑原因</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -6071,22 +6071,22 @@
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>选填；观察到的偏差包含其他时必填</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>设备故障</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>始终可选填写事件上下文，不与干预动作或附件拼接；选择“其他”偏差时必须具体说明</t>
+          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr"/>
@@ -6099,22 +6099,22 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>干预动作</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>事件发生后实际采取的操作</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -6124,22 +6124,22 @@
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选填；观察到的偏差包含其他时必填</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>恢复供应</t>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>始终可选填写事件上下文，不与干预动作或附件拼接；选择“其他”偏差时必须具体说明</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr"/>
@@ -6152,27 +6152,27 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>排除的数据时间范围</t>
+          <t>干预动作</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>因该事件不应参与后续分析的时间区间</t>
+          <t>事件发生后实际采取的操作</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>时间区间数组</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>[{start_s, end_s}]</t>
+          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>[{start_s: 1680, end_s: 1800}]</t>
+          <t>恢复供应</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
+          <t>与事件说明独立保存</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr"/>
@@ -6205,120 +6205,120 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
+          <t>排除的数据时间范围</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>因该事件不应参与后续分析的时间区间</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>时间区间数组</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>[{start_s, end_s}]</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>[{start_s: 1680, end_s: 1800}]</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>科学修订契约</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
+        </is>
+      </c>
+      <c r="K112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
           <t>事件附件</t>
         </is>
       </c>
-      <c r="C112" s="11" t="inlineStr">
+      <c r="C113" s="11" t="inlineStr">
         <is>
           <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
+      <c r="D113" s="11" t="inlineStr">
         <is>
           <t>FileAsset引用数组</t>
         </is>
       </c>
-      <c r="E112" s="11" t="inlineStr">
+      <c r="E113" s="11" t="inlineStr">
         <is>
           <t>FileAsset UUID列表</t>
         </is>
       </c>
-      <c r="F112" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G112" s="13" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H112" s="11" t="inlineStr">
+      <c r="H113" s="11" t="inlineStr">
         <is>
           <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
-      <c r="I112" s="11" t="inlineStr">
+      <c r="I113" s="11" t="inlineStr">
         <is>
           <t>2026-07-24导师走查</t>
         </is>
       </c>
-      <c r="J112" s="11" t="inlineStr">
+      <c r="J113" s="11" t="inlineStr">
         <is>
           <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
-      <c r="K112" s="11" t="inlineStr"/>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="10" t="inlineStr">
+      <c r="K113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>§7 旧扁平结果字段（未发布；由 MeasurementRun → AnalysisRun → PropertyValue / MaterialAssertion 替代）</t>
         </is>
       </c>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="8" t="n"/>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="8" t="n"/>
-      <c r="G113" s="8" t="n"/>
-      <c r="H113" s="8" t="n"/>
-      <c r="I113" s="8" t="n"/>
-      <c r="J113" s="8" t="n"/>
-      <c r="K113" s="8" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t>表征方法</t>
-        </is>
-      </c>
-      <c r="C114" s="11" t="inlineStr">
-        <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
-        </is>
-      </c>
-      <c r="D114" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
-        </is>
-      </c>
-      <c r="F114" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G114" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H114" s="11" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I114" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J114" s="15" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
-        </is>
-      </c>
-      <c r="K114" s="11" t="inlineStr"/>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="8" t="n"/>
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
@@ -6328,22 +6328,22 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>表征方法</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -6366,9 +6366,9 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J115" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
+      <c r="J115" s="15" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr"/>
@@ -6381,17 +6381,17 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -6411,41 +6411,45 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J116" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
+        </is>
+      </c>
       <c r="K116" s="11" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -6460,19 +6464,15 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J117" s="15" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr"/>
       <c r="K117" s="11" t="inlineStr"/>
     </row>
     <row r="118">
@@ -6483,22 +6483,22 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -6513,17 +6513,17 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J118" s="15" t="inlineStr">
         <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr"/>
@@ -6536,17 +6536,17 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
@@ -6566,24 +6566,20 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J119" s="11" t="inlineStr">
-        <is>
-          <t>仅作为 MaterialAssertion.layer_count 录入，不生成 PropertyValue；与覆盖率拆分，0 表示在该测点未检出层状产物</t>
-        </is>
-      </c>
-      <c r="K119" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J119" s="15" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
@@ -6593,12 +6589,12 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
@@ -6613,7 +6609,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
@@ -6623,7 +6619,7 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -6633,12 +6629,12 @@
       </c>
       <c r="J120" s="11" t="inlineStr">
         <is>
-          <t>量化口径仍须随表征条件记录</t>
+          <t>仅作为 MaterialAssertion.layer_count 录入，不生成 PropertyValue；与覆盖率拆分，0 表示在该测点未检出层状产物</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0,"le":100}</t>
+          <t>{"ge":0,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6646,12 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
@@ -6670,7 +6666,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
@@ -6680,7 +6676,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -6688,10 +6684,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J121" s="11" t="inlineStr"/>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"le":100}</t>
         </is>
       </c>
     </row>
@@ -6703,12 +6703,12 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>μm</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -6744,7 +6744,7 @@
       <c r="J122" s="11" t="inlineStr"/>
       <c r="K122" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -6756,120 +6756,124 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
+          <t>成核密度</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>指定统计区域内单位面积成核点数量</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr"/>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
           <t>关键谱学指标</t>
         </is>
       </c>
-      <c r="C123" s="11" t="inlineStr">
+      <c r="C124" s="11" t="inlineStr">
         <is>
           <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D124" s="11" t="inlineStr">
         <is>
           <t>结构化指标数组</t>
         </is>
       </c>
-      <c r="E123" s="11" t="inlineStr">
+      <c r="E124" s="11" t="inlineStr">
         <is>
           <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
-      <c r="F123" s="11" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>按指标</t>
         </is>
       </c>
-      <c r="G123" s="13" t="inlineStr">
+      <c r="G124" s="13" t="inlineStr">
         <is>
           <t>未发布</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr">
+      <c r="H124" s="11" t="inlineStr">
         <is>
           <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
-      <c r="I123" s="11" t="inlineStr">
+      <c r="I124" s="11" t="inlineStr">
         <is>
           <t>复审/导师</t>
         </is>
       </c>
-      <c r="J123" s="15" t="inlineStr">
+      <c r="J124" s="15" t="inlineStr">
         <is>
           <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
         </is>
       </c>
-      <c r="K123" s="11" t="inlineStr">
+      <c r="K124" s="11" t="inlineStr">
         <is>
           <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="10" t="inlineStr">
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
         </is>
       </c>
-      <c r="B124" s="8" t="n"/>
-      <c r="C124" s="8" t="n"/>
-      <c r="D124" s="8" t="n"/>
-      <c r="E124" s="8" t="n"/>
-      <c r="F124" s="8" t="n"/>
-      <c r="G124" s="8" t="n"/>
-      <c r="H124" s="8" t="n"/>
-      <c r="I124" s="8" t="n"/>
-      <c r="J124" s="8" t="n"/>
-      <c r="K124" s="8" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t>靶材（批次）</t>
-        </is>
-      </c>
-      <c r="C125" s="11" t="inlineStr">
-        <is>
-          <t>靶材化学身份 + 批次</t>
-        </is>
-      </c>
-      <c r="D125" s="11" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>批次库</t>
-        </is>
-      </c>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G125" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr">
-        <is>
-          <t>MoS₂ 靶-T01</t>
-        </is>
-      </c>
-      <c r="I125" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J125" s="11" t="inlineStr"/>
-      <c r="K125" s="11" t="inlineStr"/>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="8" t="n"/>
+      <c r="J125" s="8" t="n"/>
+      <c r="K125" s="8" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -6879,27 +6883,27 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
@@ -6909,7 +6913,7 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -6918,11 +6922,7 @@
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr"/>
-      <c r="K126" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K126" s="11" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -6971,7 +6971,11 @@
         </is>
       </c>
       <c r="J127" s="11" t="inlineStr"/>
-      <c r="K127" s="11" t="inlineStr"/>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -6981,27 +6985,27 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
@@ -7011,7 +7015,7 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -7020,11 +7024,7 @@
         </is>
       </c>
       <c r="J128" s="11" t="inlineStr"/>
-      <c r="K128" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
+      <c r="K128" s="11" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
@@ -7034,27 +7034,27 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -7075,7 +7075,7 @@
       <c r="J129" s="11" t="inlineStr"/>
       <c r="K129" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"gt":0,"require_value":true}</t>
         </is>
       </c>
     </row>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>沉积速率</t>
+          <t>预溅射与挡板时序</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>速率（QCM 等）</t>
+          <t>预溅射时长、挡板开合时序</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>nm/s</t>
+          <t>min·s</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>预溅 5 min</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -7132,16 +7132,69 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>沉积速率</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>速率（QCM 等）</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>nm/s</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="inlineStr"/>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A114:K114"/>
     <mergeCell ref="A62:K62"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A100:K100"/>
-    <mergeCell ref="A124:K124"/>
+    <mergeCell ref="A101:K101"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A43:K43"/>
     <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A113:K113"/>
+    <mergeCell ref="A125:K125"/>
     <mergeCell ref="A14:K14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7154,7 +7207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8113,50 +8166,50 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·氧化层厚度</t>
+          <t>▸衬底·云母类型</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>仅SiO₂/Si</t>
+          <t>云母衬底的矿物类型；用于生成对应的理想化学式</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>白云母·金云母·氟金云母</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>条件必填(SiO₂/Si)</t>
+          <t>条件必填(云母)</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>氟金云母</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-09-01用户试填反馈</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>选择后系统生成理想化学式；具体成分仍以包装标签、规格书或CoA为准</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -8166,50 +8219,50 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光信息</t>
+          <t>▸衬底·氧化层厚度</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
+          <t>仅SiO₂/Si</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(SiO₂/Si)</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr"/>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -8219,22 +8272,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光</t>
+          <t>▸衬底·晶向与抛光信息</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>供应商是否提供且该衬底是否适用晶面取向与抛光规格</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -8244,29 +8297,25 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>选填(仅供应商明确提供时)</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>供应商资料明确给出且实验需要区分时填写；实验引用批次后只读带出</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>{"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>Cu/Au箔等不适用时明确选择不适用；禁止伪填晶向或抛光面</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -8276,22 +8325,22 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切信息</t>
+          <t>▸衬底·晶向与抛光</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -8301,25 +8350,29 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填(仅供应商明确提供时)</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr"/>
+          <t>供应商资料明确给出且实验需要区分时填写；实验引用批次后只读带出</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>{"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -8329,27 +8382,27 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切角</t>
+          <t>▸衬底·偏切信息</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角</t>
+          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -8359,24 +8412,20 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>大于0时必须同时填写substrate_miscut_direction</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -8386,17 +8435,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切方向</t>
+          <t>▸衬底·偏切角</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向</t>
+          <t>实际晶面相对标称晶面的偏切角</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -8406,7 +8455,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -8416,7 +8465,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -8426,10 +8475,14 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr"/>
+          <t>大于0时必须同时填写substrate_miscut_direction</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -8439,27 +8492,27 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·标称表面粗糙度</t>
+          <t>▸衬底·偏切方向</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度</t>
+          <t>偏切角所指的晶轴或晶向</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -8469,17 +8522,17 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>{availability: not_provided}</t>
+          <t>c面向a轴</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
+          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr"/>
@@ -8492,27 +8545,27 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·来料尺寸规格</t>
+          <t>▸衬底·标称表面粗糙度</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
+          <t>供应商或批次规格中的标称粗糙度</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -8522,17 +8575,17 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>{availability: not_provided}</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>不替代每次实验的本片实际尺寸</t>
+          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -8545,27 +8598,27 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·层堆栈</t>
+          <t>▸衬底·来料尺寸规格</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
+          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
@@ -8575,17 +8628,17 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
+          <t>不替代每次实验的本片实际尺寸</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -8598,27 +8651,27 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·顶表面</t>
+          <t>▸衬底·层堆栈</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>实验放样时实际暴露的最上层表面</t>
+          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
@@ -8628,7 +8681,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -8638,7 +8691,7 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>与层堆栈配套</t>
+          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -8651,54 +8704,50 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·气体组成</t>
+          <t>▸衬底·顶表面</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>气瓶标签或CoA声明的固定组成；单组分100%表示纯气，多组分表示供应商预混气</t>
+          <t>实验放样时实际暴露的最上层表面</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>[{species: 气体词表|other, other_name?, volume_percent}]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>vol%</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(气瓶)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>[{"species":"H2","volume_percent":5},{"species":"Ar","volume_percent":95}]</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13真实试填反馈</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>依标签或CoA登记一次；实验只引用该气瓶版本，不重复填配比</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>{"item_required":["species","volume_percent"],"sum":100,"tolerance":0.01,"unique_by":["species","other_name"]}</t>
-        </is>
-      </c>
+          <t>与层堆栈配套</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -8708,50 +8757,54 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸气瓶·气体组成</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>气瓶标签或CoA声明的固定组成；单组分100%表示纯气，多组分表示供应商预混气</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级</t>
+          <t>[{species: 气体词表|other, other_name?, volume_percent}]</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>vol%</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(气瓶)</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>[{"species":"H2","volume_percent":5},{"species":"Ar","volume_percent":95}]</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-08-13真实试填反馈</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>有供应商等级标签可照录；没有则留空</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr"/>
+          <t>依标签或CoA登记一次；实验只引用该气瓶版本，不重复填配比</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>{"item_required":["species","volume_percent"],"sum":100,"tolerance":0.01,"unique_by":["species","other_name"]}</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -8761,112 +8814,116 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
+          <t>▸气瓶·纯度等级</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>下拉</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>6N/5N/4N/工业级</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>5N</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>有供应商等级标签可照录；没有则留空</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
           <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>钢瓶追溯号</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>GC-Ar-07</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr"/>
-      <c r="K32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>装置名称</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>人读名</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="inlineStr">
-        <is>
-          <t>1号双温区管式炉</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
-      <c r="K34" s="11" t="inlineStr"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -8876,17 +8933,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>装置名称</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>人读名</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -8899,26 +8956,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>定义项（实体版本外层元数据）</t>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>对标 v1 setup_version_snapshot</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
@@ -8929,22 +8982,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>装置来源</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>商业设备/实验室自制/改造设备</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -8952,22 +9005,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>定义项（实体版本外层元数据）</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>商业设备</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>对标 v1 setup_version_snapshot</t>
+        </is>
+      </c>
       <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
@@ -8978,22 +9035,22 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>制造商或品牌</t>
+          <t>装置来源</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
+          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>商业设备/实验室自制/改造设备</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -9001,14 +9058,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>条件选填(商业设备或改造设备)</t>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶</t>
+          <t>商业设备</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -9027,12 +9084,12 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>制造商或品牌</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>制造商给出的设备型号</t>
+          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -9057,7 +9114,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>OTF-1200X</t>
+          <t>合肥科晶</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -9076,12 +9133,12 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>设计或建造单位</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置的设计或建造单位</t>
+          <t>制造商给出的设备型号</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -9101,12 +9158,12 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>条件选填(实验室自制)</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>二维材料课题组</t>
+          <t>OTF-1200X</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -9125,12 +9182,12 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>内部型号</t>
+          <t>设计或建造单位</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置使用的内部型号或版本名称</t>
+          <t>实验室自制装置的设计或建造单位</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -9155,7 +9212,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>CVD-LAB-A</t>
+          <t>二维材料课题组</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -9174,12 +9231,12 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>改造内容</t>
+          <t>内部型号</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
+          <t>实验室自制装置使用的内部型号或版本名称</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -9199,12 +9256,12 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>条件选填(改造设备)</t>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>更换三温区加热模块并增加独立控温</t>
+          <t>CVD-LAB-A</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -9223,12 +9280,12 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>实验室装置编号（资产编号）</t>
+          <t>改造内容</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
+          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -9246,26 +9303,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>条件选填(改造设备)</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>更换三温区加热模块并增加独立控温</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B·2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
@@ -9276,17 +9329,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>实验室装置编号（资产编号）</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -9296,7 +9349,7 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -9306,20 +9359,20 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr"/>
-      <c r="K43" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>review§4.1B·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -9329,27 +9382,27 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -9359,20 +9412,20 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
-        </is>
-      </c>
-      <c r="K44" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -9382,27 +9435,27 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -9412,15 +9465,19 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
+        </is>
+      </c>
       <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
@@ -9431,22 +9488,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -9461,19 +9518,15 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
@@ -9484,47 +9537,47 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>必填；按炉管截面填写</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr"/>
@@ -9537,47 +9590,47 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>壁型</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr"/>
@@ -9590,22 +9643,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>壁型</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -9613,24 +9666,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr"/>
@@ -9643,22 +9696,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>外场能力</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光、电或等离子体能力</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>无/光/电/等离子体</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -9666,14 +9719,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
@@ -9683,7 +9736,7 @@
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr"/>
@@ -9696,22 +9749,22 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>外场能力</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图及文字说明</t>
+          <t>装置具备的光、电或等离子体能力</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>无/光/电/等离子体</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -9719,22 +9772,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+        </is>
+      </c>
       <c r="K51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
@@ -9745,116 +9802,116 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
+          <t>装置示意图与描述</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>装置照片或示意图及文字说明</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>FileAsset引用+自由</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>{file_asset_id, sha256, note}</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>setup.png</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
           <t>可更换部件绑定</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>当前Setup版本实际安装的炉管、传感器、MFC、压力计等部件</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>JSON数组</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>[{component_id,role,position?}]</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>[{"component_id":"UUID","role":"furnace_tube"}]</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>2026-07-28深度审查</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>部件身份、校准和维护走独立生命周期事件</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="K53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
         </is>
       </c>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>仪器编号</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>唯一编号</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>RAMAN-1</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr"/>
-      <c r="K54" s="11" t="inlineStr"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -9864,22 +9921,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -9894,19 +9951,15 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
@@ -9917,22 +9970,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>光镜/SEM/Raman/低波数Raman/PL/AFM/XRD/TEM/其他</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -9940,22 +9993,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
+        </is>
+      </c>
       <c r="K56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
@@ -9966,12 +10023,12 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -9996,7 +10053,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -10015,12 +10072,12 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -10038,14 +10095,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -10064,12 +10121,12 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -10099,14 +10156,10 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
@@ -10117,12 +10170,12 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -10147,15 +10200,19 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr"/>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
       <c r="K60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
@@ -10166,22 +10223,22 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -10196,19 +10253,15 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr"/>
       <c r="K61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
@@ -10219,22 +10272,22 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>测量能力配置</t>
+          <t>关键固定配置</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>仪器版本支持的测量方法及其可选固定配置</t>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>[{code,configuration}]</t>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -10242,24 +10295,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>[{"code":"Raman","configuration":{"lasers_nm":[532]}}]</t>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>本次MeasurementRun只能选择这里声明的能力</t>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr"/>
@@ -10272,52 +10325,105 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
+          <t>支持的表征方法</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>JSON数组</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>[{code,configuration}]</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>[{"code":"Raman","configuration":{}}]</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>UI 使用勾选项，不要求用户手写 JSON；本次 MeasurementRun 只能选择这里声明的能力</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
           <t>最近校准或维护日期</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>校准/维护日期</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J63" s="11" t="inlineStr"/>
-      <c r="K63" s="11" t="inlineStr"/>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10330,7 +10436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12008,20 +12114,64 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.20</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>实体/物料批次</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>云母衬底增加白云母、金云母和氟金云母类型选择，并由系统生成理想化学式，避免选择材料后在表单顶部突然出现手填化学式</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01用户试填反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.21</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>实体/制备/样品与表征流程</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>仪器能力改为勾选、日期改为日期控件、装置使用身份标签、异常改为显式确认、表征入口保留样品上下文，并在编辑后清除旧校验错误</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01全表单交互复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>最小可复现核心(27项，含条件必填)</t>
         </is>
       </c>
-      <c r="C80" s="11" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
         </is>
       </c>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>目标性能</t>
+          <t>实验目标</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>应用导向的目标性能（写清想要什么性能 + 打算用什么方法/判据衡量）</t>
+          <t>本炉希望获得的目标性能或需要验证的研究目标</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>当前炉管的累计清洗或更换次数，以及本次实验是最近一次清洗或更换后的第几次使用</t>
+          <t>当前炉管的清洗或更换累计次数，以及本次是最近一次清洗或更换后的第几炉</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>每炉手填；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
+          <t>界面分为“清洗或更换累计次数”和“清洗或更换后第几炉”；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>使用前处理</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>前驱体放置位置</t>
+          <t>热电偶相对位置</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>前驱体加热温区</t>
+          <t>前驱体所在温区</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>预处理（有序步骤）</t>
+          <t>衬底处理（有序步骤）</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>所在温区与热电偶距离</t>
+          <t>所在温区与热电偶相对位置</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
@@ -4749,22 +4749,22 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>异常情况确认</t>
+          <t>本炉发生过异常</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>明确确认本炉是否发生异常，避免将未填写误判为无异常</t>
+          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>勾选框</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>勾选=是；未勾选=否</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未勾选</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈</t>
+          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>选择是时至少填写一条过程异常事件</t>
+          <t>勾选时至少填写一条过程异常事件</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr"/>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>反应压力类别</t>
+          <t>反应压力条件</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>预处理操作</t>
+          <t>实验前准备操作</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -10436,7 +10436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12158,20 +12158,64 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.22</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>§3/§5 生长条件与装置履历</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>生长条件按实验前准备、温度、气体、反应压力、降温和异常分区；温度步骤移除待判断与初始温度伪时长；异常改为勾选框，并缩短温区和炉管履历文案</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02用户界面复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>v4.0-alpha.23</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>§1b/§3/§4/§5 制备记录填写体验</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>缩短晶体结构、实验目标、热电偶相对位置、使用前处理、衬底处理和压力条件文案；明确必填空状态与提交检查，并减少气体首段录入步骤</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02用户全流程复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>最小可复现核心(27项，含条件必填)</t>
         </is>
       </c>
-      <c r="C82" s="11" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
         </is>
       </c>
-      <c r="D82" s="11" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>选填的实验前操作；每项记录实际持续时间，气路置换引用实际气瓶版本</t>
+          <t>选填的实验前操作；抽真空优先记录终点绝对压力，无压力读数时记录持续时间，气路置换引用实际气瓶版本</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: pump_down|gas_exchange|leak_check|other, duration_min, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, snapshot?}], other_name?}</t>
+          <t>{operation_type: pump_down|gas_exchange|leak_check|other, duration_min?, target_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, snapshot?}], other_name?}</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: gas_exchange, duration_min: 10, cycle_count: 3, gas_sources: [{material_lot_id: UUID, material_lot_version: 2}]}]</t>
+          <t>[{operation_type: pump_down, target_absolute_pressure_Pa: 10}, {operation_type: gas_exchange, duration_min: 10, cycle_count: 3, gas_sources: [{material_lot_id: UUID, material_lot_version: 2}]}]</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>置换可引用一瓶预混气或多瓶现场混合气；固定组成仅在气瓶版本登记</t>
+          <t>抽真空的 target_absolute_pressure_Pa 与 duration_min 至少填一项，已填项必须大于 0；置换可引用一瓶预混气或多瓶现场混合气，固定组成仅在气瓶版本登记</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr"/>
@@ -10436,7 +10436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12202,20 +12202,42 @@
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.24</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>§5 实验前准备</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>抽真空优先记录终点绝对压力；有压力读数时持续时间改为选填，无压力读数时持续时间必填</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02用户实验前准备复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>最小可复现核心(27项，含条件必填)</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
         </is>
       </c>
-      <c r="D84" s="11" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>晶面取向与抛光（来自批次）</t>
+          <t>标称晶面取向（来自批次）</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>单晶衬底的晶面或晶轴取向及抛光面；引用批次后只读</t>
+          <t>批次标称晶面、取向状态或供应商切型；SiO₂/Si指底层Si；历史混合文本保留原意</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>例如 (100)、c面、a面</t>
+          <t>规范晶面指数或明确的未知/非晶/多晶状态</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>c面；单面抛</t>
+          <t>(0 0 0 1)</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>偏切信息（来自批次）</t>
+          <t>抛光状态（来自批次）</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
+          <t>批次独立登记的抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>单面抛/双面抛/未抛光/未知</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填（来自批次）</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>single_side_polished</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
+          <t>不从晶面或非晶状态推断抛光；旧记录的混合文本不重写</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4145,27 +4145,27 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>偏切角（相对标称晶面，来自批次）</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -4185,14 +4185,10 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -4202,17 +4198,17 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>偏切方向（来自批次）</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -4222,7 +4218,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -4232,20 +4228,24 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴偏0.2°</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="inlineStr"/>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -4255,50 +4255,50 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度（来自批次）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr"/>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24用户走查</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -4308,22 +4308,22 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>标称表面粗糙度（来自批次）</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -4331,27 +4331,27 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G75" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J75" s="11" t="inlineStr">
-        <is>
-          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
-        </is>
-      </c>
-      <c r="K75" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr"/>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -4361,47 +4361,47 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>本片实际尺寸与姿态</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>片间生长面相对关系</t>
+          <t>本片实际尺寸与姿态</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
+          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>衬底片间关系数组</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4437,14 +4437,14 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>选填（仅多片衬底且存在该关系时）</t>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
+          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
@@ -4467,47 +4467,47 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>衬底处理（有序步骤）</t>
+          <t>片间生长面相对关系</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>衬底片间关系数组</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外臭氧联合处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外臭氧联合处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
+          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>选填（仅多片衬底且存在该关系时）</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
+          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-09-03用户复核</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外臭氧联合处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr"/>
@@ -4520,54 +4520,50 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>衬底处理（有序步骤）</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外臭氧联合处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外臭氧联合处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G79" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K79" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外臭氧联合处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -4577,27 +4573,27 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
@@ -4607,20 +4603,24 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>与时间间隔独立保存</t>
-        </is>
-      </c>
-      <c r="K80" s="11" t="inlineStr"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -4630,47 +4630,47 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>所在温区与相对测温点位置</t>
+          <t>暴露环境</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>第几温区、距离(±)</t>
+          <t>处理完成到放入实验装置期间所处环境</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>温区距离对象</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, distance_mm}</t>
+          <t>空气/氮气/真空/其他</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>温区2，+15</t>
+          <t>空气</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>上游为负、下游为正</t>
+          <t>与时间间隔独立保存</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -4683,22 +4683,22 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>轴向位置</t>
+          <t>所在温区与相对测温点位置</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>本片衬底相对装置轴向原点的位置</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -4706,24 +4706,24 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>2026-07-30产品简化</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>仅兼容旧记录；新记录统一填写所在温区与测温点距离，不再使用未定义物理原点的全局轴向位置</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr"/>
@@ -4736,166 +4736,166 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
+          <t>轴向位置</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>本片衬底相对装置轴向原点的位置</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-30产品简化</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>仅兼容旧记录；新记录统一填写所在温区与测温点距离，不再使用未定义物理原点的全局轴向位置</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="C83" s="11" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>本片衬底摆放或处理的补充说明</t>
         </is>
       </c>
-      <c r="D83" s="11" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>自由</t>
         </is>
       </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr">
+      <c r="H84" s="11" t="inlineStr">
         <is>
           <t>靠近气体入口</t>
         </is>
       </c>
-      <c r="I83" s="11" t="inlineStr">
+      <c r="I84" s="11" t="inlineStr">
         <is>
           <t>2026-07-30产品简化</t>
         </is>
       </c>
-      <c r="J83" s="11" t="inlineStr"/>
-      <c r="K83" s="11" t="inlineStr"/>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
         </is>
       </c>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>过程阶段</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr">
-        <is>
-          <t>兼容已有具名过程阶段；新记录可留空，实际时间由过程通道和操作派生</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>过程阶段数组</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>{segment_key, segment_type, sequence, start_s, end_s, label?, note?}</t>
-        </is>
-      </c>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G85" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史修订只读兼容）</t>
-        </is>
-      </c>
-      <c r="H85" s="11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-07用户复核</t>
-        </is>
-      </c>
-      <c r="J85" s="11" t="inlineStr">
-        <is>
-          <t>不要求用户划分反应开始或手算阶段起止时间</t>
-        </is>
-      </c>
-      <c r="K85" s="11" t="inlineStr"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>过程通道</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>温度、气体与压力程序</t>
+          <t>过程阶段</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
+          <t>兼容已有具名过程阶段；新记录可留空，实际时间由过程通道和操作派生</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>强类型过程通道数组</t>
+          <t>过程阶段数组</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
+          <t>{segment_key, segment_type, sequence, start_s, end_s, label?, note?}</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>按通道</t>
-        </is>
-      </c>
-      <c r="G86" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>未发布（历史修订只读兼容）</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-08-07用户复核</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
+          <t>不要求用户划分反应开始或手算阶段起止时间</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr"/>
@@ -4908,54 +4908,50 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>过程总时长</t>
+          <t>温度、气体与压力程序</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
+          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>强类型过程通道数组</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>按通道</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>必填（历史记录可缺省，不推算补值）</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户确认</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -4965,75 +4961,79 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>本炉发生过异常</t>
+          <t>过程总时长</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
+          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>勾选框</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>勾选=是；未勾选=否</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>必填</t>
+          <t>必填（历史记录可缺省，不推算补值）</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>未勾选</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
+          <t>2026-09-04用户确认</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>勾选时至少填写一条过程异常事件</t>
-        </is>
-      </c>
-      <c r="K88" s="11" t="inlineStr"/>
+          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>过程通道</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件</t>
+          <t>本炉发生过异常</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>相对于当地环境大气压的减压、常压或加压条件</t>
+          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>勾选框</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>atmospheric/low_pressure/high_pressure</t>
+          <t>勾选=是；未勾选=否</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -5048,17 +5048,17 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>low_pressure</t>
+          <t>未勾选</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
+          <t>勾选时至少填写一条过程异常事件</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
@@ -5066,17 +5066,17 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>降温方式</t>
+          <t>反应压力条件</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>本炉实际采用的降温方式</t>
+          <t>相对于当地环境大气压的减压、常压或加压条件</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
+          <t>atmospheric/low_pressure/high_pressure</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling</t>
+          <t>low_pressure</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
+          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr"/>
@@ -5124,22 +5124,22 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>降温顺序</t>
+          <t>降温方式</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
+          <t>本炉实际采用的降温方式</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>有序降温操作数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>{method, lid_open_temperature_C?, other_name?}</t>
+          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -5147,24 +5147,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G91" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=staged_cooling)</t>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
+          <t>furnace_cooling</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户确认</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
+          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr"/>
@@ -5177,22 +5177,22 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>其他降温方式</t>
+          <t>降温顺序</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>降温方式选择其他时的具体操作</t>
+          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>有序降温操作数组</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{method, lid_open_temperature_C?, other_name?}</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>条件必填(降温方式=other)</t>
+          <t>条件必填(降温方式=staged_cooling)</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>打开保温层自然冷却</t>
+          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-09-04用户确认</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>仅选择其他时保存</t>
+          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr"/>
@@ -5230,17 +5230,17 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>旧记录设定降温速率</t>
+          <t>其他降温方式</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>保留旧记录独立填写的设定降温速率；新记录按温度程序各降温段派生</t>
+          <t>降温方式选择其他时的具体操作</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -5250,17 +5250,17 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>℃/min</t>
-        </is>
-      </c>
-      <c r="G93" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史兼容）</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=other)</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>打开保温层自然冷却</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -5270,14 +5270,10 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>不再要求新记录填写单一降温速率；旧记录保留，不解释为实测值</t>
-        </is>
-      </c>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>仅选择其他时保存</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -5287,12 +5283,12 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>开盖温度</t>
+          <t>旧记录设定降温速率</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>开盖冷却时实际开盖的温度</t>
+          <t>保留旧记录独立填写的设定降温速率；新记录按温度程序各降温段派生</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
@@ -5307,17 +5303,17 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G94" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=open_lid_cooling)</t>
+          <t>℃/min</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>未发布（历史兼容）</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -5327,60 +5323,64 @@
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>仅开盖冷却时保存</t>
-        </is>
-      </c>
-      <c r="K94" s="11" t="inlineStr"/>
+          <t>不再要求新记录填写单一降温速率；旧记录保留，不解释为实测值</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>开盖温度</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>开盖冷却时实际开盖的温度</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=open_lid_cooling)</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
+          <t>仅开盖冷却时保存</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr"/>
@@ -5393,22 +5393,22 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>实验前准备操作</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>预处理操作数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -5418,22 +5418,22 @@
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13师兄试填复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr"/>
@@ -5441,52 +5441,52 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>实验前准备操作</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-08-13师兄试填复核</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr"/>
@@ -5499,27 +5499,27 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr"/>
@@ -5547,32 +5547,32 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>℃ 随时间</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr"/>
@@ -5600,32 +5600,32 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件与工作绝对压力</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>常压；或低压 500 Pa</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -5645,44 +5645,40 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K100" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
-        </is>
-      </c>
+          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>反应压力条件与工作绝对压力</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -5692,50 +5688,54 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>常压；或低压 500 Pa</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
-        </is>
-      </c>
-      <c r="K101" s="11" t="inlineStr"/>
+          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
@@ -5745,17 +5745,17 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr"/>
@@ -5763,42 +5763,42 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>附加能力使用记录</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
+          <t>℃·℃/min</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表；旧单名称兼容，不按标点猜拆</t>
+          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr"/>
@@ -5816,52 +5816,52 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>附加能力使用记录</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>按参数</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表；旧单名称兼容，不按标点猜拆</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr"/>
@@ -5874,120 +5874,120 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
+          <t>其他记录名称</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>未发布（旧过程步兼容）</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>临时移动源舟</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24整改</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>禁止仅保存“其他”</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
           <t>其他记录说明</t>
         </is>
       </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
-      <c r="D105" s="11" t="inlineStr">
+      <c r="D106" s="11" t="inlineStr">
         <is>
           <t>自由</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F105" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G105" s="13" t="inlineStr">
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
         <is>
           <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
-      <c r="H105" s="11" t="inlineStr">
+      <c r="H106" s="11" t="inlineStr">
         <is>
           <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
-      <c r="I105" s="11" t="inlineStr">
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J105" s="11" t="inlineStr">
+      <c r="J106" s="11" t="inlineStr">
         <is>
           <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
-      <c r="K105" s="11" t="inlineStr"/>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="K106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>§6 过程事件 Process Events（记录异常、中断与计划变更等客观事件；只记客观事实，不判成败）</t>
         </is>
       </c>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
-      <c r="E106" s="8" t="n"/>
-      <c r="F106" s="8" t="n"/>
-      <c r="G106" s="8" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="8" t="n"/>
-      <c r="J106" s="8" t="n"/>
-      <c r="K106" s="8" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t>事件标识</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr">
-        <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
-        </is>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>系统生成键</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="F107" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G107" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H107" s="11" t="inlineStr">
-        <is>
-          <t>event_1</t>
-        </is>
-      </c>
-      <c r="I107" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24整改</t>
-        </is>
-      </c>
-      <c r="J107" s="11" t="inlineStr">
-        <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
-        </is>
-      </c>
-      <c r="K107" s="11" t="inlineStr"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="8" t="n"/>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差</t>
+          <t>事件标识</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>多选+其他</t>
+          <t>系统生成键</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -6027,17 +6027,17 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>供气中断</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果；旧类型读取时归并并保留原类型文字，不修改历史原文</t>
+          <t>创建事件时生成，排序和编辑不得改变</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr"/>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>受影响对象</t>
+          <t>观察到的偏差</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差涉及的实验对象</t>
+          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>多选+其他</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -6073,14 +6073,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G109" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>气路</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
+          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果；旧类型读取时归并并保留原类型文字，不修改历史原文</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr"/>
@@ -6103,37 +6103,37 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>开始时间</t>
+          <t>受影响对象</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件开始时间</t>
+          <t>观察到的偏差涉及的实验对象</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G110" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>气路</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="J110" s="11" t="inlineStr">
         <is>
-          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
+          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr"/>
@@ -6156,12 +6156,12 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>结束时间</t>
+          <t>开始时间</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件结束时间</t>
+          <t>相对本炉实验开始时刻的事件开始时间</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
@@ -6179,14 +6179,14 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G111" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>填写时不得早于开始时间</t>
+          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr"/>
@@ -6209,27 +6209,27 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>处理结果</t>
+          <t>结束时间</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>异常发生后过程是否恢复或终止</t>
+          <t>相对本炉实验开始时刻的事件结束时间</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>已恢复/部分恢复/实验终止/未知</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>已恢复</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="J112" s="11" t="inlineStr">
         <is>
-          <t>未知可显式记录，不等同于对产物成败的判定</t>
+          <t>填写时不得早于开始时间</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr"/>
@@ -6262,12 +6262,12 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>对数据有效性的影响</t>
+          <t>处理结果</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
+          <t>异常发生后过程是否恢复或终止</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>不影响/部分影响/数据无效/未知</t>
+          <t>已恢复/部分恢复/实验终止/未知</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>部分影响</t>
+          <t>已恢复</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>只判断过程数据有效性，不判定产物成败</t>
+          <t>未知可显式记录，不等同于对产物成败的判定</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr"/>
@@ -6315,22 +6315,22 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因</t>
+          <t>对数据有效性的影响</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
+          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
+          <t>不影响/部分影响/数据无效/未知</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>设备故障</t>
+          <t>部分影响</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="J114" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
+          <t>只判断过程数据有效性，不判定产物成败</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr"/>
@@ -6368,22 +6368,22 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>怀疑原因</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -6393,22 +6393,22 @@
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>选填；观察到的偏差包含其他时必填</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>设备故障</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
+          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr"/>
@@ -6421,22 +6421,22 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>干预动作</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>事件发生后实际采取的操作</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选填；观察到的偏差包含其他时必填</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>恢复供应</t>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr"/>
@@ -6474,27 +6474,27 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>排除的数据时间范围</t>
+          <t>干预动作</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>因该事件不应参与后续分析的时间区间</t>
+          <t>事件发生后实际采取的操作</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>时间区间数组</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>[{start_s, end_s}]</t>
+          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>[{start_s: 1680, end_s: 1800}]</t>
+          <t>恢复供应</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
+          <t>与事件说明独立保存</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr"/>
@@ -6527,120 +6527,120 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
+          <t>排除的数据时间范围</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>因该事件不应参与后续分析的时间区间</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>时间区间数组</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>[{start_s, end_s}]</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>[{start_s: 1680, end_s: 1800}]</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>科学修订契约</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
           <t>事件附件</t>
         </is>
       </c>
-      <c r="C118" s="11" t="inlineStr">
+      <c r="C119" s="11" t="inlineStr">
         <is>
           <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
+      <c r="D119" s="11" t="inlineStr">
         <is>
           <t>FileAsset引用数组</t>
         </is>
       </c>
-      <c r="E118" s="11" t="inlineStr">
+      <c r="E119" s="11" t="inlineStr">
         <is>
           <t>FileAsset UUID列表</t>
         </is>
       </c>
-      <c r="F118" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G118" s="13" t="inlineStr">
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H118" s="11" t="inlineStr">
+      <c r="H119" s="11" t="inlineStr">
         <is>
           <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
-      <c r="I118" s="11" t="inlineStr">
+      <c r="I119" s="11" t="inlineStr">
         <is>
           <t>2026-07-24导师走查</t>
         </is>
       </c>
-      <c r="J118" s="11" t="inlineStr">
+      <c r="J119" s="11" t="inlineStr">
         <is>
           <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
-      <c r="K118" s="11" t="inlineStr"/>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="10" t="inlineStr">
+      <c r="K119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>§7 旧扁平结果字段（未发布；由 MeasurementRun → AnalysisRun → PropertyValue / MaterialAssertion 替代）</t>
         </is>
       </c>
-      <c r="B119" s="8" t="n"/>
-      <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="8" t="n"/>
-      <c r="F119" s="8" t="n"/>
-      <c r="G119" s="8" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="8" t="n"/>
-      <c r="J119" s="8" t="n"/>
-      <c r="K119" s="8" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>表征</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t>表征方法</t>
-        </is>
-      </c>
-      <c r="C120" s="11" t="inlineStr">
-        <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
-        </is>
-      </c>
-      <c r="D120" s="11" t="inlineStr">
-        <is>
-          <t>下拉+其他</t>
-        </is>
-      </c>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
-        </is>
-      </c>
-      <c r="F120" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G120" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H120" s="11" t="inlineStr">
-        <is>
-          <t>Raman</t>
-        </is>
-      </c>
-      <c r="I120" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J120" s="15" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
-        </is>
-      </c>
-      <c r="K120" s="11" t="inlineStr"/>
+      <c r="B120" s="8" t="n"/>
+      <c r="C120" s="8" t="n"/>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="8" t="n"/>
+      <c r="F120" s="8" t="n"/>
+      <c r="G120" s="8" t="n"/>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="8" t="n"/>
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -6650,22 +6650,22 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>表征方法</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -6688,9 +6688,9 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J121" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
+      <c r="J121" s="15" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr"/>
@@ -6703,17 +6703,17 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -6733,41 +6733,45 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J122" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
+        </is>
+      </c>
       <c r="K122" s="11" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>表征</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
@@ -6782,19 +6786,15 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J123" s="15" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr"/>
       <c r="K123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
@@ -6805,22 +6805,22 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
@@ -6835,17 +6835,17 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J124" s="15" t="inlineStr">
         <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr"/>
@@ -6858,17 +6858,17 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
@@ -6888,24 +6888,20 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J125" s="11" t="inlineStr">
-        <is>
-          <t>历史字段，保留原记录；新表征不录入层数判定，也不将未检出写成层数 0</t>
-        </is>
-      </c>
-      <c r="K125" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J125" s="15" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -6915,12 +6911,12 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
@@ -6935,7 +6931,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
@@ -6945,7 +6941,7 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -6955,12 +6951,12 @@
       </c>
       <c r="J126" s="11" t="inlineStr">
         <is>
-          <t>量化口径仍须随表征条件记录</t>
+          <t>历史字段，保留原记录；新表征不录入层数判定，也不将未检出写成层数 0</t>
         </is>
       </c>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0,"le":100}</t>
+          <t>{"ge":0,"type":"integer"}</t>
         </is>
       </c>
     </row>
@@ -6972,12 +6968,12 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -6992,7 +6988,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
@@ -7002,7 +6998,7 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -7010,10 +7006,14 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J127" s="11" t="inlineStr"/>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>量化口径仍须随表征条件记录</t>
+        </is>
+      </c>
       <c r="K127" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0,"le":100}</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>μm</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -7066,7 +7066,7 @@
       <c r="J128" s="11" t="inlineStr"/>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -7078,120 +7078,124 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
+          <t>成核密度</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>指定统计区域内单位面积成核点数量</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>cm⁻²</t>
+        </is>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr"/>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>实测产物</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
           <t>关键谱学指标</t>
         </is>
       </c>
-      <c r="C129" s="11" t="inlineStr">
+      <c r="C130" s="11" t="inlineStr">
         <is>
           <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>结构化指标数组</t>
         </is>
       </c>
-      <c r="E129" s="11" t="inlineStr">
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
-      <c r="F129" s="11" t="inlineStr">
+      <c r="F130" s="11" t="inlineStr">
         <is>
           <t>按指标</t>
         </is>
       </c>
-      <c r="G129" s="13" t="inlineStr">
+      <c r="G130" s="13" t="inlineStr">
         <is>
           <t>未发布</t>
         </is>
       </c>
-      <c r="H129" s="11" t="inlineStr">
+      <c r="H130" s="11" t="inlineStr">
         <is>
           <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
-      <c r="I129" s="11" t="inlineStr">
+      <c r="I130" s="11" t="inlineStr">
         <is>
           <t>复审/导师</t>
         </is>
       </c>
-      <c r="J129" s="15" t="inlineStr">
+      <c r="J130" s="15" t="inlineStr">
         <is>
           <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
         </is>
       </c>
-      <c r="K129" s="11" t="inlineStr">
+      <c r="K130" s="11" t="inlineStr">
         <is>
           <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="10" t="inlineStr">
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
         </is>
       </c>
-      <c r="B130" s="8" t="n"/>
-      <c r="C130" s="8" t="n"/>
-      <c r="D130" s="8" t="n"/>
-      <c r="E130" s="8" t="n"/>
-      <c r="F130" s="8" t="n"/>
-      <c r="G130" s="8" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="8" t="n"/>
-      <c r="J130" s="8" t="n"/>
-      <c r="K130" s="8" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B131" s="11" t="inlineStr">
-        <is>
-          <t>靶材（批次）</t>
-        </is>
-      </c>
-      <c r="C131" s="11" t="inlineStr">
-        <is>
-          <t>靶材化学身份 + 批次</t>
-        </is>
-      </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>批次库</t>
-        </is>
-      </c>
-      <c r="F131" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G131" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H131" s="11" t="inlineStr">
-        <is>
-          <t>MoS₂ 靶-T01</t>
-        </is>
-      </c>
-      <c r="I131" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J131" s="11" t="inlineStr"/>
-      <c r="K131" s="11" t="inlineStr"/>
+      <c r="B131" s="8" t="n"/>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="8" t="n"/>
+      <c r="G131" s="8" t="n"/>
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="8" t="n"/>
+      <c r="J131" s="8" t="n"/>
+      <c r="K131" s="8" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -7201,27 +7205,27 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
@@ -7231,7 +7235,7 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -7240,11 +7244,7 @@
         </is>
       </c>
       <c r="J132" s="11" t="inlineStr"/>
-      <c r="K132" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K132" s="11" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -7293,7 +7293,11 @@
         </is>
       </c>
       <c r="J133" s="11" t="inlineStr"/>
-      <c r="K133" s="11" t="inlineStr"/>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
@@ -7303,27 +7307,27 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
@@ -7333,7 +7337,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -7342,11 +7346,7 @@
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr"/>
-      <c r="K134" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
+      <c r="K134" s="11" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
@@ -7356,27 +7356,27 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
@@ -7397,7 +7397,7 @@
       <c r="J135" s="11" t="inlineStr"/>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"gt":0,"require_value":true}</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>沉积速率</t>
+          <t>预溅射与挡板时序</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>速率（QCM 等）</t>
+          <t>预溅射时长、挡板开合时序</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>nm/s</t>
+          <t>min·s</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>预溅 5 min</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -7454,17 +7454,70 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>沉积速率</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>速率（QCM 等）</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>nm/s</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="inlineStr"/>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A119:K119"/>
+    <mergeCell ref="A131:K131"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A130:K130"/>
     <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A107:K107"/>
     <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A85:K85"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A106:K106"/>
+    <mergeCell ref="A120:K120"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7476,7 +7529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8700,22 +8753,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光</t>
+          <t>▸衬底·石英类型</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>区分石英单晶与非晶石英玻璃；不根据石英名称推断</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>石英单晶·熔融石英／石英玻璃·未知／供应商未提供</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -8725,29 +8778,25 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>选填(仅供应商明确提供时)</t>
+          <t>选填(石英；填写晶面前明确类型)</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>石英单晶</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>供应商资料明确给出且实验需要区分时填写；实验引用批次后只读带出</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>{"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>旧批次未明确类型时保持未知；熔融石英无晶面指数</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -8757,22 +8806,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切信息</t>
+          <t>▸衬底·标称晶面取向</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
+          <t>标称表面晶面或明确取向状态；SiO₂/Si记录底层Si的晶面，非表面氧化层</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>未知／供应商未提供·非晶，不适用·多晶，无单一取向·供应商切型·其他</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -8782,22 +8831,22 @@
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>(0 0 0 1)</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
+          <t>按substrate_orientation提供候选并校验；不自动选择常见晶面；供应商切型须附原文；抛光独立</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr"/>
@@ -8810,17 +8859,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切角</t>
+          <t>▸衬底·供应商切型原文</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角</t>
+          <t>无法直接作为标称晶面指数记录的供应商切型原文</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -8830,34 +8879,30 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(供应商切型)</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>AT-cut，按供应商规格书</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>大于0时必须同时填写substrate_miscut_direction</t>
-        </is>
-      </c>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>保留原文，不猜测转换为晶面指数；最长128字符</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -8867,22 +8912,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切方向</t>
+          <t>▸衬底·抛光状态</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向</t>
+          <t>供应商给出的独立抛光规格；不依赖晶面是否适用或已知</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>单面抛·双面抛·未抛光·未知／供应商未提供</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -8892,22 +8937,22 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴</t>
+          <t>单面抛</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>未填写不代表未抛光；非晶、多晶亦可单独记录</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -8920,50 +8965,54 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·标称表面粗糙度</t>
+          <t>▸衬底·晶向与抛光</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度</t>
+          <t>取向与抛光面</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>文本+下拉</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>晶向；单面抛/双面抛</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>未发布(历史兼容)</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>{availability: not_provided}</t>
+          <t>Si(100)；单面抛</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr"/>
+          <t>历史合并记录保留原文与导出；新录入使用独立的substrate_crystal_plane和substrate_polish</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>{"require_option":true,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -8973,27 +9022,27 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·来料尺寸规格</t>
+          <t>▸衬底·偏切信息</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
+          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
@@ -9003,17 +9052,17 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>不替代每次实验的本片实际尺寸</t>
+          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -9026,27 +9075,27 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·层堆栈</t>
+          <t>▸衬底·偏切角</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
+          <t>实际晶面相对标称晶面的偏切角</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -9056,20 +9105,24 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr"/>
+          <t>大于0时必须同时填写substrate_miscut_direction</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -9079,12 +9132,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·顶表面</t>
+          <t>▸衬底·偏切方向</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>实验放样时实际暴露的最上层表面</t>
+          <t>偏切角所指的晶轴或晶向</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -9109,17 +9162,17 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>c面向a轴</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>与层堆栈配套</t>
+          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -9132,54 +9185,50 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·气体组成</t>
+          <t>▸衬底·标称表面粗糙度</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>气瓶标签或CoA声明的固定组成；单组分100%表示纯气，多组分表示供应商预混气</t>
+          <t>供应商或批次规格中的标称粗糙度</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>[{species: 气体词表|other, other_name?, volume_percent}]</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>vol%</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(气瓶)</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>[{"species":"H2","volume_percent":5},{"species":"Ar","volume_percent":95}]</t>
+          <t>{availability: not_provided}</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13真实试填反馈</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>依标签或CoA登记一次；实验只引用该气瓶版本，不重复填配比</t>
-        </is>
-      </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>{"item_required":["species","volume_percent"],"sum":100,"tolerance":0.01,"unique_by":["species","other_name"]}</t>
-        </is>
-      </c>
+          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -9189,37 +9238,37 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸衬底·来料尺寸规格</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -9229,7 +9278,7 @@
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>有供应商等级标签可照录；没有则留空</t>
+          <t>不替代每次实验的本片实际尺寸</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -9242,137 +9291,185 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·气瓶编号</t>
+          <t>▸衬底·层堆栈</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>钢瓶追溯号</t>
+          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
+          <t>JSON数组</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>MaterialLot</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>▸衬底·顶表面</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>实验放样时实际暴露的最上层表面</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>GC-Ar-07</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr"/>
-      <c r="K35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>与层堆栈配套</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>▸气瓶·气体组成</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>气瓶标签或CoA声明的固定组成；单组分100%表示纯气，多组分表示供应商预混气</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[{species: 气体词表|other, other_name?, volume_percent}]</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>vol%</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(气瓶)</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>[{"species":"H2","volume_percent":5},{"species":"Ar","volume_percent":95}]</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr"/>
+          <t>2026-08-13真实试填反馈</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>依标签或CoA登记一次；实验只引用该气瓶版本，不重复填配比</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>{"item_required":["species","volume_percent"],"sum":100,"tolerance":0.01,"unique_by":["species","other_name"]}</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>▸气瓶·纯度等级</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6N/5N/4N/工业级</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -9380,24 +9477,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>定义项（实体版本外层元数据）</t>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5N</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>对标 v1 setup_version_snapshot</t>
+          <t>有供应商等级标签可照录；没有则留空</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -9405,27 +9502,27 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>装置Setup</t>
+          <t>MaterialLot</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>装置来源</t>
+          <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
+          <t>钢瓶追溯号</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>商业设备/实验室自制/改造设备</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -9433,72 +9530,40 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>商业设备</t>
+          <t>GC-Ar-07</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr"/>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>制造商或品牌</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>条件选填(商业设备或改造设备)</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>合肥科晶</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr"/>
-      <c r="K40" s="11" t="inlineStr"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -9508,12 +9573,12 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>装置名称</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>制造商给出的设备型号</t>
+          <t>人读名</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -9531,19 +9596,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>条件选填(商业设备或改造设备)</t>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>OTF-1200X</t>
+          <t>1号双温区管式炉</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr"/>
@@ -9557,17 +9622,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>设计或建造单位</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置的设计或建造单位</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -9580,22 +9645,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>条件选填(实验室自制)</t>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>定义项（实体版本外层元数据）</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>二维材料课题组</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>对标 v1 setup_version_snapshot</t>
+        </is>
+      </c>
       <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
@@ -9606,22 +9675,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>内部型号</t>
+          <t>装置来源</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置使用的内部型号或版本名称</t>
+          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>商业设备/实验室自制/改造设备</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -9629,14 +9698,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>条件选填(实验室自制)</t>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>CVD-LAB-A</t>
+          <t>商业设备</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -9655,12 +9724,12 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>改造内容</t>
+          <t>制造商或品牌</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
+          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -9680,12 +9749,12 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>条件选填(改造设备)</t>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>更换三温区加热模块并增加独立控温</t>
+          <t>合肥科晶</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -9704,12 +9773,12 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>实验室装置编号（资产编号）</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
+          <t>制造商给出的设备型号</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -9727,26 +9796,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>OTF-1200X</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B·2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr">
-        <is>
-          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
@@ -9757,17 +9822,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>设计或建造单位</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>实验室自制装置的设计或建造单位</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -9777,30 +9842,26 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>二维材料课题组</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr"/>
-      <c r="K46" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+      <c r="K46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -9810,49 +9871,45 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>内部型号</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
+          <t>实验室自制装置使用的内部型号或版本名称</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
+          <t>CVD-LAB-A</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="inlineStr">
-        <is>
-          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
@@ -9863,22 +9920,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>改造内容</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -9886,19 +9943,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>条件选填(改造设备)</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>更换三温区加热模块并增加独立控温</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr"/>
@@ -9912,22 +9969,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>实验室装置编号（资产编号）</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -9942,17 +9999,17 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>review§4.1B·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr"/>
@@ -9965,50 +10022,50 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>必填；按炉管截面填写</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -10018,47 +10075,47 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>反应器类型（热壁/冷壁）</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
+          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr"/>
@@ -10071,22 +10128,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -10094,26 +10151,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
@@ -10124,22 +10177,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>装置附加能力</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光照、电场、等离子体或其他外场能力</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>无/光照/电场/等离子体/其他</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -10154,7 +10207,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -10164,7 +10217,7 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr"/>
@@ -10177,47 +10230,47 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>其他附加能力名称（历史）</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>外场能力选择“其他”时填写可复用的能力名称</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="13" t="inlineStr">
-        <is>
-          <t>历史单名称兼容</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>磁场</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户在线复核</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>一个装置版本登记一个其他外场名称；不同能力需要分别登记时再扩展为结构化列表</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
@@ -10230,22 +10283,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>其他附加能力</t>
+          <t>反应器类型（热壁/冷壁）</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>文本数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -10253,24 +10306,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
-        <is>
-          <t>选择其他时必填；旧单名称兼容</t>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>[磁场, 机械振动]</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09用户制备字段复核</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
@@ -10283,22 +10336,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图及文字说明</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>FileAsset引用+自由</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, sha256, note}</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -10306,22 +10359,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>setup.png</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+        </is>
+      </c>
       <c r="K56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
@@ -10332,22 +10389,22 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>可更换部件绑定</t>
+          <t>装置附加能力</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>当前Setup版本实际安装的炉管、传感器、MFC、压力计等部件</t>
+          <t>装置具备的光照、电场、等离子体或其他外场能力</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>[{component_id,role,position?}]</t>
+          <t>无/光照/电场/等离子体/其他</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -10355,64 +10412,100 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>[{"component_id":"UUID","role":"furnace_tube"}]</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>部件身份、校准和维护走独立生命周期事件</t>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr"/>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="8" t="n"/>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>其他附加能力名称（历史）</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>外场能力选择“其他”时填写可复用的能力名称</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>历史单名称兼容</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>磁场</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03用户在线复核</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>一个装置版本登记一个其他外场名称；不同能力需要分别登记时再扩展为结构化列表</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>其他附加能力</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本数组</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -10425,48 +10518,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>选择其他时必填；旧单名称兼容</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>[磁场, 机械振动]</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="inlineStr"/>
+          <t>2026-09-09用户制备字段复核</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
+        </is>
+      </c>
       <c r="K59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -10474,14 +10571,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -10489,37 +10586,33 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
-        </is>
-      </c>
+      <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>表征仪器</t>
+          <t>装置Setup</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>可更换部件绑定</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>当前Setup版本实际安装的炉管、传感器、MFC、压力计等部件</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[{component_id,role,position?}]</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -10534,65 +10627,37 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>[{"component_id":"UUID","role":"furnace_tube"}]</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr"/>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>部件身份、校准和维护走独立生命周期事件</t>
+        </is>
+      </c>
       <c r="K61" s="11" t="inlineStr"/>
     </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>型号</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>型号</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>LabRAM HR</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr"/>
-      <c r="K62" s="11" t="inlineStr"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -10602,12 +10667,12 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>仪器编号</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>唯一编号</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
@@ -10625,19 +10690,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RAMAN-1</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr"/>
@@ -10651,22 +10716,22 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -10674,24 +10739,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr"/>
@@ -10704,12 +10769,12 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -10727,19 +10792,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★NXfabrication</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr"/>
@@ -10753,22 +10818,22 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -10776,26 +10841,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G66" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr"/>
       <c r="K66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
@@ -10806,22 +10867,22 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>支持的表征方法</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>[{code,configuration}]；code=other 时 configuration.method_names 为方法名称列表</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -10829,26 +10890,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>[{"code":"Raman","configuration":{}}]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>UI 使用多选；其他展开方法名称列表，可逐项添加/删除，名称非空且去首尾空白后长度 1–128、忽略大小写不重复；仍以一个 other 能力行保存多个名称，不改变仪器版本和能力代码唯一约束。</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr"/>
       <c r="K67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
@@ -10859,52 +10916,260 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
+          <t>仪器持久标识</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>所在实验室与位置</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>物理位置</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>A305</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>关键固定配置</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>支持的表征方法</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>JSON数组</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>[{code,configuration}]；code=other 时 configuration.method_names 为方法名称列表</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>[{"code":"Raman","configuration":{}}]</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-28深度审查</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>UI 使用多选；其他展开方法名称列表，可逐项添加/删除，名称非空且去首尾空白后长度 1–128、忽略大小写不重复；仍以一个 other 能力行保存多个名称，不改变仪器版本和能力代码唯一约束。</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
           <t>最近校准或维护日期</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>校准/维护日期</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D72" s="11" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
         <is>
           <t>选填</t>
         </is>
       </c>
-      <c r="H68" s="11" t="inlineStr">
+      <c r="H72" s="11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="11" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -11018,7 +11018,7 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>关键固定配置</t>
+          <t>其他固定配置说明</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>[{code,configuration}]；code=other 时 configuration.method_names 为方法名称列表</t>
+          <t>[{code,configuration}]；configuration.presets=[{name,conditions}]；code=other 时另有 method_names</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>UI 使用多选；其他展开方法名称列表，可逐项添加/删除，名称非空且去首尾空白后长度 1–128、忽略大小写不重复；仍以一个 other 能力行保存多个名称，不改变仪器版本和能力代码唯一约束。</t>
+          <t>每种方法可维护最多50套命名预设；名称去空白后1–128字符，同方法内忽略大小写唯一。conditions复用该方法结构化采集字段、单位及校验，至少一项，不要求整套测试必填参数齐全。表征主动选用后复制为本次实际条件，可调整；预设修改产生新仪器版本，不改历史记录。其他方法继续通过method_names具名；保留历史configuration内容。</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -4535,7 +4535,7 @@
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外臭氧联合处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外臭氧联合处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
+          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外/臭氧表面处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外/臭氧表面处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外臭氧联合处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外/臭氧表面处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr"/>
